--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933127</v>
+        <v>123928438</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,42 +1127,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497133</v>
+        <v>497801</v>
       </c>
       <c r="R5" t="n">
-        <v>7067678</v>
+        <v>7068154</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,7 +1196,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,22 +1215,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,7 +1248,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123928438</v>
+        <v>123925768</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1293,13 +1288,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497801</v>
+        <v>497652</v>
       </c>
       <c r="R6" t="n">
-        <v>7068154</v>
+        <v>7067869</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,7 +1333,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123925768</v>
+        <v>123933127</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,37 +1401,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497652</v>
+        <v>497133</v>
       </c>
       <c r="R7" t="n">
-        <v>7067869</v>
+        <v>7067678</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123928574</v>
+        <v>123932682</v>
       </c>
       <c r="B9" t="n">
-        <v>79897</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1671,41 +1671,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497848</v>
+        <v>497368</v>
       </c>
       <c r="R9" t="n">
-        <v>7068101</v>
+        <v>7067763</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,7 +1749,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1759,6 +1764,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1776,10 +1801,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123929067</v>
+        <v>123933142</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1788,51 +1813,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497903</v>
+        <v>497133</v>
       </c>
       <c r="R10" t="n">
-        <v>7068110</v>
+        <v>7067678</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1861,7 +1881,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1871,12 +1891,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1895,22 +1910,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1928,10 +1943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123927991</v>
+        <v>123933962</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1944,47 +1959,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497659</v>
+        <v>496999</v>
       </c>
       <c r="R11" t="n">
-        <v>7068053</v>
+        <v>7067688</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2013,7 +2018,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2023,12 +2028,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123932385</v>
+        <v>123928574</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2092,25 +2092,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497528</v>
+        <v>497848</v>
       </c>
       <c r="R12" t="n">
-        <v>7067930</v>
+        <v>7068101</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2180,26 +2180,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2217,10 +2197,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123932682</v>
+        <v>123929067</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2233,42 +2213,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497368</v>
+        <v>497903</v>
       </c>
       <c r="R13" t="n">
-        <v>7067763</v>
+        <v>7068110</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2297,7 +2282,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2307,7 +2292,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2326,22 +2316,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2359,10 +2349,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123933142</v>
+        <v>123927991</v>
       </c>
       <c r="B14" t="n">
-        <v>79905</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2371,46 +2361,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497133</v>
+        <v>497659</v>
       </c>
       <c r="R14" t="n">
-        <v>7067678</v>
+        <v>7068053</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2439,7 +2434,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2449,7 +2444,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2463,27 +2463,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123933962</v>
+        <v>123932385</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2537,17 +2537,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496999</v>
+        <v>497528</v>
       </c>
       <c r="R15" t="n">
-        <v>7067688</v>
+        <v>7067930</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123934404</v>
+        <v>123928858</v>
       </c>
       <c r="B51" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7605,47 +7605,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496972</v>
+        <v>497900</v>
       </c>
       <c r="R51" t="n">
-        <v>7067780</v>
+        <v>7068251</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7674,7 +7664,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7684,12 +7674,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7718,12 +7708,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7741,7 +7731,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123928858</v>
+        <v>123928379</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -7781,13 +7771,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497900</v>
+        <v>497732</v>
       </c>
       <c r="R52" t="n">
-        <v>7068251</v>
+        <v>7068101</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7816,7 +7806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7826,12 +7816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7883,10 +7868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123928379</v>
+        <v>123933712</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7895,41 +7880,51 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497732</v>
+        <v>497111</v>
       </c>
       <c r="R53" t="n">
-        <v>7068101</v>
+        <v>7067721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7958,7 +7953,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7968,7 +7963,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7982,27 +7982,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8020,10 +8000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123933712</v>
+        <v>123934404</v>
       </c>
       <c r="B54" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8032,31 +8012,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -8070,10 +8050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497111</v>
+        <v>496972</v>
       </c>
       <c r="R54" t="n">
-        <v>7067721</v>
+        <v>7067780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -8105,7 +8085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8115,12 +8095,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8134,7 +8114,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123934255</v>
+        <v>123928327</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9162,41 +9162,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496932</v>
+        <v>497712</v>
       </c>
       <c r="R62" t="n">
-        <v>7067736</v>
+        <v>7068103</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -9225,7 +9235,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9235,7 +9245,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9249,27 +9264,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9287,10 +9282,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123928327</v>
+        <v>123932608</v>
       </c>
       <c r="B63" t="n">
-        <v>56703</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9299,48 +9294,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497712</v>
+        <v>497492</v>
       </c>
       <c r="R63" t="n">
-        <v>7068103</v>
+        <v>7067833</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -9372,7 +9357,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9382,12 +9367,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9402,6 +9382,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9419,7 +9419,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123932608</v>
+        <v>123934255</v>
       </c>
       <c r="B64" t="n">
         <v>78788</v>
@@ -9455,17 +9455,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497492</v>
+        <v>496932</v>
       </c>
       <c r="R64" t="n">
-        <v>7067833</v>
+        <v>7067736</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123935937</v>
+        <v>123948037</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9713,37 +9713,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497510</v>
+        <v>497443</v>
       </c>
       <c r="R66" t="n">
-        <v>7067357</v>
+        <v>7067840</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9770,21 +9770,11 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:42</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:42</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9793,51 +9783,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123936388</v>
+        <v>123948066</v>
       </c>
       <c r="B67" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9850,34 +9815,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497347</v>
+        <v>497568</v>
       </c>
       <c r="R67" t="n">
-        <v>7067031</v>
+        <v>7067974</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9907,19 +9872,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>18:05</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9930,48 +9890,23 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123935511</v>
+        <v>123948048</v>
       </c>
       <c r="B68" t="n">
         <v>57491</v>
@@ -10005,29 +9940,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497429</v>
+        <v>497417</v>
       </c>
       <c r="R68" t="n">
-        <v>7067368</v>
+        <v>7067613</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -10054,19 +9979,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:29</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10077,51 +9997,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123935971</v>
+        <v>123948050</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10134,37 +10029,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497477</v>
+        <v>496963</v>
       </c>
       <c r="R69" t="n">
-        <v>7067373</v>
+        <v>7067823</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -10191,19 +10086,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10214,51 +10104,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123935623</v>
+        <v>123948061</v>
       </c>
       <c r="B70" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10271,37 +10136,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497400</v>
+        <v>497152</v>
       </c>
       <c r="R70" t="n">
-        <v>7067320</v>
+        <v>7067720</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -10328,19 +10193,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:33</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>17:33</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10351,51 +10211,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123935892</v>
+        <v>123948062</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10408,37 +10243,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497488</v>
+        <v>497431</v>
       </c>
       <c r="R71" t="n">
-        <v>7067338</v>
+        <v>7067834</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10465,19 +10300,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>17:40</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10488,48 +10318,23 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123936336</v>
+        <v>123948078</v>
       </c>
       <c r="B72" t="n">
         <v>57491</v>
@@ -10563,26 +10368,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497296</v>
+        <v>497569</v>
       </c>
       <c r="R72" t="n">
-        <v>7067024</v>
+        <v>7068352</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10612,24 +10407,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10640,51 +10425,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123935469</v>
+        <v>123948059</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10697,37 +10457,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497429</v>
+        <v>497338</v>
       </c>
       <c r="R73" t="n">
-        <v>7067378</v>
+        <v>7068065</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10754,19 +10514,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:27</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10777,51 +10532,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123935662</v>
+        <v>123948077</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10834,37 +10564,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497407</v>
+        <v>497583</v>
       </c>
       <c r="R74" t="n">
-        <v>7067289</v>
+        <v>7068342</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10891,19 +10621,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:35</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10914,44 +10639,5104 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123948058</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>497156</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7067976</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123948075</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>497629</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7068330</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123948076</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>497599</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7068342</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123948063</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>497448</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7067857</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123948057</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>497142</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7068071</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123948073</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>497810</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7068216</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123948051</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>496962</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7067810</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>123948041</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>497578</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7067475</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>123948070</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>497876</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7068110</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>123948049</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>496958</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7067783</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>123948068</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>497549</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7067939</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>123948081</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>497267</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7068098</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>123948074</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>497809</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7068221</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>123948064</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>497471</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7067944</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>123948053</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>497052</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7067797</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>123948071</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>497830</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7068267</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>123948060</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>497140</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7067713</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>123948052</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>496977</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7067794</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>123948065</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>497547</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7068008</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>123948079</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>497614</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7067898</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>123948067</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>497567</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7067939</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>123948069</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>497544</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7067872</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>123948084</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>497101</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7067728</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>123948083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>497012</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7067783</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>123948082</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>497300</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7068117</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>123948085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>497243</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7067786</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>123948054</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>497062</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7068118</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>123948056</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>497093</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7068094</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>123948055</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>497062</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7068109</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>123935937</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>497510</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7067357</v>
+      </c>
+      <c r="S104" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AX104" t="inlineStr">
         <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>123936388</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>497347</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7067031</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>123935511</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>497429</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7067368</v>
+      </c>
+      <c r="S106" t="n">
+        <v>9</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>123935971</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>497477</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7067373</v>
+      </c>
+      <c r="S107" t="n">
+        <v>9</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>123935623</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>497400</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7067320</v>
+      </c>
+      <c r="S108" t="n">
+        <v>8</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>123935892</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>497488</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7067338</v>
+      </c>
+      <c r="S109" t="n">
+        <v>8</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>123936336</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>497296</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7067024</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>123935469</v>
+      </c>
+      <c r="B111" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>497429</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7067378</v>
+      </c>
+      <c r="S111" t="n">
+        <v>7</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>123935662</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>497407</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7067289</v>
+      </c>
+      <c r="S112" t="n">
+        <v>7</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>123948039</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>497241</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7067063</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>123948038</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>497227</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7067047</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>123948042</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>497448</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7067435</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>123948080</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>497370</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7067042</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Hack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>123948045</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>497439</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7067336</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>123948040</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>497269</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7067065</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>123948047</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Piprörflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>497422</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7067360</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Gåxsjö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123928438</v>
+        <v>123933127</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,37 +1127,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497801</v>
+        <v>497133</v>
       </c>
       <c r="R5" t="n">
-        <v>7068154</v>
+        <v>7067678</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1196,7 +1201,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,22 +1220,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1248,7 +1253,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123925768</v>
+        <v>123928438</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1288,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497652</v>
+        <v>497801</v>
       </c>
       <c r="R6" t="n">
-        <v>7067869</v>
+        <v>7068154</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,10 +1390,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933127</v>
+        <v>123925768</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,42 +1406,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497133</v>
+        <v>497652</v>
       </c>
       <c r="R7" t="n">
-        <v>7067678</v>
+        <v>7067869</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123932682</v>
+        <v>123928574</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>79897</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1671,46 +1671,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497368</v>
+        <v>497848</v>
       </c>
       <c r="R9" t="n">
-        <v>7067763</v>
+        <v>7068101</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1734,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,7 +1744,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1764,26 +1759,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1801,10 +1776,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123933142</v>
+        <v>123929067</v>
       </c>
       <c r="B10" t="n">
-        <v>79905</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1813,46 +1788,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497133</v>
+        <v>497903</v>
       </c>
       <c r="R10" t="n">
-        <v>7067678</v>
+        <v>7068110</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1881,7 +1861,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1891,7 +1871,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1910,22 +1895,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1943,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123933962</v>
+        <v>123927991</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1959,37 +1944,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496999</v>
+        <v>497659</v>
       </c>
       <c r="R11" t="n">
-        <v>7067688</v>
+        <v>7068053</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,7 +2023,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123928574</v>
+        <v>123932682</v>
       </c>
       <c r="B12" t="n">
-        <v>79897</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2092,41 +2092,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497848</v>
+        <v>497368</v>
       </c>
       <c r="R12" t="n">
-        <v>7068101</v>
+        <v>7067763</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2155,7 +2160,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2165,7 +2170,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2180,6 +2185,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2197,10 +2222,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123929067</v>
+        <v>123932385</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,44 +2238,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497903</v>
+        <v>497528</v>
       </c>
       <c r="R13" t="n">
-        <v>7068110</v>
+        <v>7067930</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2282,7 +2297,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2292,12 +2307,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2326,12 +2336,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2349,10 +2359,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123927991</v>
+        <v>123933142</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2361,51 +2371,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497659</v>
+        <v>497133</v>
       </c>
       <c r="R14" t="n">
-        <v>7068053</v>
+        <v>7067678</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2434,7 +2439,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2444,12 +2449,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2463,27 +2463,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123932385</v>
+        <v>123933962</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2537,17 +2537,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497528</v>
+        <v>496999</v>
       </c>
       <c r="R15" t="n">
-        <v>7067930</v>
+        <v>7067688</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123928803</v>
+        <v>123934908</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3764,37 +3764,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497932</v>
+        <v>497399</v>
       </c>
       <c r="R24" t="n">
-        <v>7068202</v>
+        <v>7067620</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3823,7 +3828,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3833,12 +3838,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123927793</v>
+        <v>123934442</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3906,51 +3906,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497653</v>
+        <v>496964</v>
       </c>
       <c r="R25" t="n">
-        <v>7068061</v>
+        <v>7067764</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3979,7 +3965,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3989,12 +3975,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4008,7 +3989,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4023,12 +4004,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4188,10 +4169,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123934908</v>
+        <v>123928803</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4204,42 +4185,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497399</v>
+        <v>497932</v>
       </c>
       <c r="R27" t="n">
-        <v>7067620</v>
+        <v>7068202</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4268,7 +4244,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4278,7 +4254,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4307,12 +4288,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4330,10 +4311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123934442</v>
+        <v>123927793</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4346,37 +4327,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496964</v>
+        <v>497653</v>
       </c>
       <c r="R28" t="n">
-        <v>7067764</v>
+        <v>7068061</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4405,7 +4400,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4415,7 +4410,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123926766</v>
+        <v>123929190</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497661</v>
+        <v>497832</v>
       </c>
       <c r="R2" t="n">
-        <v>7067931</v>
+        <v>7067981</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -822,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123927550</v>
+        <v>123932608</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -862,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497670</v>
+        <v>497492</v>
       </c>
       <c r="R3" t="n">
-        <v>7068014</v>
+        <v>7067833</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -959,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123931338</v>
+        <v>123933962</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,47 +970,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497552</v>
+        <v>496999</v>
       </c>
       <c r="R4" t="n">
-        <v>7067881</v>
+        <v>7067688</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,12 +1068,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933127</v>
+        <v>123927793</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,42 +1107,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497133</v>
+        <v>497653</v>
       </c>
       <c r="R5" t="n">
-        <v>7067678</v>
+        <v>7068061</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,7 +1190,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,27 +1209,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,10 +1247,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123928438</v>
+        <v>123935093</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,34 +1263,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497801</v>
+        <v>497438</v>
       </c>
       <c r="R6" t="n">
-        <v>7068154</v>
+        <v>7067653</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1328,7 +1327,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,7 +1337,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,7 +1351,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1367,12 +1366,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1390,10 +1389,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123925768</v>
+        <v>123932697</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,37 +1405,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497652</v>
+        <v>497385</v>
       </c>
       <c r="R7" t="n">
-        <v>7067869</v>
+        <v>7067784</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1469,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1498,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1531,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123932969</v>
+        <v>123928858</v>
       </c>
       <c r="B8" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,47 +1547,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497236</v>
+        <v>497900</v>
       </c>
       <c r="R8" t="n">
-        <v>7067739</v>
+        <v>7068251</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1622,12 +1616,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1642,6 +1636,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1659,10 +1673,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123928574</v>
+        <v>123933142</v>
       </c>
       <c r="B9" t="n">
-        <v>79897</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1675,34 +1689,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497848</v>
+        <v>497133</v>
       </c>
       <c r="R9" t="n">
-        <v>7068101</v>
+        <v>7067678</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1734,7 +1753,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,7 +1763,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1759,6 +1778,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1776,10 +1815,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123929067</v>
+        <v>123928831</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79897</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1788,51 +1827,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497903</v>
+        <v>497927</v>
       </c>
       <c r="R10" t="n">
-        <v>7068110</v>
+        <v>7068210</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1861,7 +1890,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1871,12 +1900,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1891,26 +1915,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1928,10 +1932,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123927991</v>
+        <v>123934022</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1944,47 +1948,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497659</v>
+        <v>496970</v>
       </c>
       <c r="R11" t="n">
-        <v>7068053</v>
+        <v>7067716</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2013,7 +2007,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2023,12 +2017,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2042,7 +2036,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2057,12 +2051,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2080,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123932682</v>
+        <v>123929459</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2096,42 +2090,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497368</v>
+        <v>497843</v>
       </c>
       <c r="R12" t="n">
-        <v>7067763</v>
+        <v>7067903</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2160,7 +2159,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2170,7 +2169,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2189,22 +2193,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2222,10 +2226,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123932385</v>
+        <v>123933422</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2238,34 +2242,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497528</v>
+        <v>497077</v>
       </c>
       <c r="R13" t="n">
-        <v>7067930</v>
+        <v>7067679</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2297,7 +2306,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2307,7 +2316,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2336,12 +2345,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2359,10 +2368,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123933142</v>
+        <v>123933492</v>
       </c>
       <c r="B14" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2371,43 +2380,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497133</v>
+        <v>497103</v>
       </c>
       <c r="R14" t="n">
-        <v>7067678</v>
+        <v>7067696</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2439,7 +2443,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2449,7 +2453,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2468,22 +2472,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2501,7 +2505,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123933962</v>
+        <v>123925856</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2537,17 +2541,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496999</v>
+        <v>497652</v>
       </c>
       <c r="R15" t="n">
-        <v>7067688</v>
+        <v>7067886</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2586,7 +2590,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2638,7 +2642,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123925856</v>
+        <v>123925768</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2681,10 +2685,10 @@
         <v>497652</v>
       </c>
       <c r="R16" t="n">
-        <v>7067886</v>
+        <v>7067869</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2713,7 +2717,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2723,7 +2727,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2775,10 +2779,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123931528</v>
+        <v>123927679</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2787,20 +2791,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2808,10 +2812,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2825,13 +2838,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497563</v>
+        <v>497679</v>
       </c>
       <c r="R17" t="n">
-        <v>7067965</v>
+        <v>7068046</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2860,7 +2873,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2870,12 +2883,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2890,26 +2903,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2927,10 +2920,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123934085</v>
+        <v>123926190</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2939,60 +2932,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496980</v>
+        <v>497654</v>
       </c>
       <c r="R18" t="n">
-        <v>7067690</v>
+        <v>7067926</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3021,7 +2995,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3031,12 +3005,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3051,6 +3020,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3068,10 +3057,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123929301</v>
+        <v>123931616</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3084,42 +3073,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497846</v>
+        <v>497562</v>
       </c>
       <c r="R19" t="n">
-        <v>7067985</v>
+        <v>7067959</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3148,7 +3132,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3158,12 +3142,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3215,10 +3194,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123928831</v>
+        <v>123935202</v>
       </c>
       <c r="B20" t="n">
-        <v>79897</v>
+        <v>90986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3227,41 +3206,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497927</v>
+        <v>497524</v>
       </c>
       <c r="R20" t="n">
-        <v>7068210</v>
+        <v>7067827</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3290,7 +3274,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3300,7 +3284,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,6 +3299,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3332,7 +3336,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123933086</v>
+        <v>123934255</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -3372,13 +3376,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497126</v>
+        <v>496932</v>
       </c>
       <c r="R21" t="n">
-        <v>7067709</v>
+        <v>7067736</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3407,7 +3411,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3417,7 +3421,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3431,7 +3435,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3469,10 +3473,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123932697</v>
+        <v>123928438</v>
       </c>
       <c r="B22" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3485,42 +3489,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497385</v>
+        <v>497801</v>
       </c>
       <c r="R22" t="n">
-        <v>7067784</v>
+        <v>7068154</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3549,7 +3548,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3559,7 +3558,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3578,22 +3577,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3748,10 +3747,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123934908</v>
+        <v>123932710</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>79870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3764,42 +3763,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497399</v>
+        <v>497376</v>
       </c>
       <c r="R24" t="n">
-        <v>7067620</v>
+        <v>7067768</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3828,7 +3822,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3838,7 +3832,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3867,12 +3861,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3890,10 +3884,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123934442</v>
+        <v>123934085</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3902,41 +3896,60 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496964</v>
+        <v>496980</v>
       </c>
       <c r="R25" t="n">
-        <v>7067764</v>
+        <v>7067690</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3965,7 +3978,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3975,7 +3988,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3990,26 +4008,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4027,10 +4025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123933650</v>
+        <v>123933712</v>
       </c>
       <c r="B26" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4039,31 +4037,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4072,13 +4075,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497112</v>
+        <v>497111</v>
       </c>
       <c r="R26" t="n">
-        <v>7067726</v>
+        <v>7067721</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4107,7 +4110,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4117,7 +4120,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4132,26 +4140,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4169,7 +4157,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123928803</v>
+        <v>123934349</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -4205,17 +4193,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497932</v>
+        <v>496957</v>
       </c>
       <c r="R27" t="n">
-        <v>7068202</v>
+        <v>7067780</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4244,7 +4232,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4254,12 +4242,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4311,10 +4294,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123927793</v>
+        <v>123928379</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4327,51 +4310,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497653</v>
+        <v>497732</v>
       </c>
       <c r="R28" t="n">
-        <v>7068061</v>
+        <v>7068101</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4400,7 +4369,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4410,12 +4379,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4429,7 +4393,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4444,12 +4408,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4467,10 +4431,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123935093</v>
+        <v>123934742</v>
       </c>
       <c r="B29" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4483,27 +4447,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4512,13 +4481,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497438</v>
+        <v>497184</v>
       </c>
       <c r="R29" t="n">
-        <v>7067653</v>
+        <v>7067677</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4547,7 +4516,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4557,7 +4526,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4572,26 +4546,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4609,7 +4563,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123934349</v>
+        <v>123926766</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -4643,19 +4597,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496957</v>
+        <v>497661</v>
       </c>
       <c r="R30" t="n">
-        <v>7067780</v>
+        <v>7067931</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4684,7 +4643,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4694,7 +4653,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4746,10 +4710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123932552</v>
+        <v>123931528</v>
       </c>
       <c r="B31" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4762,16 +4726,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4782,7 +4746,12 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4791,10 +4760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497461</v>
+        <v>497563</v>
       </c>
       <c r="R31" t="n">
-        <v>7067890</v>
+        <v>7067965</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4826,7 +4795,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4836,12 +4805,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4893,10 +4862,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123931616</v>
+        <v>123929370</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4905,20 +4874,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4927,19 +4896,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497562</v>
+        <v>497852</v>
       </c>
       <c r="R32" t="n">
-        <v>7067959</v>
+        <v>7067984</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4968,7 +4942,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4978,7 +4952,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4997,22 +4971,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5030,10 +5004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123933422</v>
+        <v>123932385</v>
       </c>
       <c r="B33" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5046,39 +5020,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497077</v>
+        <v>497528</v>
       </c>
       <c r="R33" t="n">
-        <v>7067679</v>
+        <v>7067930</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -5110,7 +5079,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5120,7 +5089,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5149,12 +5118,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5172,10 +5141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123925995</v>
+        <v>123932969</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5188,37 +5157,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497628</v>
+        <v>497236</v>
       </c>
       <c r="R34" t="n">
-        <v>7067895</v>
+        <v>7067739</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5247,7 +5226,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5257,7 +5236,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5272,26 +5256,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5309,10 +5273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123928741</v>
+        <v>123934404</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5321,20 +5285,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5342,19 +5306,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5364,14 +5319,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497907</v>
+        <v>496972</v>
       </c>
       <c r="R35" t="n">
-        <v>7068146</v>
+        <v>7067780</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5403,7 +5358,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5413,12 +5368,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5433,6 +5388,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5450,10 +5425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123929370</v>
+        <v>123934442</v>
       </c>
       <c r="B36" t="n">
-        <v>79904</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5462,20 +5437,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5484,24 +5459,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497852</v>
+        <v>496964</v>
       </c>
       <c r="R36" t="n">
-        <v>7067984</v>
+        <v>7067764</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5530,7 +5500,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5540,7 +5510,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5559,22 +5529,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5592,10 +5562,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123935202</v>
+        <v>123933127</v>
       </c>
       <c r="B37" t="n">
-        <v>90986</v>
+        <v>79870</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5608,42 +5578,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497524</v>
+        <v>497133</v>
       </c>
       <c r="R37" t="n">
-        <v>7067827</v>
+        <v>7067678</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5672,7 +5642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5682,7 +5652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5701,22 +5671,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5734,10 +5704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123928514</v>
+        <v>123925602</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5750,37 +5720,47 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497851</v>
+        <v>497599</v>
       </c>
       <c r="R38" t="n">
-        <v>7068090</v>
+        <v>7067878</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5809,7 +5789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5819,7 +5799,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5848,12 +5833,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5871,10 +5856,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123932201</v>
+        <v>123933086</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5883,55 +5868,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497553</v>
+        <v>497126</v>
       </c>
       <c r="R39" t="n">
-        <v>7068083</v>
+        <v>7067709</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5960,7 +5931,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5970,12 +5941,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5986,6 +5952,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -6002,10 +5993,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123931433</v>
+        <v>123928574</v>
       </c>
       <c r="B40" t="n">
-        <v>57491</v>
+        <v>79897</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6014,48 +6005,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497554</v>
+        <v>497848</v>
       </c>
       <c r="R40" t="n">
-        <v>7067886</v>
+        <v>7068101</v>
       </c>
       <c r="S40" t="n">
         <v>8</v>
@@ -6087,7 +6068,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6097,12 +6078,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6117,26 +6093,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6154,10 +6110,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123931684</v>
+        <v>123933774</v>
       </c>
       <c r="B41" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6170,47 +6126,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497576</v>
+        <v>497066</v>
       </c>
       <c r="R41" t="n">
-        <v>7067995</v>
+        <v>7067728</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6239,7 +6185,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6249,12 +6195,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6268,7 +6209,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -6283,12 +6224,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6306,10 +6247,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123926190</v>
+        <v>123928327</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6318,41 +6259,51 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497654</v>
+        <v>497712</v>
       </c>
       <c r="R42" t="n">
-        <v>7067926</v>
+        <v>7068103</v>
       </c>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6381,7 +6332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6391,7 +6342,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6406,26 +6362,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6443,10 +6379,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123934022</v>
+        <v>123929282</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6459,37 +6395,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496970</v>
+        <v>497853</v>
       </c>
       <c r="R43" t="n">
-        <v>7067716</v>
+        <v>7067970</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6518,7 +6454,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6528,12 +6464,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6552,22 +6488,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6585,10 +6521,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123933859</v>
+        <v>123929301</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6601,37 +6537,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497016</v>
+        <v>497846</v>
       </c>
       <c r="R44" t="n">
-        <v>7067743</v>
+        <v>7067985</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6660,7 +6601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6670,12 +6611,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6727,10 +6668,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123934695</v>
+        <v>123929267</v>
       </c>
       <c r="B45" t="n">
-        <v>79773</v>
+        <v>79869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6739,43 +6680,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497164</v>
+        <v>497833</v>
       </c>
       <c r="R45" t="n">
-        <v>7067665</v>
+        <v>7067988</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6807,7 +6748,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6817,12 +6758,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6836,17 +6777,17 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6856,7 +6797,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6874,10 +6815,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123934742</v>
+        <v>123925387</v>
       </c>
       <c r="B46" t="n">
-        <v>56692</v>
+        <v>57861</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6886,20 +6827,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6907,10 +6848,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6920,17 +6870,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497184</v>
+        <v>497600</v>
       </c>
       <c r="R46" t="n">
-        <v>7067677</v>
+        <v>7067872</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6957,24 +6907,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6988,7 +6928,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7006,7 +6946,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123925602</v>
+        <v>123932552</v>
       </c>
       <c r="B47" t="n">
         <v>57491</v>
@@ -7042,12 +6982,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7056,13 +6991,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497599</v>
+        <v>497461</v>
       </c>
       <c r="R47" t="n">
-        <v>7067878</v>
+        <v>7067890</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7091,7 +7026,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7101,12 +7036,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7158,10 +7093,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123933492</v>
+        <v>123934908</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7174,34 +7109,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497103</v>
+        <v>497399</v>
       </c>
       <c r="R48" t="n">
-        <v>7067696</v>
+        <v>7067620</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7233,7 +7173,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7243,7 +7183,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7272,12 +7212,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7295,10 +7235,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123929282</v>
+        <v>123925995</v>
       </c>
       <c r="B49" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7311,21 +7251,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7335,13 +7275,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497853</v>
+        <v>497628</v>
       </c>
       <c r="R49" t="n">
-        <v>7067970</v>
+        <v>7067895</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7370,7 +7310,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7380,12 +7320,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7404,22 +7339,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7437,10 +7372,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123929497</v>
+        <v>123928514</v>
       </c>
       <c r="B50" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7453,44 +7388,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497846</v>
+        <v>497851</v>
       </c>
       <c r="R50" t="n">
-        <v>7067895</v>
+        <v>7068090</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -7522,7 +7447,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7532,12 +7457,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7566,12 +7486,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7589,10 +7509,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123928858</v>
+        <v>123931338</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7605,34 +7525,44 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497900</v>
+        <v>497552</v>
       </c>
       <c r="R51" t="n">
-        <v>7068251</v>
+        <v>7067881</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -7664,7 +7594,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7674,12 +7604,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7708,12 +7638,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7731,10 +7661,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123928379</v>
+        <v>123934695</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7743,41 +7673,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497732</v>
+        <v>497164</v>
       </c>
       <c r="R52" t="n">
-        <v>7068101</v>
+        <v>7067665</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7806,7 +7741,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7816,7 +7751,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7830,27 +7770,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7868,10 +7808,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123933712</v>
+        <v>123933859</v>
       </c>
       <c r="B53" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7880,51 +7820,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497111</v>
+        <v>497016</v>
       </c>
       <c r="R53" t="n">
-        <v>7067721</v>
+        <v>7067743</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7953,7 +7883,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7963,12 +7893,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7982,7 +7912,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8000,10 +7950,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123934404</v>
+        <v>123931684</v>
       </c>
       <c r="B54" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8016,16 +7966,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8036,7 +7986,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -8046,17 +7996,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496972</v>
+        <v>497576</v>
       </c>
       <c r="R54" t="n">
-        <v>7067780</v>
+        <v>7067995</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8085,7 +8035,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8095,12 +8045,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8129,12 +8079,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8152,10 +8102,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123929267</v>
+        <v>123929497</v>
       </c>
       <c r="B55" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8168,27 +8118,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8197,13 +8152,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497833</v>
+        <v>497846</v>
       </c>
       <c r="R55" t="n">
-        <v>7067988</v>
+        <v>7067895</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8232,7 +8187,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8242,12 +8197,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8266,22 +8221,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8451,7 +8406,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123933774</v>
+        <v>123927550</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -8487,14 +8442,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497066</v>
+        <v>497670</v>
       </c>
       <c r="R57" t="n">
-        <v>7067728</v>
+        <v>7068014</v>
       </c>
       <c r="S57" t="n">
         <v>11</v>
@@ -8526,7 +8481,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8536,7 +8491,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8550,7 +8505,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8588,10 +8543,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123929190</v>
+        <v>123928741</v>
       </c>
       <c r="B58" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8600,41 +8555,60 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497832</v>
+        <v>497907</v>
       </c>
       <c r="R58" t="n">
-        <v>7067981</v>
+        <v>7068146</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8663,7 +8637,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8673,12 +8647,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8693,26 +8667,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8730,10 +8684,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123925387</v>
+        <v>123931433</v>
       </c>
       <c r="B59" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8742,20 +8696,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8763,19 +8717,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8789,13 +8734,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497600</v>
+        <v>497554</v>
       </c>
       <c r="R59" t="n">
-        <v>7067872</v>
+        <v>7067886</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8822,14 +8767,24 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8844,6 +8799,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8861,10 +8836,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123929459</v>
+        <v>123932201</v>
       </c>
       <c r="B60" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8873,36 +8848,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8911,10 +8890,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497843</v>
+        <v>497553</v>
       </c>
       <c r="R60" t="n">
-        <v>7067903</v>
+        <v>7068083</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -8946,7 +8925,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8956,12 +8935,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8972,31 +8951,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -9013,10 +8967,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123932710</v>
+        <v>123933650</v>
       </c>
       <c r="B61" t="n">
-        <v>79870</v>
+        <v>91008</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9029,37 +8983,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497376</v>
+        <v>497112</v>
       </c>
       <c r="R61" t="n">
-        <v>7067768</v>
+        <v>7067726</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -9088,7 +9047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9098,7 +9057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9112,7 +9071,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -9127,12 +9086,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9150,10 +9109,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123928327</v>
+        <v>123927991</v>
       </c>
       <c r="B62" t="n">
-        <v>56703</v>
+        <v>57491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9162,20 +9121,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9186,7 +9145,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -9200,13 +9159,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497712</v>
+        <v>497659</v>
       </c>
       <c r="R62" t="n">
-        <v>7068103</v>
+        <v>7068053</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -9235,7 +9194,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9245,12 +9204,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9264,7 +9223,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9282,7 +9261,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123932608</v>
+        <v>123928803</v>
       </c>
       <c r="B63" t="n">
         <v>78788</v>
@@ -9322,10 +9301,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497492</v>
+        <v>497932</v>
       </c>
       <c r="R63" t="n">
-        <v>7067833</v>
+        <v>7068202</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -9357,7 +9336,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9367,7 +9346,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9419,10 +9403,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123934255</v>
+        <v>123932682</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9435,37 +9419,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496932</v>
+        <v>497368</v>
       </c>
       <c r="R64" t="n">
-        <v>7067736</v>
+        <v>7067763</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9494,7 +9483,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9504,7 +9493,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9518,27 +9507,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9556,10 +9545,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123927679</v>
+        <v>123929067</v>
       </c>
       <c r="B65" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9568,20 +9557,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9589,19 +9578,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9615,13 +9595,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497679</v>
+        <v>497903</v>
       </c>
       <c r="R65" t="n">
-        <v>7068046</v>
+        <v>7068110</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9650,7 +9630,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9660,12 +9640,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9680,6 +9660,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9799,10 +9799,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948066</v>
+        <v>123948084</v>
       </c>
       <c r="B67" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9815,21 +9815,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497568</v>
+        <v>497101</v>
       </c>
       <c r="R67" t="n">
-        <v>7067974</v>
+        <v>7067728</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9875,11 +9875,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9906,7 +9901,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948048</v>
+        <v>123948071</v>
       </c>
       <c r="B68" t="n">
         <v>57491</v>
@@ -9946,10 +9941,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497417</v>
+        <v>497830</v>
       </c>
       <c r="R68" t="n">
-        <v>7067613</v>
+        <v>7068267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -10013,7 +10008,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948050</v>
+        <v>123948055</v>
       </c>
       <c r="B69" t="n">
         <v>57491</v>
@@ -10053,10 +10048,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496963</v>
+        <v>497062</v>
       </c>
       <c r="R69" t="n">
-        <v>7067823</v>
+        <v>7068109</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -10093,7 +10088,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10120,7 +10115,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948061</v>
+        <v>123948075</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -10160,10 +10155,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497152</v>
+        <v>497629</v>
       </c>
       <c r="R70" t="n">
-        <v>7067720</v>
+        <v>7068330</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10200,7 +10195,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10227,7 +10222,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948062</v>
+        <v>123948070</v>
       </c>
       <c r="B71" t="n">
         <v>57491</v>
@@ -10267,10 +10262,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497431</v>
+        <v>497876</v>
       </c>
       <c r="R71" t="n">
-        <v>7067834</v>
+        <v>7068110</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10334,10 +10329,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948078</v>
+        <v>123948085</v>
       </c>
       <c r="B72" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10350,21 +10345,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10374,10 +10369,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497569</v>
+        <v>497243</v>
       </c>
       <c r="R72" t="n">
-        <v>7068352</v>
+        <v>7067786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10410,11 +10405,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10441,7 +10431,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948059</v>
+        <v>123948048</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -10481,10 +10471,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497338</v>
+        <v>497417</v>
       </c>
       <c r="R73" t="n">
-        <v>7068065</v>
+        <v>7067613</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10521,7 +10511,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10548,7 +10538,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948077</v>
+        <v>123948057</v>
       </c>
       <c r="B74" t="n">
         <v>57491</v>
@@ -10588,10 +10578,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497583</v>
+        <v>497142</v>
       </c>
       <c r="R74" t="n">
-        <v>7068342</v>
+        <v>7068071</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10628,7 +10618,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10655,10 +10645,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948058</v>
+        <v>123948081</v>
       </c>
       <c r="B75" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10667,25 +10657,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10695,10 +10685,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497156</v>
+        <v>497267</v>
       </c>
       <c r="R75" t="n">
-        <v>7067976</v>
+        <v>7068098</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10731,11 +10721,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10762,7 +10747,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948075</v>
+        <v>123948078</v>
       </c>
       <c r="B76" t="n">
         <v>57491</v>
@@ -10802,10 +10787,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497629</v>
+        <v>497569</v>
       </c>
       <c r="R76" t="n">
-        <v>7068330</v>
+        <v>7068352</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10842,7 +10827,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10869,7 +10854,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948076</v>
+        <v>123948079</v>
       </c>
       <c r="B77" t="n">
         <v>57491</v>
@@ -10909,10 +10894,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497599</v>
+        <v>497614</v>
       </c>
       <c r="R77" t="n">
-        <v>7068342</v>
+        <v>7067898</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10976,7 +10961,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948063</v>
+        <v>123948061</v>
       </c>
       <c r="B78" t="n">
         <v>57491</v>
@@ -11016,10 +11001,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497448</v>
+        <v>497152</v>
       </c>
       <c r="R78" t="n">
-        <v>7067857</v>
+        <v>7067720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -11083,7 +11068,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948057</v>
+        <v>123948049</v>
       </c>
       <c r="B79" t="n">
         <v>57491</v>
@@ -11123,10 +11108,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497142</v>
+        <v>496958</v>
       </c>
       <c r="R79" t="n">
-        <v>7068071</v>
+        <v>7067783</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11163,7 +11148,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11190,7 +11175,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948073</v>
+        <v>123948067</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11230,10 +11215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497810</v>
+        <v>497567</v>
       </c>
       <c r="R80" t="n">
-        <v>7068216</v>
+        <v>7067939</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11270,7 +11255,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11297,7 +11282,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948051</v>
+        <v>123948058</v>
       </c>
       <c r="B81" t="n">
         <v>57491</v>
@@ -11337,10 +11322,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496962</v>
+        <v>497156</v>
       </c>
       <c r="R81" t="n">
-        <v>7067810</v>
+        <v>7067976</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11377,7 +11362,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11404,7 +11389,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948041</v>
+        <v>123948068</v>
       </c>
       <c r="B82" t="n">
         <v>57491</v>
@@ -11444,10 +11429,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497578</v>
+        <v>497549</v>
       </c>
       <c r="R82" t="n">
-        <v>7067475</v>
+        <v>7067939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11511,7 +11496,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948070</v>
+        <v>123948073</v>
       </c>
       <c r="B83" t="n">
         <v>57491</v>
@@ -11551,10 +11536,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497876</v>
+        <v>497810</v>
       </c>
       <c r="R83" t="n">
-        <v>7068110</v>
+        <v>7068216</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11618,7 +11603,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948049</v>
+        <v>123948066</v>
       </c>
       <c r="B84" t="n">
         <v>57491</v>
@@ -11658,10 +11643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496958</v>
+        <v>497568</v>
       </c>
       <c r="R84" t="n">
-        <v>7067783</v>
+        <v>7067974</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11725,7 +11710,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948068</v>
+        <v>123948059</v>
       </c>
       <c r="B85" t="n">
         <v>57491</v>
@@ -11765,10 +11750,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497549</v>
+        <v>497338</v>
       </c>
       <c r="R85" t="n">
-        <v>7067939</v>
+        <v>7068065</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11805,7 +11790,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11832,10 +11817,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948081</v>
+        <v>123948069</v>
       </c>
       <c r="B86" t="n">
-        <v>98504</v>
+        <v>57491</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11844,25 +11829,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11872,10 +11857,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497267</v>
+        <v>497544</v>
       </c>
       <c r="R86" t="n">
-        <v>7068098</v>
+        <v>7067872</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11908,6 +11893,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11934,7 +11924,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948074</v>
+        <v>123948052</v>
       </c>
       <c r="B87" t="n">
         <v>57491</v>
@@ -11974,10 +11964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497809</v>
+        <v>496977</v>
       </c>
       <c r="R87" t="n">
-        <v>7068221</v>
+        <v>7067794</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12041,7 +12031,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948064</v>
+        <v>123948062</v>
       </c>
       <c r="B88" t="n">
         <v>57491</v>
@@ -12081,10 +12071,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497471</v>
+        <v>497431</v>
       </c>
       <c r="R88" t="n">
-        <v>7067944</v>
+        <v>7067834</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12148,10 +12138,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948053</v>
+        <v>123948083</v>
       </c>
       <c r="B89" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12164,21 +12154,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12188,10 +12178,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497052</v>
+        <v>497012</v>
       </c>
       <c r="R89" t="n">
-        <v>7067797</v>
+        <v>7067783</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12224,11 +12214,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12255,7 +12240,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948071</v>
+        <v>123948074</v>
       </c>
       <c r="B90" t="n">
         <v>57491</v>
@@ -12295,10 +12280,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497830</v>
+        <v>497809</v>
       </c>
       <c r="R90" t="n">
-        <v>7068267</v>
+        <v>7068221</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12362,7 +12347,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948060</v>
+        <v>123948050</v>
       </c>
       <c r="B91" t="n">
         <v>57491</v>
@@ -12402,10 +12387,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497140</v>
+        <v>496963</v>
       </c>
       <c r="R91" t="n">
-        <v>7067713</v>
+        <v>7067823</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12442,7 +12427,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12469,7 +12454,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948052</v>
+        <v>123948056</v>
       </c>
       <c r="B92" t="n">
         <v>57491</v>
@@ -12509,10 +12494,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496977</v>
+        <v>497093</v>
       </c>
       <c r="R92" t="n">
-        <v>7067794</v>
+        <v>7068094</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12576,7 +12561,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948065</v>
+        <v>123948053</v>
       </c>
       <c r="B93" t="n">
         <v>57491</v>
@@ -12616,10 +12601,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497547</v>
+        <v>497052</v>
       </c>
       <c r="R93" t="n">
-        <v>7068008</v>
+        <v>7067797</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12656,7 +12641,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12683,7 +12668,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948079</v>
+        <v>123948064</v>
       </c>
       <c r="B94" t="n">
         <v>57491</v>
@@ -12723,10 +12708,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497614</v>
+        <v>497471</v>
       </c>
       <c r="R94" t="n">
-        <v>7067898</v>
+        <v>7067944</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12790,7 +12775,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123948067</v>
+        <v>123948065</v>
       </c>
       <c r="B95" t="n">
         <v>57491</v>
@@ -12830,10 +12815,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497567</v>
+        <v>497547</v>
       </c>
       <c r="R95" t="n">
-        <v>7067939</v>
+        <v>7068008</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12870,7 +12855,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12897,7 +12882,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123948069</v>
+        <v>123948051</v>
       </c>
       <c r="B96" t="n">
         <v>57491</v>
@@ -12937,10 +12922,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497544</v>
+        <v>496962</v>
       </c>
       <c r="R96" t="n">
-        <v>7067872</v>
+        <v>7067810</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13004,10 +12989,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123948084</v>
+        <v>123948041</v>
       </c>
       <c r="B97" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13020,21 +13005,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -13044,10 +13029,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497101</v>
+        <v>497578</v>
       </c>
       <c r="R97" t="n">
-        <v>7067728</v>
+        <v>7067475</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13080,6 +13065,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13106,10 +13096,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123948083</v>
+        <v>123948082</v>
       </c>
       <c r="B98" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13118,25 +13108,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13146,10 +13136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497012</v>
+        <v>497300</v>
       </c>
       <c r="R98" t="n">
-        <v>7067783</v>
+        <v>7068117</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13208,10 +13198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123948082</v>
+        <v>123948060</v>
       </c>
       <c r="B99" t="n">
-        <v>98504</v>
+        <v>57491</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13220,25 +13210,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -13248,10 +13238,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497300</v>
+        <v>497140</v>
       </c>
       <c r="R99" t="n">
-        <v>7068117</v>
+        <v>7067713</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13284,6 +13274,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13310,10 +13305,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123948085</v>
+        <v>123948077</v>
       </c>
       <c r="B100" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13326,21 +13321,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13350,10 +13345,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497243</v>
+        <v>497583</v>
       </c>
       <c r="R100" t="n">
-        <v>7067786</v>
+        <v>7068342</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13386,6 +13381,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13412,7 +13412,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948054</v>
+        <v>123948076</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497062</v>
+        <v>497599</v>
       </c>
       <c r="R101" t="n">
-        <v>7068118</v>
+        <v>7068342</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13519,7 +13519,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123948056</v>
+        <v>123948063</v>
       </c>
       <c r="B102" t="n">
         <v>57491</v>
@@ -13559,10 +13559,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497093</v>
+        <v>497448</v>
       </c>
       <c r="R102" t="n">
-        <v>7068094</v>
+        <v>7067857</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123948055</v>
+        <v>123948054</v>
       </c>
       <c r="B103" t="n">
         <v>57491</v>
@@ -13669,7 +13669,7 @@
         <v>497062</v>
       </c>
       <c r="R103" t="n">
-        <v>7068109</v>
+        <v>7068118</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123936388</v>
+        <v>123935511</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,37 +13886,47 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497347</v>
+        <v>497429</v>
       </c>
       <c r="R105" t="n">
-        <v>7067031</v>
+        <v>7067368</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13945,7 +13955,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13955,7 +13965,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13984,12 +13994,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14007,10 +14017,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935511</v>
+        <v>123936388</v>
       </c>
       <c r="B106" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14023,47 +14033,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497429</v>
+        <v>497347</v>
       </c>
       <c r="R106" t="n">
-        <v>7067368</v>
+        <v>7067031</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935971</v>
+        <v>123935469</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -14194,13 +14194,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497477</v>
+        <v>497429</v>
       </c>
       <c r="R107" t="n">
-        <v>7067373</v>
+        <v>7067378</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14291,7 +14291,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123935623</v>
+        <v>123935892</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497400</v>
+        <v>497488</v>
       </c>
       <c r="R108" t="n">
-        <v>7067320</v>
+        <v>7067338</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14428,7 +14428,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123935892</v>
+        <v>123935971</v>
       </c>
       <c r="B109" t="n">
         <v>78788</v>
@@ -14468,13 +14468,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497488</v>
+        <v>497477</v>
       </c>
       <c r="R109" t="n">
-        <v>7067338</v>
+        <v>7067373</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14717,7 +14717,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935469</v>
+        <v>123935623</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -14757,13 +14757,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497429</v>
+        <v>497400</v>
       </c>
       <c r="R111" t="n">
-        <v>7067378</v>
+        <v>7067320</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14991,7 +14991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948039</v>
+        <v>123948045</v>
       </c>
       <c r="B113" t="n">
         <v>57491</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497241</v>
+        <v>497439</v>
       </c>
       <c r="R113" t="n">
-        <v>7067063</v>
+        <v>7067336</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948038</v>
+        <v>123948047</v>
       </c>
       <c r="B114" t="n">
         <v>57491</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497227</v>
+        <v>497422</v>
       </c>
       <c r="R114" t="n">
-        <v>7067047</v>
+        <v>7067360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,7 +15205,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948042</v>
+        <v>123948040</v>
       </c>
       <c r="B115" t="n">
         <v>57491</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497448</v>
+        <v>497269</v>
       </c>
       <c r="R115" t="n">
-        <v>7067435</v>
+        <v>7067065</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948045</v>
+        <v>123948042</v>
       </c>
       <c r="B117" t="n">
         <v>57491</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497439</v>
+        <v>497448</v>
       </c>
       <c r="R117" t="n">
-        <v>7067336</v>
+        <v>7067435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948040</v>
+        <v>123948038</v>
       </c>
       <c r="B118" t="n">
         <v>57491</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497269</v>
+        <v>497227</v>
       </c>
       <c r="R118" t="n">
-        <v>7067065</v>
+        <v>7067047</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15633,7 +15633,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948047</v>
+        <v>123948039</v>
       </c>
       <c r="B119" t="n">
         <v>57491</v>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497422</v>
+        <v>497241</v>
       </c>
       <c r="R119" t="n">
-        <v>7067360</v>
+        <v>7067063</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -5704,10 +5704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123925602</v>
+        <v>123933086</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5720,47 +5720,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497599</v>
+        <v>497126</v>
       </c>
       <c r="R38" t="n">
-        <v>7067878</v>
+        <v>7067709</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5789,7 +5779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5799,12 +5789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5833,12 +5818,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5856,10 +5841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123933086</v>
+        <v>123928574</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5868,41 +5853,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497126</v>
+        <v>497848</v>
       </c>
       <c r="R39" t="n">
-        <v>7067709</v>
+        <v>7068101</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5931,7 +5916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5941,7 +5926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5956,26 +5941,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5993,10 +5958,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123928574</v>
+        <v>123933774</v>
       </c>
       <c r="B40" t="n">
-        <v>79897</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6005,41 +5970,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497848</v>
+        <v>497066</v>
       </c>
       <c r="R40" t="n">
-        <v>7068101</v>
+        <v>7067728</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6068,7 +6033,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6078,7 +6043,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6092,7 +6057,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6110,10 +6095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123933774</v>
+        <v>123928327</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6122,41 +6107,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497066</v>
+        <v>497712</v>
       </c>
       <c r="R41" t="n">
-        <v>7067728</v>
+        <v>7068103</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6185,7 +6180,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6195,7 +6190,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6209,27 +6209,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6247,10 +6227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123928327</v>
+        <v>123925602</v>
       </c>
       <c r="B42" t="n">
-        <v>56703</v>
+        <v>57491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6259,20 +6239,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6283,7 +6263,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6297,10 +6277,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497712</v>
+        <v>497599</v>
       </c>
       <c r="R42" t="n">
-        <v>7068103</v>
+        <v>7067878</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -6332,7 +6312,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6342,12 +6322,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6362,6 +6342,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -9403,10 +9403,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123932682</v>
+        <v>123929067</v>
       </c>
       <c r="B64" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9419,42 +9419,47 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497368</v>
+        <v>497903</v>
       </c>
       <c r="R64" t="n">
-        <v>7067763</v>
+        <v>7068110</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9483,7 +9488,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9493,7 +9498,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9512,22 +9522,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9545,10 +9555,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123929067</v>
+        <v>123932682</v>
       </c>
       <c r="B65" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9561,47 +9571,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497903</v>
+        <v>497368</v>
       </c>
       <c r="R65" t="n">
-        <v>7068110</v>
+        <v>7067763</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9630,7 +9635,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9640,12 +9645,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9664,22 +9664,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -11068,7 +11068,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948049</v>
+        <v>123948067</v>
       </c>
       <c r="B79" t="n">
         <v>57491</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496958</v>
+        <v>497567</v>
       </c>
       <c r="R79" t="n">
-        <v>7067783</v>
+        <v>7067939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948067</v>
+        <v>123948049</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497567</v>
+        <v>496958</v>
       </c>
       <c r="R80" t="n">
-        <v>7067939</v>
+        <v>7067783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13305,7 +13305,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123948077</v>
+        <v>123948076</v>
       </c>
       <c r="B100" t="n">
         <v>57491</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497583</v>
+        <v>497599</v>
       </c>
       <c r="R100" t="n">
         <v>7068342</v>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13412,7 +13412,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948076</v>
+        <v>123948077</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497599</v>
+        <v>497583</v>
       </c>
       <c r="R101" t="n">
         <v>7068342</v>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123929190</v>
+        <v>123926190</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497832</v>
+        <v>497654</v>
       </c>
       <c r="R2" t="n">
-        <v>7067981</v>
+        <v>7067926</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -817,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123932608</v>
+        <v>123931616</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -857,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497492</v>
+        <v>497562</v>
       </c>
       <c r="R3" t="n">
-        <v>7067833</v>
+        <v>7067959</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,7 +949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123933962</v>
+        <v>123933859</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -994,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496999</v>
+        <v>497016</v>
       </c>
       <c r="R4" t="n">
-        <v>7067688</v>
+        <v>7067743</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1091,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123927793</v>
+        <v>123933086</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,51 +1107,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497653</v>
+        <v>497126</v>
       </c>
       <c r="R5" t="n">
-        <v>7068061</v>
+        <v>7067709</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,12 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,7 +1190,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1224,12 +1205,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1247,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123935093</v>
+        <v>123934908</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1263,21 +1244,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1292,13 +1273,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497438</v>
+        <v>497399</v>
       </c>
       <c r="R6" t="n">
-        <v>7067653</v>
+        <v>7067620</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1327,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1337,7 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,7 +1332,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1366,12 +1347,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1389,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123932697</v>
+        <v>123927991</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1405,42 +1386,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497385</v>
+        <v>497659</v>
       </c>
       <c r="R7" t="n">
-        <v>7067784</v>
+        <v>7068053</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1469,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1479,7 +1465,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,27 +1484,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,10 +1522,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123928858</v>
+        <v>123931433</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1547,37 +1538,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497900</v>
+        <v>497554</v>
       </c>
       <c r="R8" t="n">
-        <v>7068251</v>
+        <v>7067886</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1606,7 +1607,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1616,12 +1617,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1650,12 +1651,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1673,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123933142</v>
+        <v>123925856</v>
       </c>
       <c r="B9" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1685,46 +1686,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497133</v>
+        <v>497652</v>
       </c>
       <c r="R9" t="n">
-        <v>7067678</v>
+        <v>7067886</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1753,7 +1749,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1782,22 +1778,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1815,10 +1811,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123928831</v>
+        <v>123935202</v>
       </c>
       <c r="B10" t="n">
-        <v>79897</v>
+        <v>90986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1827,41 +1823,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497927</v>
+        <v>497524</v>
       </c>
       <c r="R10" t="n">
-        <v>7068210</v>
+        <v>7067827</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1890,7 +1891,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1900,7 +1901,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1915,6 +1916,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1932,10 +1953,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123934022</v>
+        <v>123925602</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1948,34 +1969,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496970</v>
+        <v>497599</v>
       </c>
       <c r="R11" t="n">
-        <v>7067716</v>
+        <v>7067878</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2007,7 +2038,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2017,12 +2048,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2051,12 +2082,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,10 +2105,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123929459</v>
+        <v>123934255</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2090,47 +2121,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497843</v>
+        <v>496932</v>
       </c>
       <c r="R12" t="n">
-        <v>7067903</v>
+        <v>7067736</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2159,7 +2180,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2169,12 +2190,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2188,7 +2204,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2203,12 +2219,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2226,10 +2242,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123933422</v>
+        <v>123925768</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2242,42 +2258,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497077</v>
+        <v>497652</v>
       </c>
       <c r="R13" t="n">
-        <v>7067679</v>
+        <v>7067869</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2306,7 +2317,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2316,7 +2327,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2345,12 +2356,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2368,10 +2379,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123933492</v>
+        <v>123933142</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2380,38 +2391,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497103</v>
+        <v>497133</v>
       </c>
       <c r="R14" t="n">
-        <v>7067696</v>
+        <v>7067678</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2443,7 +2459,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2453,7 +2469,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2472,22 +2488,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2505,10 +2521,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123925856</v>
+        <v>123928574</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2517,25 +2533,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2545,13 +2561,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497652</v>
+        <v>497848</v>
       </c>
       <c r="R15" t="n">
-        <v>7067886</v>
+        <v>7068101</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2580,7 +2596,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2590,7 +2606,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2605,26 +2621,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2642,10 +2638,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123925768</v>
+        <v>123928327</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2654,41 +2650,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497652</v>
+        <v>497712</v>
       </c>
       <c r="R16" t="n">
-        <v>7067869</v>
+        <v>7068103</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2717,7 +2723,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2727,7 +2733,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2742,26 +2753,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2779,10 +2770,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123927679</v>
+        <v>123934742</v>
       </c>
       <c r="B17" t="n">
-        <v>57861</v>
+        <v>56692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2791,20 +2782,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2812,19 +2803,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2834,17 +2816,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497679</v>
+        <v>497184</v>
       </c>
       <c r="R17" t="n">
-        <v>7068046</v>
+        <v>7067677</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2873,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2883,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2902,7 +2884,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2920,7 +2902,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123926190</v>
+        <v>123928803</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2960,13 +2942,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497654</v>
+        <v>497932</v>
       </c>
       <c r="R18" t="n">
-        <v>7067926</v>
+        <v>7068202</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2995,7 +2977,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3005,7 +2987,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3057,10 +3044,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123931616</v>
+        <v>123931528</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3073,37 +3060,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497562</v>
+        <v>497563</v>
       </c>
       <c r="R19" t="n">
-        <v>7067959</v>
+        <v>7067965</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3132,7 +3129,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3142,7 +3139,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3171,12 +3173,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3194,10 +3196,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123935202</v>
+        <v>123929282</v>
       </c>
       <c r="B20" t="n">
-        <v>90986</v>
+        <v>79870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3210,39 +3212,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497524</v>
+        <v>497853</v>
       </c>
       <c r="R20" t="n">
-        <v>7067827</v>
+        <v>7067970</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -3274,7 +3271,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3284,7 +3281,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3303,22 +3305,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3336,10 +3338,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123934255</v>
+        <v>123933650</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3352,37 +3354,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496932</v>
+        <v>497112</v>
       </c>
       <c r="R21" t="n">
-        <v>7067736</v>
+        <v>7067726</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3411,7 +3418,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3421,7 +3428,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3450,12 +3457,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3473,10 +3480,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123928438</v>
+        <v>123932682</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3489,34 +3496,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497801</v>
+        <v>497368</v>
       </c>
       <c r="R22" t="n">
-        <v>7068154</v>
+        <v>7067763</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3548,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3558,7 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3577,22 +3589,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3610,10 +3622,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123934569</v>
+        <v>123929700</v>
       </c>
       <c r="B23" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3626,34 +3638,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497124</v>
+        <v>497829</v>
       </c>
       <c r="R23" t="n">
-        <v>7067682</v>
+        <v>7067835</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3685,7 +3707,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,7 +3717,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3714,22 +3741,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3747,10 +3774,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932710</v>
+        <v>123931338</v>
       </c>
       <c r="B24" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3763,37 +3790,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497376</v>
+        <v>497552</v>
       </c>
       <c r="R24" t="n">
-        <v>7067768</v>
+        <v>7067881</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3822,7 +3859,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3832,7 +3869,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3861,12 +3903,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3884,10 +3926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123934085</v>
+        <v>123934022</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3896,60 +3938,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496980</v>
+        <v>496970</v>
       </c>
       <c r="R25" t="n">
-        <v>7067690</v>
+        <v>7067716</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3978,7 +4001,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3988,12 +4011,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4008,6 +4031,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4025,10 +4068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123933712</v>
+        <v>123934569</v>
       </c>
       <c r="B26" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4037,51 +4080,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497111</v>
+        <v>497124</v>
       </c>
       <c r="R26" t="n">
-        <v>7067721</v>
+        <v>7067682</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4110,7 +4143,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4120,12 +4153,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4140,6 +4168,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4157,10 +4205,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123934349</v>
+        <v>123929301</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4173,37 +4221,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496957</v>
+        <v>497846</v>
       </c>
       <c r="R27" t="n">
-        <v>7067780</v>
+        <v>7067985</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4232,7 +4285,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4242,7 +4295,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4294,7 +4352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123928379</v>
+        <v>123926766</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -4328,19 +4386,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497732</v>
+        <v>497661</v>
       </c>
       <c r="R28" t="n">
-        <v>7068101</v>
+        <v>7067931</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4369,7 +4432,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4379,7 +4442,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4431,10 +4499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123934742</v>
+        <v>123928514</v>
       </c>
       <c r="B29" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4447,47 +4515,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497184</v>
+        <v>497851</v>
       </c>
       <c r="R29" t="n">
-        <v>7067677</v>
+        <v>7068090</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4516,7 +4574,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4526,12 +4584,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4545,7 +4598,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4563,10 +4636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123926766</v>
+        <v>123931684</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4579,27 +4652,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4608,13 +4686,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497661</v>
+        <v>497576</v>
       </c>
       <c r="R30" t="n">
-        <v>7067931</v>
+        <v>7067995</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4643,7 +4721,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4653,12 +4731,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4687,12 +4765,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4710,7 +4788,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123931528</v>
+        <v>123929459</v>
       </c>
       <c r="B31" t="n">
         <v>57507</v>
@@ -4760,10 +4838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497563</v>
+        <v>497843</v>
       </c>
       <c r="R31" t="n">
-        <v>7067965</v>
+        <v>7067903</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4795,7 +4873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4805,7 +4883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4862,10 +4940,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123929370</v>
+        <v>123932969</v>
       </c>
       <c r="B32" t="n">
-        <v>79904</v>
+        <v>56692</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4874,46 +4952,51 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497852</v>
+        <v>497236</v>
       </c>
       <c r="R32" t="n">
-        <v>7067984</v>
+        <v>7067739</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4942,7 +5025,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4952,7 +5035,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4967,26 +5055,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5004,10 +5072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123932385</v>
+        <v>123932710</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5020,37 +5088,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497528</v>
+        <v>497376</v>
       </c>
       <c r="R33" t="n">
-        <v>7067930</v>
+        <v>7067768</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5079,7 +5147,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5089,7 +5157,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5141,10 +5209,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123932969</v>
+        <v>123935093</v>
       </c>
       <c r="B34" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5157,32 +5225,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5191,13 +5254,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497236</v>
+        <v>497438</v>
       </c>
       <c r="R34" t="n">
-        <v>7067739</v>
+        <v>7067653</v>
       </c>
       <c r="S34" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5226,7 +5289,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5236,12 +5299,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5255,7 +5313,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5273,10 +5351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123934404</v>
+        <v>123925387</v>
       </c>
       <c r="B35" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5285,20 +5363,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5306,10 +5384,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5319,14 +5406,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496972</v>
+        <v>497600</v>
       </c>
       <c r="R35" t="n">
-        <v>7067780</v>
+        <v>7067872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5356,24 +5443,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5388,26 +5465,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5425,10 +5482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123934442</v>
+        <v>123927679</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5437,41 +5494,60 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496964</v>
+        <v>497679</v>
       </c>
       <c r="R36" t="n">
-        <v>7067764</v>
+        <v>7068046</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5500,7 +5576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5510,7 +5586,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5525,26 +5606,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5562,10 +5623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123933127</v>
+        <v>123927793</v>
       </c>
       <c r="B37" t="n">
-        <v>79870</v>
+        <v>91008</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5578,42 +5639,51 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497133</v>
+        <v>497653</v>
       </c>
       <c r="R37" t="n">
-        <v>7067678</v>
+        <v>7068061</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5642,7 +5712,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5652,7 +5722,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5666,27 +5741,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5704,10 +5779,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123933086</v>
+        <v>123934404</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5720,37 +5795,47 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497126</v>
+        <v>496972</v>
       </c>
       <c r="R38" t="n">
-        <v>7067709</v>
+        <v>7067780</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5779,7 +5864,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5789,7 +5874,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5818,12 +5908,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5841,7 +5931,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123928574</v>
+        <v>123928831</v>
       </c>
       <c r="B39" t="n">
         <v>79897</v>
@@ -5881,10 +5971,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497848</v>
+        <v>497927</v>
       </c>
       <c r="R39" t="n">
-        <v>7068101</v>
+        <v>7068210</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
@@ -5916,7 +6006,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5926,7 +6016,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5958,10 +6048,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123933774</v>
+        <v>123929067</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5974,37 +6064,47 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497066</v>
+        <v>497903</v>
       </c>
       <c r="R40" t="n">
-        <v>7067728</v>
+        <v>7068110</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6033,7 +6133,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6043,7 +6143,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6057,7 +6162,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -6072,12 +6177,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6095,10 +6200,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123928327</v>
+        <v>123928858</v>
       </c>
       <c r="B41" t="n">
-        <v>56703</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6107,48 +6212,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497712</v>
+        <v>497900</v>
       </c>
       <c r="R41" t="n">
-        <v>7068103</v>
+        <v>7068251</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -6180,7 +6275,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6190,12 +6285,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6210,6 +6305,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6227,10 +6342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123925602</v>
+        <v>123933712</v>
       </c>
       <c r="B42" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6239,31 +6354,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6273,17 +6388,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497599</v>
+        <v>497111</v>
       </c>
       <c r="R42" t="n">
-        <v>7067878</v>
+        <v>7067721</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6312,7 +6427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6322,12 +6437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6341,27 +6456,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6379,10 +6474,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123929282</v>
+        <v>123933422</v>
       </c>
       <c r="B43" t="n">
-        <v>79870</v>
+        <v>90986</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6395,37 +6490,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497853</v>
+        <v>497077</v>
       </c>
       <c r="R43" t="n">
-        <v>7067970</v>
+        <v>7067679</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6454,7 +6554,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6464,12 +6564,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6488,22 +6583,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6521,10 +6616,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123929301</v>
+        <v>123928438</v>
       </c>
       <c r="B44" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6537,42 +6632,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497846</v>
+        <v>497801</v>
       </c>
       <c r="R44" t="n">
-        <v>7067985</v>
+        <v>7068154</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6601,7 +6691,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6611,12 +6701,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6668,10 +6753,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123929267</v>
+        <v>123928379</v>
       </c>
       <c r="B45" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6684,42 +6769,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497833</v>
+        <v>497732</v>
       </c>
       <c r="R45" t="n">
-        <v>7067988</v>
+        <v>7068101</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6748,7 +6828,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6758,12 +6838,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6782,22 +6857,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6815,10 +6890,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123925387</v>
+        <v>123934442</v>
       </c>
       <c r="B46" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6827,60 +6902,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497600</v>
+        <v>496964</v>
       </c>
       <c r="R46" t="n">
-        <v>7067872</v>
+        <v>7067764</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6907,14 +6963,19 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6929,6 +6990,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6946,10 +7027,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123932552</v>
+        <v>123928741</v>
       </c>
       <c r="B47" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6958,20 +7039,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6979,10 +7060,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6991,13 +7086,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497461</v>
+        <v>497907</v>
       </c>
       <c r="R47" t="n">
-        <v>7067890</v>
+        <v>7068146</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7026,7 +7121,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7036,12 +7131,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7056,26 +7151,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7093,10 +7168,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123934908</v>
+        <v>123929497</v>
       </c>
       <c r="B48" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7109,39 +7184,44 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497399</v>
+        <v>497846</v>
       </c>
       <c r="R48" t="n">
-        <v>7067620</v>
+        <v>7067895</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7173,7 +7253,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7183,7 +7263,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7212,12 +7297,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7235,10 +7320,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123925995</v>
+        <v>123932552</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7251,37 +7336,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497628</v>
+        <v>497461</v>
       </c>
       <c r="R49" t="n">
-        <v>7067895</v>
+        <v>7067890</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7310,7 +7400,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7320,7 +7410,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7349,12 +7444,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7372,10 +7467,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123928514</v>
+        <v>123932697</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7388,37 +7483,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497851</v>
+        <v>497385</v>
       </c>
       <c r="R50" t="n">
-        <v>7068090</v>
+        <v>7067784</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7447,7 +7547,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7457,7 +7557,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7476,22 +7576,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7509,10 +7609,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123931338</v>
+        <v>123933774</v>
       </c>
       <c r="B51" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7525,47 +7625,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497552</v>
+        <v>497066</v>
       </c>
       <c r="R51" t="n">
-        <v>7067881</v>
+        <v>7067728</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7594,7 +7684,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7604,12 +7694,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7623,7 +7708,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7638,12 +7723,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7661,10 +7746,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123934695</v>
+        <v>123934349</v>
       </c>
       <c r="B52" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7673,46 +7758,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497164</v>
+        <v>496957</v>
       </c>
       <c r="R52" t="n">
-        <v>7067665</v>
+        <v>7067780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7741,7 +7821,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7751,12 +7831,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7770,27 +7845,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7808,7 +7883,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123933859</v>
+        <v>123927550</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -7844,14 +7919,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497016</v>
+        <v>497670</v>
       </c>
       <c r="R53" t="n">
-        <v>7067743</v>
+        <v>7068014</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7883,7 +7958,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7893,12 +7968,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7950,10 +8020,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123931684</v>
+        <v>123929190</v>
       </c>
       <c r="B54" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7966,47 +8036,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497576</v>
+        <v>497832</v>
       </c>
       <c r="R54" t="n">
-        <v>7067995</v>
+        <v>7067981</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8035,7 +8095,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8045,12 +8105,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8079,12 +8139,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8102,10 +8162,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123929497</v>
+        <v>123933492</v>
       </c>
       <c r="B55" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8118,44 +8178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497846</v>
+        <v>497103</v>
       </c>
       <c r="R55" t="n">
-        <v>7067895</v>
+        <v>7067696</v>
       </c>
       <c r="S55" t="n">
         <v>8</v>
@@ -8187,7 +8237,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8197,12 +8247,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8231,12 +8276,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8254,10 +8299,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123929700</v>
+        <v>123932385</v>
       </c>
       <c r="B56" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8270,47 +8315,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497829</v>
+        <v>497528</v>
       </c>
       <c r="R56" t="n">
-        <v>7067835</v>
+        <v>7067930</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8339,7 +8374,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8349,12 +8384,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8368,7 +8398,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -8383,12 +8413,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8406,7 +8436,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123927550</v>
+        <v>123933962</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -8442,17 +8472,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497670</v>
+        <v>496999</v>
       </c>
       <c r="R57" t="n">
-        <v>7068014</v>
+        <v>7067688</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8481,7 +8511,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8491,7 +8521,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8543,10 +8573,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123928741</v>
+        <v>123929267</v>
       </c>
       <c r="B58" t="n">
-        <v>57861</v>
+        <v>79869</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8555,45 +8585,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8602,13 +8618,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497907</v>
+        <v>497833</v>
       </c>
       <c r="R58" t="n">
-        <v>7068146</v>
+        <v>7067988</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8637,7 +8653,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8647,12 +8663,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8667,6 +8683,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8684,10 +8720,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123931433</v>
+        <v>123933127</v>
       </c>
       <c r="B59" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8700,47 +8736,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497554</v>
+        <v>497133</v>
       </c>
       <c r="R59" t="n">
-        <v>7067886</v>
+        <v>7067678</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8769,7 +8800,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8779,12 +8810,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8803,22 +8829,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8836,10 +8862,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123932201</v>
+        <v>123934085</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8848,55 +8874,60 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497553</v>
+        <v>496980</v>
       </c>
       <c r="R60" t="n">
-        <v>7068083</v>
+        <v>7067690</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8925,7 +8956,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8935,12 +8966,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8951,6 +8982,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8967,10 +9003,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123933650</v>
+        <v>123932201</v>
       </c>
       <c r="B61" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8979,46 +9015,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497112</v>
+        <v>497553</v>
       </c>
       <c r="R61" t="n">
-        <v>7067726</v>
+        <v>7068083</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -9047,7 +9092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9057,7 +9102,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9068,31 +9118,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -9109,10 +9134,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123927991</v>
+        <v>123934695</v>
       </c>
       <c r="B62" t="n">
-        <v>57491</v>
+        <v>79773</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9121,51 +9146,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497659</v>
+        <v>497164</v>
       </c>
       <c r="R62" t="n">
-        <v>7068053</v>
+        <v>7067665</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -9194,7 +9214,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9204,12 +9224,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9228,22 +9248,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9261,7 +9281,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123928803</v>
+        <v>123932608</v>
       </c>
       <c r="B63" t="n">
         <v>78788</v>
@@ -9301,10 +9321,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497932</v>
+        <v>497492</v>
       </c>
       <c r="R63" t="n">
-        <v>7068202</v>
+        <v>7067833</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -9336,7 +9356,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9346,12 +9366,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9403,10 +9418,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123929067</v>
+        <v>123925995</v>
       </c>
       <c r="B64" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9419,47 +9434,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497903</v>
+        <v>497628</v>
       </c>
       <c r="R64" t="n">
-        <v>7068110</v>
+        <v>7067895</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9488,7 +9493,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9498,12 +9503,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9555,10 +9555,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123932682</v>
+        <v>123929370</v>
       </c>
       <c r="B65" t="n">
-        <v>79869</v>
+        <v>79904</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9567,25 +9567,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497368</v>
+        <v>497852</v>
       </c>
       <c r="R65" t="n">
-        <v>7067763</v>
+        <v>7067984</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9697,10 +9697,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948037</v>
+        <v>123948048</v>
       </c>
       <c r="B66" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497443</v>
+        <v>497417</v>
       </c>
       <c r="R66" t="n">
-        <v>7067840</v>
+        <v>7067613</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9773,6 +9773,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9799,10 +9804,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948084</v>
+        <v>123948065</v>
       </c>
       <c r="B67" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9815,21 +9820,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9839,10 +9844,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497101</v>
+        <v>497547</v>
       </c>
       <c r="R67" t="n">
-        <v>7067728</v>
+        <v>7068008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9875,6 +9880,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9901,7 +9911,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948071</v>
+        <v>123948058</v>
       </c>
       <c r="B68" t="n">
         <v>57491</v>
@@ -9941,10 +9951,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497830</v>
+        <v>497156</v>
       </c>
       <c r="R68" t="n">
-        <v>7068267</v>
+        <v>7067976</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9981,7 +9991,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10008,7 +10018,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948055</v>
+        <v>123948041</v>
       </c>
       <c r="B69" t="n">
         <v>57491</v>
@@ -10048,10 +10058,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497062</v>
+        <v>497578</v>
       </c>
       <c r="R69" t="n">
-        <v>7068109</v>
+        <v>7067475</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -10088,7 +10098,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10115,7 +10125,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948075</v>
+        <v>123948053</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -10155,10 +10165,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497629</v>
+        <v>497052</v>
       </c>
       <c r="R70" t="n">
-        <v>7068330</v>
+        <v>7067797</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10195,7 +10205,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10222,7 +10232,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948070</v>
+        <v>123948077</v>
       </c>
       <c r="B71" t="n">
         <v>57491</v>
@@ -10262,10 +10272,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497876</v>
+        <v>497583</v>
       </c>
       <c r="R71" t="n">
-        <v>7068110</v>
+        <v>7068342</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10302,7 +10312,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10329,7 +10339,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948085</v>
+        <v>123948084</v>
       </c>
       <c r="B72" t="n">
         <v>91008</v>
@@ -10369,10 +10379,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497243</v>
+        <v>497101</v>
       </c>
       <c r="R72" t="n">
-        <v>7067786</v>
+        <v>7067728</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10431,7 +10441,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948048</v>
+        <v>123948069</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -10471,10 +10481,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497417</v>
+        <v>497544</v>
       </c>
       <c r="R73" t="n">
-        <v>7067613</v>
+        <v>7067872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10538,7 +10548,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948057</v>
+        <v>123948075</v>
       </c>
       <c r="B74" t="n">
         <v>57491</v>
@@ -10578,10 +10588,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497142</v>
+        <v>497629</v>
       </c>
       <c r="R74" t="n">
-        <v>7068071</v>
+        <v>7068330</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10618,7 +10628,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10645,10 +10655,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948081</v>
+        <v>123948049</v>
       </c>
       <c r="B75" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10657,25 +10667,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10685,10 +10695,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497267</v>
+        <v>496958</v>
       </c>
       <c r="R75" t="n">
-        <v>7068098</v>
+        <v>7067783</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10721,6 +10731,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10747,7 +10762,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948078</v>
+        <v>123948060</v>
       </c>
       <c r="B76" t="n">
         <v>57491</v>
@@ -10787,10 +10802,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497569</v>
+        <v>497140</v>
       </c>
       <c r="R76" t="n">
-        <v>7068352</v>
+        <v>7067713</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10854,10 +10869,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948079</v>
+        <v>123948085</v>
       </c>
       <c r="B77" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10870,21 +10885,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10894,10 +10909,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497614</v>
+        <v>497243</v>
       </c>
       <c r="R77" t="n">
-        <v>7067898</v>
+        <v>7067786</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10930,11 +10945,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10961,7 +10971,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948061</v>
+        <v>123948051</v>
       </c>
       <c r="B78" t="n">
         <v>57491</v>
@@ -11001,10 +11011,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497152</v>
+        <v>496962</v>
       </c>
       <c r="R78" t="n">
-        <v>7067720</v>
+        <v>7067810</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -11068,7 +11078,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948067</v>
+        <v>123948055</v>
       </c>
       <c r="B79" t="n">
         <v>57491</v>
@@ -11108,10 +11118,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497567</v>
+        <v>497062</v>
       </c>
       <c r="R79" t="n">
-        <v>7067939</v>
+        <v>7068109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11148,7 +11158,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11175,7 +11185,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948049</v>
+        <v>123948059</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11215,10 +11225,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496958</v>
+        <v>497338</v>
       </c>
       <c r="R80" t="n">
-        <v>7067783</v>
+        <v>7068065</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11255,7 +11265,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11282,7 +11292,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948058</v>
+        <v>123948050</v>
       </c>
       <c r="B81" t="n">
         <v>57491</v>
@@ -11322,10 +11332,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497156</v>
+        <v>496963</v>
       </c>
       <c r="R81" t="n">
-        <v>7067976</v>
+        <v>7067823</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11389,7 +11399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948068</v>
+        <v>123948063</v>
       </c>
       <c r="B82" t="n">
         <v>57491</v>
@@ -11429,10 +11439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497549</v>
+        <v>497448</v>
       </c>
       <c r="R82" t="n">
-        <v>7067939</v>
+        <v>7067857</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11469,7 +11479,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11496,7 +11506,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948073</v>
+        <v>123948078</v>
       </c>
       <c r="B83" t="n">
         <v>57491</v>
@@ -11536,10 +11546,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497810</v>
+        <v>497569</v>
       </c>
       <c r="R83" t="n">
-        <v>7068216</v>
+        <v>7068352</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11603,10 +11613,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948066</v>
+        <v>123948081</v>
       </c>
       <c r="B84" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11615,25 +11625,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11643,10 +11653,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497568</v>
+        <v>497267</v>
       </c>
       <c r="R84" t="n">
-        <v>7067974</v>
+        <v>7068098</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11679,11 +11689,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11710,7 +11715,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948059</v>
+        <v>123948079</v>
       </c>
       <c r="B85" t="n">
         <v>57491</v>
@@ -11750,10 +11755,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497338</v>
+        <v>497614</v>
       </c>
       <c r="R85" t="n">
-        <v>7068065</v>
+        <v>7067898</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11790,7 +11795,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11817,7 +11822,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948069</v>
+        <v>123948061</v>
       </c>
       <c r="B86" t="n">
         <v>57491</v>
@@ -11857,10 +11862,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497544</v>
+        <v>497152</v>
       </c>
       <c r="R86" t="n">
-        <v>7067872</v>
+        <v>7067720</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11924,7 +11929,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948052</v>
+        <v>123948057</v>
       </c>
       <c r="B87" t="n">
         <v>57491</v>
@@ -11964,10 +11969,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>496977</v>
+        <v>497142</v>
       </c>
       <c r="R87" t="n">
-        <v>7067794</v>
+        <v>7068071</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12031,7 +12036,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948062</v>
+        <v>123948064</v>
       </c>
       <c r="B88" t="n">
         <v>57491</v>
@@ -12071,10 +12076,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497431</v>
+        <v>497471</v>
       </c>
       <c r="R88" t="n">
-        <v>7067834</v>
+        <v>7067944</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12138,10 +12143,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948083</v>
+        <v>123948062</v>
       </c>
       <c r="B89" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12154,21 +12159,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12178,10 +12183,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497012</v>
+        <v>497431</v>
       </c>
       <c r="R89" t="n">
-        <v>7067783</v>
+        <v>7067834</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12214,6 +12219,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12240,7 +12250,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948074</v>
+        <v>123948054</v>
       </c>
       <c r="B90" t="n">
         <v>57491</v>
@@ -12280,10 +12290,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497809</v>
+        <v>497062</v>
       </c>
       <c r="R90" t="n">
-        <v>7068221</v>
+        <v>7068118</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12347,7 +12357,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948050</v>
+        <v>123948074</v>
       </c>
       <c r="B91" t="n">
         <v>57491</v>
@@ -12387,10 +12397,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>496963</v>
+        <v>497809</v>
       </c>
       <c r="R91" t="n">
-        <v>7067823</v>
+        <v>7068221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12427,7 +12437,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12561,7 +12571,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948053</v>
+        <v>123948066</v>
       </c>
       <c r="B93" t="n">
         <v>57491</v>
@@ -12601,10 +12611,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497052</v>
+        <v>497568</v>
       </c>
       <c r="R93" t="n">
-        <v>7067797</v>
+        <v>7067974</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12641,7 +12651,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12668,7 +12678,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948064</v>
+        <v>123948076</v>
       </c>
       <c r="B94" t="n">
         <v>57491</v>
@@ -12708,10 +12718,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497471</v>
+        <v>497599</v>
       </c>
       <c r="R94" t="n">
-        <v>7067944</v>
+        <v>7068342</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12775,7 +12785,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123948065</v>
+        <v>123948068</v>
       </c>
       <c r="B95" t="n">
         <v>57491</v>
@@ -12815,10 +12825,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497547</v>
+        <v>497549</v>
       </c>
       <c r="R95" t="n">
-        <v>7068008</v>
+        <v>7067939</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12882,7 +12892,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123948051</v>
+        <v>123948067</v>
       </c>
       <c r="B96" t="n">
         <v>57491</v>
@@ -12922,10 +12932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>496962</v>
+        <v>497567</v>
       </c>
       <c r="R96" t="n">
-        <v>7067810</v>
+        <v>7067939</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12962,7 +12972,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12989,7 +12999,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123948041</v>
+        <v>123948070</v>
       </c>
       <c r="B97" t="n">
         <v>57491</v>
@@ -13029,10 +13039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497578</v>
+        <v>497876</v>
       </c>
       <c r="R97" t="n">
-        <v>7067475</v>
+        <v>7068110</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13069,7 +13079,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13096,10 +13106,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123948082</v>
+        <v>123948071</v>
       </c>
       <c r="B98" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13108,25 +13118,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13136,10 +13146,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497300</v>
+        <v>497830</v>
       </c>
       <c r="R98" t="n">
-        <v>7068117</v>
+        <v>7068267</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13172,6 +13182,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13198,7 +13213,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123948060</v>
+        <v>123948052</v>
       </c>
       <c r="B99" t="n">
         <v>57491</v>
@@ -13238,10 +13253,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497140</v>
+        <v>496977</v>
       </c>
       <c r="R99" t="n">
-        <v>7067713</v>
+        <v>7067794</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13305,10 +13320,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123948076</v>
+        <v>123948082</v>
       </c>
       <c r="B100" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13317,25 +13332,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13345,10 +13360,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497599</v>
+        <v>497300</v>
       </c>
       <c r="R100" t="n">
-        <v>7068342</v>
+        <v>7068117</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13381,11 +13396,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13412,7 +13422,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948077</v>
+        <v>123948073</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13452,10 +13462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497583</v>
+        <v>497810</v>
       </c>
       <c r="R101" t="n">
-        <v>7068342</v>
+        <v>7068216</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13492,7 +13502,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13519,10 +13529,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123948063</v>
+        <v>123948037</v>
       </c>
       <c r="B102" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13535,21 +13545,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13559,10 +13569,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497448</v>
+        <v>497443</v>
       </c>
       <c r="R102" t="n">
-        <v>7067857</v>
+        <v>7067840</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13595,11 +13605,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13626,10 +13631,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123948054</v>
+        <v>123948083</v>
       </c>
       <c r="B103" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13642,21 +13647,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13666,10 +13671,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497062</v>
+        <v>497012</v>
       </c>
       <c r="R103" t="n">
-        <v>7068118</v>
+        <v>7067783</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13702,11 +13707,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935511</v>
+        <v>123935971</v>
       </c>
       <c r="B105" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,44 +13886,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497429</v>
+        <v>497477</v>
       </c>
       <c r="R105" t="n">
-        <v>7067368</v>
+        <v>7067373</v>
       </c>
       <c r="S105" t="n">
         <v>9</v>
@@ -13955,7 +13945,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13965,7 +13955,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13994,12 +13984,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14017,7 +14007,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123936388</v>
+        <v>123935892</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -14057,13 +14047,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497347</v>
+        <v>497488</v>
       </c>
       <c r="R106" t="n">
-        <v>7067031</v>
+        <v>7067338</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14092,7 +14082,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14102,7 +14092,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14154,7 +14144,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935469</v>
+        <v>123936388</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -14194,13 +14184,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497429</v>
+        <v>497347</v>
       </c>
       <c r="R107" t="n">
-        <v>7067378</v>
+        <v>7067031</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14229,7 +14219,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14239,7 +14229,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14291,7 +14281,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123935892</v>
+        <v>123935469</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -14331,13 +14321,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497488</v>
+        <v>497429</v>
       </c>
       <c r="R108" t="n">
-        <v>7067338</v>
+        <v>7067378</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14366,7 +14356,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14376,7 +14366,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14428,10 +14418,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123935971</v>
+        <v>123936336</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14444,37 +14434,47 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497477</v>
+        <v>497296</v>
       </c>
       <c r="R109" t="n">
-        <v>7067373</v>
+        <v>7067024</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14513,7 +14513,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14542,12 +14547,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14565,7 +14570,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123936336</v>
+        <v>123935511</v>
       </c>
       <c r="B110" t="n">
         <v>57491</v>
@@ -14601,7 +14606,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -14615,13 +14620,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497296</v>
+        <v>497429</v>
       </c>
       <c r="R110" t="n">
-        <v>7067024</v>
+        <v>7067368</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14650,7 +14655,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14660,12 +14665,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14717,7 +14717,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935623</v>
+        <v>123935662</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -14757,13 +14757,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497400</v>
+        <v>497407</v>
       </c>
       <c r="R111" t="n">
-        <v>7067320</v>
+        <v>7067289</v>
       </c>
       <c r="S111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14854,7 +14854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123935662</v>
+        <v>123935623</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -14894,13 +14894,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497407</v>
+        <v>497400</v>
       </c>
       <c r="R112" t="n">
-        <v>7067289</v>
+        <v>7067320</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948047</v>
+        <v>123948039</v>
       </c>
       <c r="B114" t="n">
         <v>57491</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497422</v>
+        <v>497241</v>
       </c>
       <c r="R114" t="n">
-        <v>7067360</v>
+        <v>7067063</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,7 +15205,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948040</v>
+        <v>123948047</v>
       </c>
       <c r="B115" t="n">
         <v>57491</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497269</v>
+        <v>497422</v>
       </c>
       <c r="R115" t="n">
-        <v>7067065</v>
+        <v>7067360</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15312,10 +15312,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948080</v>
+        <v>123948040</v>
       </c>
       <c r="B116" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15328,16 +15328,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497370</v>
+        <v>497269</v>
       </c>
       <c r="R116" t="n">
-        <v>7067042</v>
+        <v>7067065</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15526,10 +15526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948038</v>
+        <v>123948080</v>
       </c>
       <c r="B118" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497227</v>
+        <v>497370</v>
       </c>
       <c r="R118" t="n">
-        <v>7067047</v>
+        <v>7067042</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15633,7 +15633,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948039</v>
+        <v>123948038</v>
       </c>
       <c r="B119" t="n">
         <v>57491</v>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497241</v>
+        <v>497227</v>
       </c>
       <c r="R119" t="n">
-        <v>7067063</v>
+        <v>7067047</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123925602</v>
+        <v>123925768</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1969,47 +1969,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497599</v>
+        <v>497652</v>
       </c>
       <c r="R11" t="n">
-        <v>7067878</v>
+        <v>7067869</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2038,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2048,12 +2038,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2082,12 +2067,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2105,10 +2090,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123934255</v>
+        <v>123928574</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2117,41 +2102,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496932</v>
+        <v>497848</v>
       </c>
       <c r="R12" t="n">
-        <v>7067736</v>
+        <v>7068101</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2180,7 +2165,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2190,7 +2175,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2204,27 +2189,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2242,10 +2207,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123925768</v>
+        <v>123925602</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2258,37 +2223,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497652</v>
+        <v>497599</v>
       </c>
       <c r="R13" t="n">
-        <v>7067869</v>
+        <v>7067878</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2317,7 +2292,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2327,7 +2302,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2356,12 +2336,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2379,10 +2359,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123933142</v>
+        <v>123934255</v>
       </c>
       <c r="B14" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2391,46 +2371,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497133</v>
+        <v>496932</v>
       </c>
       <c r="R14" t="n">
-        <v>7067678</v>
+        <v>7067736</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2459,7 +2434,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2469,7 +2444,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2483,27 +2458,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2521,10 +2496,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123928574</v>
+        <v>123933142</v>
       </c>
       <c r="B15" t="n">
-        <v>79897</v>
+        <v>79905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2537,34 +2512,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497848</v>
+        <v>497133</v>
       </c>
       <c r="R15" t="n">
-        <v>7068101</v>
+        <v>7067678</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2596,7 +2576,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2606,7 +2586,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2621,6 +2601,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123928327</v>
+        <v>123931528</v>
       </c>
       <c r="B16" t="n">
-        <v>56703</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2674,7 +2674,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497712</v>
+        <v>497563</v>
       </c>
       <c r="R16" t="n">
-        <v>7068103</v>
+        <v>7067965</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2753,6 +2753,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2770,10 +2790,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123934742</v>
+        <v>123929282</v>
       </c>
       <c r="B17" t="n">
-        <v>56692</v>
+        <v>79870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2786,47 +2806,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497184</v>
+        <v>497853</v>
       </c>
       <c r="R17" t="n">
-        <v>7067677</v>
+        <v>7067970</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2865,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2875,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2884,7 +2894,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2902,10 +2932,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123928803</v>
+        <v>123933650</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2918,34 +2948,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497932</v>
+        <v>497112</v>
       </c>
       <c r="R18" t="n">
-        <v>7068202</v>
+        <v>7067726</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2977,7 +3012,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2987,12 +3022,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3006,7 +3036,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3021,12 +3051,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3044,10 +3074,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123931528</v>
+        <v>123928803</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3060,47 +3090,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497563</v>
+        <v>497932</v>
       </c>
       <c r="R19" t="n">
-        <v>7067965</v>
+        <v>7068202</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3129,7 +3149,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3139,12 +3159,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3173,12 +3193,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3196,10 +3216,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123929282</v>
+        <v>123928327</v>
       </c>
       <c r="B20" t="n">
-        <v>79870</v>
+        <v>56703</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3208,41 +3228,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497853</v>
+        <v>497712</v>
       </c>
       <c r="R20" t="n">
-        <v>7067970</v>
+        <v>7068103</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3271,7 +3301,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3281,12 +3311,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3301,26 +3331,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3338,10 +3348,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123933650</v>
+        <v>123934742</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>56692</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3354,27 +3364,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3383,13 +3398,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497112</v>
+        <v>497184</v>
       </c>
       <c r="R21" t="n">
-        <v>7067726</v>
+        <v>7067677</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3418,7 +3433,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3428,7 +3443,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3443,26 +3463,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123932682</v>
+        <v>123929700</v>
       </c>
       <c r="B22" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3496,42 +3496,47 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497368</v>
+        <v>497829</v>
       </c>
       <c r="R22" t="n">
-        <v>7067763</v>
+        <v>7067835</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3575,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3584,27 +3594,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,7 +3632,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123929700</v>
+        <v>123931338</v>
       </c>
       <c r="B23" t="n">
         <v>57491</v>
@@ -3658,7 +3668,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3668,17 +3678,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497829</v>
+        <v>497552</v>
       </c>
       <c r="R23" t="n">
-        <v>7067835</v>
+        <v>7067881</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3707,7 +3717,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3717,12 +3727,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3736,7 +3746,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3774,10 +3784,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931338</v>
+        <v>123932682</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3790,47 +3800,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497552</v>
+        <v>497368</v>
       </c>
       <c r="R24" t="n">
-        <v>7067881</v>
+        <v>7067763</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3859,7 +3864,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3869,12 +3874,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123932969</v>
+        <v>123932710</v>
       </c>
       <c r="B32" t="n">
-        <v>56692</v>
+        <v>79870</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4956,47 +4956,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497236</v>
+        <v>497376</v>
       </c>
       <c r="R32" t="n">
-        <v>7067739</v>
+        <v>7067768</v>
       </c>
       <c r="S32" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -5025,7 +5015,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5035,12 +5025,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5055,6 +5040,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5072,10 +5077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123932710</v>
+        <v>123932969</v>
       </c>
       <c r="B33" t="n">
-        <v>79870</v>
+        <v>56692</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5088,37 +5093,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497376</v>
+        <v>497236</v>
       </c>
       <c r="R33" t="n">
-        <v>7067768</v>
+        <v>7067739</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5147,7 +5162,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5157,7 +5172,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5172,26 +5192,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6048,10 +6048,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123929067</v>
+        <v>123928858</v>
       </c>
       <c r="B40" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6064,44 +6064,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497903</v>
+        <v>497900</v>
       </c>
       <c r="R40" t="n">
-        <v>7068110</v>
+        <v>7068251</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6133,7 +6123,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6143,12 +6133,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6177,12 +6167,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6200,10 +6190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123928858</v>
+        <v>123933712</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6212,41 +6202,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497900</v>
+        <v>497111</v>
       </c>
       <c r="R41" t="n">
-        <v>7068251</v>
+        <v>7067721</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6304,27 +6304,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6342,10 +6322,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123933712</v>
+        <v>123933422</v>
       </c>
       <c r="B42" t="n">
-        <v>56700</v>
+        <v>90986</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6354,36 +6334,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6392,13 +6367,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497111</v>
+        <v>497077</v>
       </c>
       <c r="R42" t="n">
-        <v>7067721</v>
+        <v>7067679</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6427,7 +6402,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6437,12 +6412,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6456,7 +6426,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6474,10 +6464,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123933422</v>
+        <v>123929067</v>
       </c>
       <c r="B43" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6490,39 +6480,44 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497077</v>
+        <v>497903</v>
       </c>
       <c r="R43" t="n">
-        <v>7067679</v>
+        <v>7068110</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -6554,7 +6549,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6564,7 +6559,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123925995</v>
+        <v>123929370</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9430,20 +9430,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9452,19 +9452,24 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497628</v>
+        <v>497852</v>
       </c>
       <c r="R64" t="n">
-        <v>7067895</v>
+        <v>7067984</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9493,7 +9498,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9503,7 +9508,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9522,22 +9527,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9555,10 +9560,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123929370</v>
+        <v>123925995</v>
       </c>
       <c r="B65" t="n">
-        <v>79904</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9567,20 +9572,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9589,24 +9594,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497852</v>
+        <v>497628</v>
       </c>
       <c r="R65" t="n">
-        <v>7067984</v>
+        <v>7067895</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9664,22 +9664,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -10655,10 +10655,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948049</v>
+        <v>123948085</v>
       </c>
       <c r="B75" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10671,21 +10671,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10695,10 +10695,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496958</v>
+        <v>497243</v>
       </c>
       <c r="R75" t="n">
-        <v>7067783</v>
+        <v>7067786</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10731,11 +10731,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10762,7 +10757,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948060</v>
+        <v>123948049</v>
       </c>
       <c r="B76" t="n">
         <v>57491</v>
@@ -10802,10 +10797,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497140</v>
+        <v>496958</v>
       </c>
       <c r="R76" t="n">
-        <v>7067713</v>
+        <v>7067783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10842,7 +10837,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10869,10 +10864,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948085</v>
+        <v>123948060</v>
       </c>
       <c r="B77" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10885,21 +10880,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497243</v>
+        <v>497140</v>
       </c>
       <c r="R77" t="n">
-        <v>7067786</v>
+        <v>7067713</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10945,6 +10940,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11185,7 +11185,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948059</v>
+        <v>123948050</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497338</v>
+        <v>496963</v>
       </c>
       <c r="R80" t="n">
-        <v>7068065</v>
+        <v>7067823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11292,7 +11292,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948050</v>
+        <v>123948063</v>
       </c>
       <c r="B81" t="n">
         <v>57491</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496963</v>
+        <v>497448</v>
       </c>
       <c r="R81" t="n">
-        <v>7067823</v>
+        <v>7067857</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11399,7 +11399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948063</v>
+        <v>123948059</v>
       </c>
       <c r="B82" t="n">
         <v>57491</v>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497448</v>
+        <v>497338</v>
       </c>
       <c r="R82" t="n">
-        <v>7067857</v>
+        <v>7068065</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11506,10 +11506,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948078</v>
+        <v>123948081</v>
       </c>
       <c r="B83" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11518,25 +11518,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497569</v>
+        <v>497267</v>
       </c>
       <c r="R83" t="n">
-        <v>7068352</v>
+        <v>7068098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11582,11 +11582,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11613,10 +11608,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948081</v>
+        <v>123948078</v>
       </c>
       <c r="B84" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11625,25 +11620,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11653,10 +11648,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497267</v>
+        <v>497569</v>
       </c>
       <c r="R84" t="n">
-        <v>7068098</v>
+        <v>7068352</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11689,6 +11684,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12892,7 +12892,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123948067</v>
+        <v>123948070</v>
       </c>
       <c r="B96" t="n">
         <v>57491</v>
@@ -12932,10 +12932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497567</v>
+        <v>497876</v>
       </c>
       <c r="R96" t="n">
-        <v>7067939</v>
+        <v>7068110</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12999,7 +12999,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123948070</v>
+        <v>123948067</v>
       </c>
       <c r="B97" t="n">
         <v>57491</v>
@@ -13039,10 +13039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497876</v>
+        <v>497567</v>
       </c>
       <c r="R97" t="n">
-        <v>7068110</v>
+        <v>7067939</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123926190</v>
+        <v>123933650</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497654</v>
+        <v>497112</v>
       </c>
       <c r="R2" t="n">
-        <v>7067926</v>
+        <v>7067726</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -789,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123931616</v>
+        <v>123932697</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +833,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497562</v>
+        <v>497385</v>
       </c>
       <c r="R3" t="n">
-        <v>7067959</v>
+        <v>7067784</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,22 +926,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123933859</v>
+        <v>123931338</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,37 +975,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497016</v>
+        <v>497552</v>
       </c>
       <c r="R4" t="n">
-        <v>7067743</v>
+        <v>7067881</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1054,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,12 +1088,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,7 +1111,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933086</v>
+        <v>123926766</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1125,19 +1145,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497126</v>
+        <v>497661</v>
       </c>
       <c r="R5" t="n">
-        <v>7067709</v>
+        <v>7067931</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,7 +1201,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1228,10 +1258,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123934908</v>
+        <v>123929190</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,42 +1274,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497399</v>
+        <v>497832</v>
       </c>
       <c r="R6" t="n">
-        <v>7067620</v>
+        <v>7067981</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1308,7 +1333,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,7 +1343,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,12 +1377,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,10 +1400,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123927991</v>
+        <v>123934349</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,44 +1416,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497659</v>
+        <v>496957</v>
       </c>
       <c r="R7" t="n">
-        <v>7068053</v>
+        <v>7067780</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1455,7 +1475,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,12 +1485,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,7 +1499,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1499,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123931433</v>
+        <v>123928379</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1538,44 +1553,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497554</v>
+        <v>497732</v>
       </c>
       <c r="R8" t="n">
-        <v>7067886</v>
+        <v>7068101</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1617,12 +1622,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123925856</v>
+        <v>123929301</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1690,37 +1690,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497652</v>
+        <v>497846</v>
       </c>
       <c r="R9" t="n">
-        <v>7067886</v>
+        <v>7067985</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1749,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1759,7 +1764,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1811,10 +1821,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123935202</v>
+        <v>123928831</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
+        <v>79897</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1823,46 +1833,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497524</v>
+        <v>497927</v>
       </c>
       <c r="R10" t="n">
-        <v>7067827</v>
+        <v>7068210</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1891,7 +1896,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1901,7 +1906,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1916,26 +1921,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1953,10 +1938,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123925768</v>
+        <v>123927991</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1969,37 +1954,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497652</v>
+        <v>497659</v>
       </c>
       <c r="R11" t="n">
-        <v>7067869</v>
+        <v>7068053</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2028,7 +2023,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2038,7 +2033,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123928574</v>
+        <v>123932969</v>
       </c>
       <c r="B12" t="n">
-        <v>79897</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2102,41 +2102,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497848</v>
+        <v>497236</v>
       </c>
       <c r="R12" t="n">
-        <v>7068101</v>
+        <v>7067739</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2165,7 +2175,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2175,7 +2185,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2207,7 +2222,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123925602</v>
+        <v>123934404</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -2243,7 +2258,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2253,17 +2268,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497599</v>
+        <v>496972</v>
       </c>
       <c r="R13" t="n">
-        <v>7067878</v>
+        <v>7067780</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2292,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2302,12 +2317,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2359,10 +2374,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123934255</v>
+        <v>123932552</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2375,37 +2390,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496932</v>
+        <v>497461</v>
       </c>
       <c r="R14" t="n">
-        <v>7067736</v>
+        <v>7067890</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2434,7 +2454,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2444,7 +2464,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2458,7 +2483,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2473,12 +2498,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2496,10 +2521,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123933142</v>
+        <v>123934255</v>
       </c>
       <c r="B15" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2508,46 +2533,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497133</v>
+        <v>496932</v>
       </c>
       <c r="R15" t="n">
-        <v>7067678</v>
+        <v>7067736</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2576,7 +2596,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2586,7 +2606,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2600,27 +2620,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2638,10 +2658,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123931528</v>
+        <v>123929067</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2654,16 +2674,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2674,7 +2694,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2688,13 +2708,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497563</v>
+        <v>497903</v>
       </c>
       <c r="R16" t="n">
-        <v>7067965</v>
+        <v>7068110</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2723,7 +2743,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2733,12 +2753,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2790,10 +2810,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123929282</v>
+        <v>123934908</v>
       </c>
       <c r="B17" t="n">
-        <v>79870</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2806,37 +2826,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497853</v>
+        <v>497399</v>
       </c>
       <c r="R17" t="n">
-        <v>7067970</v>
+        <v>7067620</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2865,7 +2890,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2875,12 +2900,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2899,22 +2919,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2932,10 +2952,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123933650</v>
+        <v>123925387</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>57861</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2944,46 +2964,60 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497112</v>
+        <v>497600</v>
       </c>
       <c r="R18" t="n">
-        <v>7067726</v>
+        <v>7067872</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3010,19 +3044,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3036,27 +3065,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3074,10 +3083,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123928803</v>
+        <v>123933127</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3090,37 +3099,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497932</v>
+        <v>497133</v>
       </c>
       <c r="R19" t="n">
-        <v>7068202</v>
+        <v>7067678</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3149,7 +3163,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3159,12 +3173,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3183,22 +3192,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3216,10 +3225,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123928327</v>
+        <v>123929267</v>
       </c>
       <c r="B20" t="n">
-        <v>56703</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3228,36 +3237,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3266,10 +3270,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497712</v>
+        <v>497833</v>
       </c>
       <c r="R20" t="n">
-        <v>7068103</v>
+        <v>7067988</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3301,7 +3305,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3311,12 +3315,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3331,6 +3335,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3348,10 +3372,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123934742</v>
+        <v>123933712</v>
       </c>
       <c r="B21" t="n">
-        <v>56692</v>
+        <v>56700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3360,25 +3384,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3398,13 +3422,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497184</v>
+        <v>497111</v>
       </c>
       <c r="R21" t="n">
-        <v>7067677</v>
+        <v>7067721</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3433,7 +3457,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3443,12 +3467,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3480,10 +3504,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123929700</v>
+        <v>123931684</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3496,16 +3520,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3526,17 +3550,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497829</v>
+        <v>497576</v>
       </c>
       <c r="R22" t="n">
-        <v>7067835</v>
+        <v>7067995</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3565,7 +3589,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3575,12 +3599,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3594,7 +3618,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3609,12 +3633,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3632,7 +3656,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931338</v>
+        <v>123929497</v>
       </c>
       <c r="B23" t="n">
         <v>57491</v>
@@ -3668,7 +3692,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3682,13 +3706,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497552</v>
+        <v>497846</v>
       </c>
       <c r="R23" t="n">
-        <v>7067881</v>
+        <v>7067895</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3717,7 +3741,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3727,12 +3751,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3784,10 +3808,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932682</v>
+        <v>123929700</v>
       </c>
       <c r="B24" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3800,42 +3824,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497368</v>
+        <v>497829</v>
       </c>
       <c r="R24" t="n">
-        <v>7067763</v>
+        <v>7067835</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3864,7 +3893,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3874,7 +3903,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3888,27 +3922,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3926,10 +3960,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123934022</v>
+        <v>123931433</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3942,37 +3976,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496970</v>
+        <v>497554</v>
       </c>
       <c r="R25" t="n">
-        <v>7067716</v>
+        <v>7067886</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4001,7 +4045,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4011,12 +4055,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4045,12 +4089,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4068,10 +4112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123934569</v>
+        <v>123926190</v>
       </c>
       <c r="B26" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4084,37 +4128,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497124</v>
+        <v>497654</v>
       </c>
       <c r="R26" t="n">
-        <v>7067682</v>
+        <v>7067926</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4143,7 +4187,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4153,7 +4197,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4167,27 +4211,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4205,10 +4249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123929301</v>
+        <v>123932385</v>
       </c>
       <c r="B27" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4221,42 +4265,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497846</v>
+        <v>497528</v>
       </c>
       <c r="R27" t="n">
-        <v>7067985</v>
+        <v>7067930</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4285,7 +4324,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4295,12 +4334,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4352,10 +4386,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123926766</v>
+        <v>123932682</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4368,42 +4402,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497661</v>
+        <v>497368</v>
       </c>
       <c r="R28" t="n">
-        <v>7067931</v>
+        <v>7067763</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4432,7 +4466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4442,12 +4476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4466,22 +4495,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4499,7 +4528,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123928514</v>
+        <v>123927550</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -4539,13 +4568,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497851</v>
+        <v>497670</v>
       </c>
       <c r="R29" t="n">
-        <v>7068090</v>
+        <v>7068014</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4574,7 +4603,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4584,7 +4613,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4636,10 +4665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123931684</v>
+        <v>123933492</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4652,47 +4681,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497576</v>
+        <v>497103</v>
       </c>
       <c r="R30" t="n">
-        <v>7067995</v>
+        <v>7067696</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4721,7 +4740,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4731,12 +4750,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4765,12 +4779,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4788,10 +4802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123929459</v>
+        <v>123928574</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>79897</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4800,48 +4814,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497843</v>
+        <v>497848</v>
       </c>
       <c r="R31" t="n">
-        <v>7067903</v>
+        <v>7068101</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4873,7 +4877,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4883,12 +4887,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4903,26 +4902,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4940,10 +4919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123932710</v>
+        <v>123935202</v>
       </c>
       <c r="B32" t="n">
-        <v>79870</v>
+        <v>90986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4956,34 +4935,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497376</v>
+        <v>497524</v>
       </c>
       <c r="R32" t="n">
-        <v>7067768</v>
+        <v>7067827</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -5015,7 +4999,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5025,7 +5009,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5054,12 +5038,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5077,10 +5061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123932969</v>
+        <v>123928327</v>
       </c>
       <c r="B33" t="n">
-        <v>56692</v>
+        <v>56703</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5089,20 +5073,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5123,17 +5107,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497236</v>
+        <v>497712</v>
       </c>
       <c r="R33" t="n">
-        <v>7067739</v>
+        <v>7068103</v>
       </c>
       <c r="S33" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5162,7 +5146,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5172,12 +5156,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5209,10 +5193,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123935093</v>
+        <v>123933086</v>
       </c>
       <c r="B34" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5225,39 +5209,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497438</v>
+        <v>497126</v>
       </c>
       <c r="R34" t="n">
-        <v>7067653</v>
+        <v>7067709</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -5289,7 +5268,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5299,7 +5278,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5313,7 +5292,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5328,12 +5307,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5351,10 +5330,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123925387</v>
+        <v>123933142</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>79905</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5367,56 +5346,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497600</v>
+        <v>497133</v>
       </c>
       <c r="R35" t="n">
-        <v>7067872</v>
+        <v>7067678</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5443,14 +5408,19 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5465,6 +5435,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5482,10 +5472,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123927679</v>
+        <v>123934695</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>79773</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5498,56 +5488,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497679</v>
+        <v>497164</v>
       </c>
       <c r="R36" t="n">
-        <v>7068046</v>
+        <v>7067665</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5576,7 +5552,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5586,12 +5562,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5605,7 +5581,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5623,10 +5619,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123927793</v>
+        <v>123931616</v>
       </c>
       <c r="B37" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5639,51 +5635,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497653</v>
+        <v>497562</v>
       </c>
       <c r="R37" t="n">
-        <v>7068061</v>
+        <v>7067959</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5712,7 +5694,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5722,12 +5704,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5741,7 +5718,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5756,12 +5733,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5779,7 +5756,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123934404</v>
+        <v>123925602</v>
       </c>
       <c r="B38" t="n">
         <v>57491</v>
@@ -5815,7 +5792,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5825,17 +5802,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496972</v>
+        <v>497599</v>
       </c>
       <c r="R38" t="n">
-        <v>7067780</v>
+        <v>7067878</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5864,7 +5841,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5874,12 +5851,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5931,10 +5908,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123928831</v>
+        <v>123928438</v>
       </c>
       <c r="B39" t="n">
-        <v>79897</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5943,25 +5920,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5971,13 +5948,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497927</v>
+        <v>497801</v>
       </c>
       <c r="R39" t="n">
-        <v>7068210</v>
+        <v>7068154</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -6006,7 +5983,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6016,7 +5993,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6031,6 +6008,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6048,10 +6045,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123928858</v>
+        <v>123929459</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6064,37 +6061,47 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497900</v>
+        <v>497843</v>
       </c>
       <c r="R40" t="n">
-        <v>7068251</v>
+        <v>7067903</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6123,7 +6130,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6133,12 +6140,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6167,12 +6174,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6190,10 +6197,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123933712</v>
+        <v>123929282</v>
       </c>
       <c r="B41" t="n">
-        <v>56700</v>
+        <v>79870</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6202,51 +6209,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497111</v>
+        <v>497853</v>
       </c>
       <c r="R41" t="n">
-        <v>7067721</v>
+        <v>7067970</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6275,7 +6272,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6285,12 +6282,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6304,7 +6301,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6322,10 +6339,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123933422</v>
+        <v>123934742</v>
       </c>
       <c r="B42" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6338,27 +6355,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6367,13 +6389,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497077</v>
+        <v>497184</v>
       </c>
       <c r="R42" t="n">
-        <v>7067679</v>
+        <v>7067677</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6402,7 +6424,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6412,7 +6434,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6426,27 +6453,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6464,10 +6471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123929067</v>
+        <v>123933774</v>
       </c>
       <c r="B43" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6480,47 +6487,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497903</v>
+        <v>497066</v>
       </c>
       <c r="R43" t="n">
-        <v>7068110</v>
+        <v>7067728</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6549,7 +6546,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6559,12 +6556,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6578,7 +6570,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6593,12 +6585,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6616,7 +6608,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123928438</v>
+        <v>123933962</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -6652,17 +6644,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497801</v>
+        <v>496999</v>
       </c>
       <c r="R44" t="n">
-        <v>7068154</v>
+        <v>7067688</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6691,7 +6683,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6701,7 +6693,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6753,10 +6745,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123928379</v>
+        <v>123927679</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6765,41 +6757,60 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497732</v>
+        <v>497679</v>
       </c>
       <c r="R45" t="n">
-        <v>7068101</v>
+        <v>7068046</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6828,7 +6839,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6838,7 +6849,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6853,26 +6869,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6890,10 +6886,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123934442</v>
+        <v>123934085</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6902,41 +6898,60 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496964</v>
+        <v>496980</v>
       </c>
       <c r="R46" t="n">
-        <v>7067764</v>
+        <v>7067690</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6965,7 +6980,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6975,7 +6990,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6990,26 +7010,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123928741</v>
+        <v>123933859</v>
       </c>
       <c r="B47" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7039,60 +7039,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497907</v>
+        <v>497016</v>
       </c>
       <c r="R47" t="n">
-        <v>7068146</v>
+        <v>7067743</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7121,7 +7102,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7131,12 +7112,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7151,6 +7132,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7168,10 +7169,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123929497</v>
+        <v>123931528</v>
       </c>
       <c r="B48" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7184,16 +7185,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7218,10 +7219,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497846</v>
+        <v>497563</v>
       </c>
       <c r="R48" t="n">
-        <v>7067895</v>
+        <v>7067965</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7253,7 +7254,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7263,12 +7264,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7320,10 +7321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123932552</v>
+        <v>123928741</v>
       </c>
       <c r="B49" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7332,20 +7333,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7353,10 +7354,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7365,13 +7380,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497461</v>
+        <v>497907</v>
       </c>
       <c r="R49" t="n">
-        <v>7067890</v>
+        <v>7068146</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7400,7 +7415,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7410,12 +7425,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7430,26 +7445,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7467,10 +7462,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123932697</v>
+        <v>123925995</v>
       </c>
       <c r="B50" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7483,42 +7478,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497385</v>
+        <v>497628</v>
       </c>
       <c r="R50" t="n">
-        <v>7067784</v>
+        <v>7067895</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7547,7 +7537,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7557,7 +7547,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7576,22 +7566,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7609,7 +7599,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123933774</v>
+        <v>123932608</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -7645,17 +7635,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497066</v>
+        <v>497492</v>
       </c>
       <c r="R51" t="n">
-        <v>7067728</v>
+        <v>7067833</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7684,7 +7674,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7694,7 +7684,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7708,7 +7698,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7746,10 +7736,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123934349</v>
+        <v>123934569</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7762,21 +7752,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7786,13 +7776,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496957</v>
+        <v>497124</v>
       </c>
       <c r="R52" t="n">
-        <v>7067780</v>
+        <v>7067682</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7821,7 +7811,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7831,7 +7821,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7845,27 +7835,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7883,7 +7873,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123927550</v>
+        <v>123925856</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -7923,13 +7913,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497670</v>
+        <v>497652</v>
       </c>
       <c r="R53" t="n">
-        <v>7068014</v>
+        <v>7067886</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7958,7 +7948,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7968,7 +7958,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8020,7 +8010,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123929190</v>
+        <v>123925768</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -8060,13 +8050,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497832</v>
+        <v>497652</v>
       </c>
       <c r="R54" t="n">
-        <v>7067981</v>
+        <v>7067869</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8095,7 +8085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8105,12 +8095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8162,10 +8147,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123933492</v>
+        <v>123935093</v>
       </c>
       <c r="B55" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8178,37 +8163,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497103</v>
+        <v>497438</v>
       </c>
       <c r="R55" t="n">
-        <v>7067696</v>
+        <v>7067653</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8237,7 +8227,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8247,7 +8237,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8261,7 +8251,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -8276,12 +8266,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8299,10 +8289,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123932385</v>
+        <v>123932710</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8315,37 +8305,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497528</v>
+        <v>497376</v>
       </c>
       <c r="R56" t="n">
-        <v>7067930</v>
+        <v>7067768</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8374,7 +8364,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8384,7 +8374,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8436,7 +8426,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123933962</v>
+        <v>123928858</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -8472,17 +8462,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496999</v>
+        <v>497900</v>
       </c>
       <c r="R57" t="n">
-        <v>7067688</v>
+        <v>7068251</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8511,7 +8501,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8521,7 +8511,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8573,10 +8568,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123929267</v>
+        <v>123928514</v>
       </c>
       <c r="B58" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8589,42 +8584,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497833</v>
+        <v>497851</v>
       </c>
       <c r="R58" t="n">
-        <v>7067988</v>
+        <v>7068090</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8653,7 +8643,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8663,12 +8653,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8687,22 +8672,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8720,10 +8705,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123933127</v>
+        <v>123934442</v>
       </c>
       <c r="B59" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8736,42 +8721,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497133</v>
+        <v>496964</v>
       </c>
       <c r="R59" t="n">
-        <v>7067678</v>
+        <v>7067764</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8800,7 +8780,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8810,7 +8790,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8829,22 +8809,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8862,10 +8842,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123934085</v>
+        <v>123934022</v>
       </c>
       <c r="B60" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8874,60 +8854,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496980</v>
+        <v>496970</v>
       </c>
       <c r="R60" t="n">
-        <v>7067690</v>
+        <v>7067716</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8956,7 +8917,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8966,12 +8927,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8986,6 +8947,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -9134,10 +9115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123934695</v>
+        <v>123927793</v>
       </c>
       <c r="B62" t="n">
-        <v>79773</v>
+        <v>91008</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9146,46 +9127,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497164</v>
+        <v>497653</v>
       </c>
       <c r="R62" t="n">
-        <v>7067665</v>
+        <v>7068061</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -9214,7 +9204,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9224,12 +9214,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9248,22 +9238,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9281,10 +9271,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123932608</v>
+        <v>123933422</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9297,34 +9287,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497492</v>
+        <v>497077</v>
       </c>
       <c r="R63" t="n">
-        <v>7067833</v>
+        <v>7067679</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -9356,7 +9351,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9366,7 +9361,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9395,12 +9390,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9560,7 +9555,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123925995</v>
+        <v>123928803</v>
       </c>
       <c r="B65" t="n">
         <v>78788</v>
@@ -9600,13 +9595,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497628</v>
+        <v>497932</v>
       </c>
       <c r="R65" t="n">
-        <v>7067895</v>
+        <v>7068202</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9635,7 +9630,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9645,7 +9640,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9697,7 +9697,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948048</v>
+        <v>123948074</v>
       </c>
       <c r="B66" t="n">
         <v>57491</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497417</v>
+        <v>497809</v>
       </c>
       <c r="R66" t="n">
-        <v>7067613</v>
+        <v>7068221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948065</v>
+        <v>123948076</v>
       </c>
       <c r="B67" t="n">
         <v>57491</v>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497547</v>
+        <v>497599</v>
       </c>
       <c r="R67" t="n">
-        <v>7068008</v>
+        <v>7068342</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9911,10 +9911,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948058</v>
+        <v>123948037</v>
       </c>
       <c r="B68" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9927,21 +9927,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497156</v>
+        <v>497443</v>
       </c>
       <c r="R68" t="n">
-        <v>7067976</v>
+        <v>7067840</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9987,11 +9987,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10018,7 +10013,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948041</v>
+        <v>123948073</v>
       </c>
       <c r="B69" t="n">
         <v>57491</v>
@@ -10058,10 +10053,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497578</v>
+        <v>497810</v>
       </c>
       <c r="R69" t="n">
-        <v>7067475</v>
+        <v>7068216</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -10098,7 +10093,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10125,7 +10120,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948053</v>
+        <v>123948066</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -10165,10 +10160,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497052</v>
+        <v>497568</v>
       </c>
       <c r="R70" t="n">
-        <v>7067797</v>
+        <v>7067974</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10205,7 +10200,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10339,10 +10334,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948084</v>
+        <v>123948048</v>
       </c>
       <c r="B72" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10355,21 +10350,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10379,10 +10374,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497101</v>
+        <v>497417</v>
       </c>
       <c r="R72" t="n">
-        <v>7067728</v>
+        <v>7067613</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10415,6 +10410,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10655,7 +10655,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948085</v>
+        <v>123948083</v>
       </c>
       <c r="B75" t="n">
         <v>91008</v>
@@ -10695,10 +10695,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497243</v>
+        <v>497012</v>
       </c>
       <c r="R75" t="n">
-        <v>7067786</v>
+        <v>7067783</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10757,7 +10757,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948049</v>
+        <v>123948052</v>
       </c>
       <c r="B76" t="n">
         <v>57491</v>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496958</v>
+        <v>496977</v>
       </c>
       <c r="R76" t="n">
-        <v>7067783</v>
+        <v>7067794</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10864,7 +10864,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948060</v>
+        <v>123948058</v>
       </c>
       <c r="B77" t="n">
         <v>57491</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497140</v>
+        <v>497156</v>
       </c>
       <c r="R77" t="n">
-        <v>7067713</v>
+        <v>7067976</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948051</v>
+        <v>123948071</v>
       </c>
       <c r="B78" t="n">
         <v>57491</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496962</v>
+        <v>497830</v>
       </c>
       <c r="R78" t="n">
-        <v>7067810</v>
+        <v>7068267</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -11078,7 +11078,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948055</v>
+        <v>123948062</v>
       </c>
       <c r="B79" t="n">
         <v>57491</v>
@@ -11118,10 +11118,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497062</v>
+        <v>497431</v>
       </c>
       <c r="R79" t="n">
-        <v>7068109</v>
+        <v>7067834</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11185,7 +11185,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948050</v>
+        <v>123948053</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496963</v>
+        <v>497052</v>
       </c>
       <c r="R80" t="n">
-        <v>7067823</v>
+        <v>7067797</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11292,10 +11292,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948063</v>
+        <v>123948082</v>
       </c>
       <c r="B81" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11304,25 +11304,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497448</v>
+        <v>497300</v>
       </c>
       <c r="R81" t="n">
-        <v>7067857</v>
+        <v>7068117</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11368,11 +11368,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11399,7 +11394,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948059</v>
+        <v>123948063</v>
       </c>
       <c r="B82" t="n">
         <v>57491</v>
@@ -11439,10 +11434,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497338</v>
+        <v>497448</v>
       </c>
       <c r="R82" t="n">
-        <v>7068065</v>
+        <v>7067857</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11479,7 +11474,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11506,10 +11501,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948081</v>
+        <v>123948084</v>
       </c>
       <c r="B83" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11518,25 +11513,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11546,10 +11541,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497267</v>
+        <v>497101</v>
       </c>
       <c r="R83" t="n">
-        <v>7068098</v>
+        <v>7067728</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11608,7 +11603,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948078</v>
+        <v>123948070</v>
       </c>
       <c r="B84" t="n">
         <v>57491</v>
@@ -11648,10 +11643,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497569</v>
+        <v>497876</v>
       </c>
       <c r="R84" t="n">
-        <v>7068352</v>
+        <v>7068110</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11715,7 +11710,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948079</v>
+        <v>123948041</v>
       </c>
       <c r="B85" t="n">
         <v>57491</v>
@@ -11755,10 +11750,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497614</v>
+        <v>497578</v>
       </c>
       <c r="R85" t="n">
-        <v>7067898</v>
+        <v>7067475</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11795,7 +11790,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11822,7 +11817,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948061</v>
+        <v>123948057</v>
       </c>
       <c r="B86" t="n">
         <v>57491</v>
@@ -11862,10 +11857,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497152</v>
+        <v>497142</v>
       </c>
       <c r="R86" t="n">
-        <v>7067720</v>
+        <v>7068071</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11929,7 +11924,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948057</v>
+        <v>123948067</v>
       </c>
       <c r="B87" t="n">
         <v>57491</v>
@@ -11969,10 +11964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497142</v>
+        <v>497567</v>
       </c>
       <c r="R87" t="n">
-        <v>7068071</v>
+        <v>7067939</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12009,7 +12004,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12036,7 +12031,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948064</v>
+        <v>123948059</v>
       </c>
       <c r="B88" t="n">
         <v>57491</v>
@@ -12076,10 +12071,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497471</v>
+        <v>497338</v>
       </c>
       <c r="R88" t="n">
-        <v>7067944</v>
+        <v>7068065</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12116,7 +12111,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12143,7 +12138,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948062</v>
+        <v>123948055</v>
       </c>
       <c r="B89" t="n">
         <v>57491</v>
@@ -12183,10 +12178,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497431</v>
+        <v>497062</v>
       </c>
       <c r="R89" t="n">
-        <v>7067834</v>
+        <v>7068109</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12250,7 +12245,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948054</v>
+        <v>123948056</v>
       </c>
       <c r="B90" t="n">
         <v>57491</v>
@@ -12290,10 +12285,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497062</v>
+        <v>497093</v>
       </c>
       <c r="R90" t="n">
-        <v>7068118</v>
+        <v>7068094</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12357,7 +12352,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948074</v>
+        <v>123948054</v>
       </c>
       <c r="B91" t="n">
         <v>57491</v>
@@ -12397,10 +12392,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497809</v>
+        <v>497062</v>
       </c>
       <c r="R91" t="n">
-        <v>7068221</v>
+        <v>7068118</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12464,7 +12459,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948056</v>
+        <v>123948049</v>
       </c>
       <c r="B92" t="n">
         <v>57491</v>
@@ -12504,10 +12499,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497093</v>
+        <v>496958</v>
       </c>
       <c r="R92" t="n">
-        <v>7068094</v>
+        <v>7067783</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12544,7 +12539,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12571,7 +12566,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948066</v>
+        <v>123948051</v>
       </c>
       <c r="B93" t="n">
         <v>57491</v>
@@ -12611,10 +12606,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497568</v>
+        <v>496962</v>
       </c>
       <c r="R93" t="n">
-        <v>7067974</v>
+        <v>7067810</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12651,7 +12646,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12678,10 +12673,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948076</v>
+        <v>123948081</v>
       </c>
       <c r="B94" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12690,25 +12685,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12718,10 +12713,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497599</v>
+        <v>497267</v>
       </c>
       <c r="R94" t="n">
-        <v>7068342</v>
+        <v>7068098</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12754,11 +12749,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12785,10 +12775,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123948068</v>
+        <v>123948085</v>
       </c>
       <c r="B95" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12801,21 +12791,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12825,10 +12815,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497549</v>
+        <v>497243</v>
       </c>
       <c r="R95" t="n">
-        <v>7067939</v>
+        <v>7067786</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12861,11 +12851,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12892,7 +12877,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123948070</v>
+        <v>123948079</v>
       </c>
       <c r="B96" t="n">
         <v>57491</v>
@@ -12932,10 +12917,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497876</v>
+        <v>497614</v>
       </c>
       <c r="R96" t="n">
-        <v>7068110</v>
+        <v>7067898</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12999,7 +12984,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123948067</v>
+        <v>123948060</v>
       </c>
       <c r="B97" t="n">
         <v>57491</v>
@@ -13039,10 +13024,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497567</v>
+        <v>497140</v>
       </c>
       <c r="R97" t="n">
-        <v>7067939</v>
+        <v>7067713</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13079,7 +13064,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13106,7 +13091,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123948071</v>
+        <v>123948065</v>
       </c>
       <c r="B98" t="n">
         <v>57491</v>
@@ -13146,10 +13131,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497830</v>
+        <v>497547</v>
       </c>
       <c r="R98" t="n">
-        <v>7068267</v>
+        <v>7068008</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13186,7 +13171,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13213,7 +13198,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123948052</v>
+        <v>123948061</v>
       </c>
       <c r="B99" t="n">
         <v>57491</v>
@@ -13253,10 +13238,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496977</v>
+        <v>497152</v>
       </c>
       <c r="R99" t="n">
-        <v>7067794</v>
+        <v>7067720</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13320,10 +13305,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123948082</v>
+        <v>123948068</v>
       </c>
       <c r="B100" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13332,25 +13317,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13360,10 +13345,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497300</v>
+        <v>497549</v>
       </c>
       <c r="R100" t="n">
-        <v>7068117</v>
+        <v>7067939</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13396,6 +13381,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13422,7 +13412,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948073</v>
+        <v>123948064</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13462,10 +13452,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497810</v>
+        <v>497471</v>
       </c>
       <c r="R101" t="n">
-        <v>7068216</v>
+        <v>7067944</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13529,10 +13519,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123948037</v>
+        <v>123948050</v>
       </c>
       <c r="B102" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13545,21 +13535,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13569,10 +13559,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497443</v>
+        <v>496963</v>
       </c>
       <c r="R102" t="n">
-        <v>7067840</v>
+        <v>7067823</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13605,6 +13595,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13631,10 +13626,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123948083</v>
+        <v>123948078</v>
       </c>
       <c r="B103" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13647,21 +13642,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13671,10 +13666,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497012</v>
+        <v>497569</v>
       </c>
       <c r="R103" t="n">
-        <v>7067783</v>
+        <v>7068352</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13707,6 +13702,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935971</v>
+        <v>123935511</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,34 +13886,44 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497477</v>
+        <v>497429</v>
       </c>
       <c r="R105" t="n">
-        <v>7067373</v>
+        <v>7067368</v>
       </c>
       <c r="S105" t="n">
         <v>9</v>
@@ -13945,7 +13955,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13955,7 +13965,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13984,12 +13994,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14007,7 +14017,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935892</v>
+        <v>123935623</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -14047,10 +14057,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497488</v>
+        <v>497400</v>
       </c>
       <c r="R106" t="n">
-        <v>7067338</v>
+        <v>7067320</v>
       </c>
       <c r="S106" t="n">
         <v>8</v>
@@ -14082,7 +14092,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14092,7 +14102,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14144,7 +14154,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123936388</v>
+        <v>123935469</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -14184,13 +14194,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497347</v>
+        <v>497429</v>
       </c>
       <c r="R107" t="n">
-        <v>7067031</v>
+        <v>7067378</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14219,7 +14229,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14229,7 +14239,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14281,7 +14291,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123935469</v>
+        <v>123935971</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -14321,13 +14331,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497429</v>
+        <v>497477</v>
       </c>
       <c r="R108" t="n">
-        <v>7067378</v>
+        <v>7067373</v>
       </c>
       <c r="S108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14356,7 +14366,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14366,7 +14376,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14418,10 +14428,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123936336</v>
+        <v>123936388</v>
       </c>
       <c r="B109" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14434,44 +14444,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497296</v>
+        <v>497347</v>
       </c>
       <c r="R109" t="n">
-        <v>7067024</v>
+        <v>7067031</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14513,12 +14513,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14547,12 +14542,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14570,10 +14565,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935511</v>
+        <v>123935892</v>
       </c>
       <c r="B110" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14586,47 +14581,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497429</v>
+        <v>497488</v>
       </c>
       <c r="R110" t="n">
-        <v>7067368</v>
+        <v>7067338</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14655,7 +14640,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14665,7 +14650,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14694,12 +14679,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14717,10 +14702,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935662</v>
+        <v>123936336</v>
       </c>
       <c r="B111" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14733,37 +14718,47 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497407</v>
+        <v>497296</v>
       </c>
       <c r="R111" t="n">
-        <v>7067289</v>
+        <v>7067024</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14792,7 +14787,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14802,7 +14797,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14831,12 +14831,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14854,7 +14854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123935623</v>
+        <v>123935662</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -14894,13 +14894,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497400</v>
+        <v>497407</v>
       </c>
       <c r="R112" t="n">
-        <v>7067320</v>
+        <v>7067289</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14991,7 +14991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948045</v>
+        <v>123948040</v>
       </c>
       <c r="B113" t="n">
         <v>57491</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497439</v>
+        <v>497269</v>
       </c>
       <c r="R113" t="n">
-        <v>7067336</v>
+        <v>7067065</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948039</v>
+        <v>123948042</v>
       </c>
       <c r="B114" t="n">
         <v>57491</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497241</v>
+        <v>497448</v>
       </c>
       <c r="R114" t="n">
-        <v>7067063</v>
+        <v>7067435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,7 +15205,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948047</v>
+        <v>123948038</v>
       </c>
       <c r="B115" t="n">
         <v>57491</v>
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497422</v>
+        <v>497227</v>
       </c>
       <c r="R115" t="n">
-        <v>7067360</v>
+        <v>7067047</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15312,10 +15312,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948040</v>
+        <v>123948080</v>
       </c>
       <c r="B116" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15328,16 +15328,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497269</v>
+        <v>497370</v>
       </c>
       <c r="R116" t="n">
-        <v>7067065</v>
+        <v>7067042</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948042</v>
+        <v>123948045</v>
       </c>
       <c r="B117" t="n">
         <v>57491</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497448</v>
+        <v>497439</v>
       </c>
       <c r="R117" t="n">
-        <v>7067435</v>
+        <v>7067336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,10 +15526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948080</v>
+        <v>123948039</v>
       </c>
       <c r="B118" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497370</v>
+        <v>497241</v>
       </c>
       <c r="R118" t="n">
-        <v>7067042</v>
+        <v>7067063</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15633,7 +15633,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948038</v>
+        <v>123948047</v>
       </c>
       <c r="B119" t="n">
         <v>57491</v>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497227</v>
+        <v>497422</v>
       </c>
       <c r="R119" t="n">
-        <v>7067047</v>
+        <v>7067360</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -2658,10 +2658,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123929067</v>
+        <v>123934908</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2674,47 +2674,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497903</v>
+        <v>497399</v>
       </c>
       <c r="R16" t="n">
-        <v>7068110</v>
+        <v>7067620</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2743,7 +2738,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2753,12 +2748,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2787,12 +2777,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123934908</v>
+        <v>123925387</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>57861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2822,46 +2812,60 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497399</v>
+        <v>497600</v>
       </c>
       <c r="R17" t="n">
-        <v>7067620</v>
+        <v>7067872</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2888,19 +2892,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:03</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2915,26 +2914,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2952,10 +2931,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123925387</v>
+        <v>123929067</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2964,20 +2943,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2985,19 +2964,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3011,13 +2981,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497600</v>
+        <v>497903</v>
       </c>
       <c r="R18" t="n">
-        <v>7067872</v>
+        <v>7068110</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3044,14 +3014,24 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3066,6 +3046,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123933127</v>
+        <v>123933712</v>
       </c>
       <c r="B19" t="n">
-        <v>79870</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,31 +3095,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3128,13 +3133,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497133</v>
+        <v>497111</v>
       </c>
       <c r="R19" t="n">
-        <v>7067678</v>
+        <v>7067721</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3163,7 +3168,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3173,7 +3178,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3187,27 +3197,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3225,10 +3215,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123929267</v>
+        <v>123933127</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3241,21 +3231,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3266,17 +3256,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497833</v>
+        <v>497133</v>
       </c>
       <c r="R20" t="n">
-        <v>7067988</v>
+        <v>7067678</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3305,7 +3295,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3315,12 +3305,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3372,10 +3357,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123933712</v>
+        <v>123929267</v>
       </c>
       <c r="B21" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3384,51 +3369,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497111</v>
+        <v>497833</v>
       </c>
       <c r="R21" t="n">
-        <v>7067721</v>
+        <v>7067988</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3457,7 +3437,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3467,12 +3447,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3486,7 +3466,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -5619,10 +5619,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123931616</v>
+        <v>123925602</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5635,37 +5635,47 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497562</v>
+        <v>497599</v>
       </c>
       <c r="R37" t="n">
-        <v>7067959</v>
+        <v>7067878</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5694,7 +5704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5704,7 +5714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5733,12 +5748,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5756,10 +5771,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123925602</v>
+        <v>123928438</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5772,47 +5787,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497599</v>
+        <v>497801</v>
       </c>
       <c r="R38" t="n">
-        <v>7067878</v>
+        <v>7068154</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5841,7 +5846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5851,12 +5856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123928438</v>
+        <v>123931616</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -5948,13 +5948,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497801</v>
+        <v>497562</v>
       </c>
       <c r="R39" t="n">
-        <v>7068154</v>
+        <v>7067959</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -9115,10 +9115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123927793</v>
+        <v>123929370</v>
       </c>
       <c r="B62" t="n">
-        <v>91008</v>
+        <v>79904</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9127,40 +9127,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -9169,10 +9160,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497653</v>
+        <v>497852</v>
       </c>
       <c r="R62" t="n">
-        <v>7068061</v>
+        <v>7067984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9204,7 +9195,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9214,12 +9205,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9233,27 +9219,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9271,10 +9257,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123933422</v>
+        <v>123928803</v>
       </c>
       <c r="B63" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9287,39 +9273,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497077</v>
+        <v>497932</v>
       </c>
       <c r="R63" t="n">
-        <v>7067679</v>
+        <v>7068202</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -9351,7 +9332,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9361,7 +9342,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9390,12 +9376,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9413,10 +9399,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123929370</v>
+        <v>123927793</v>
       </c>
       <c r="B64" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9425,31 +9411,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -9458,10 +9453,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497852</v>
+        <v>497653</v>
       </c>
       <c r="R64" t="n">
-        <v>7067984</v>
+        <v>7068061</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9493,7 +9488,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9503,7 +9498,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9517,27 +9517,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9555,10 +9555,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123928803</v>
+        <v>123933422</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9571,34 +9571,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497932</v>
+        <v>497077</v>
       </c>
       <c r="R65" t="n">
-        <v>7068202</v>
+        <v>7067679</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -9630,7 +9635,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9640,12 +9645,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -10548,10 +10548,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948075</v>
+        <v>123948083</v>
       </c>
       <c r="B74" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10564,21 +10564,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10588,10 +10588,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497629</v>
+        <v>497012</v>
       </c>
       <c r="R74" t="n">
-        <v>7068330</v>
+        <v>7067783</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10624,11 +10624,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10655,10 +10650,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948083</v>
+        <v>123948075</v>
       </c>
       <c r="B75" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10671,21 +10666,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10695,10 +10690,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497012</v>
+        <v>497629</v>
       </c>
       <c r="R75" t="n">
-        <v>7067783</v>
+        <v>7068330</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10731,6 +10726,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -13412,7 +13412,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948064</v>
+        <v>123948050</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497471</v>
+        <v>496963</v>
       </c>
       <c r="R101" t="n">
-        <v>7067944</v>
+        <v>7067823</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13519,7 +13519,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123948050</v>
+        <v>123948078</v>
       </c>
       <c r="B102" t="n">
         <v>57491</v>
@@ -13559,10 +13559,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496963</v>
+        <v>497569</v>
       </c>
       <c r="R102" t="n">
-        <v>7067823</v>
+        <v>7068352</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13626,7 +13626,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123948078</v>
+        <v>123948064</v>
       </c>
       <c r="B103" t="n">
         <v>57491</v>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497569</v>
+        <v>497471</v>
       </c>
       <c r="R103" t="n">
-        <v>7068352</v>
+        <v>7067944</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123933650</v>
+        <v>123932385</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497112</v>
+        <v>497528</v>
       </c>
       <c r="R2" t="n">
-        <v>7067726</v>
+        <v>7067930</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -959,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123931338</v>
+        <v>123925602</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -995,7 +990,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,10 +1004,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497552</v>
+        <v>497599</v>
       </c>
       <c r="R4" t="n">
-        <v>7067881</v>
+        <v>7067878</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1044,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1049,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1111,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123926766</v>
+        <v>123931433</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,27 +1122,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497661</v>
+        <v>497554</v>
       </c>
       <c r="R5" t="n">
-        <v>7067931</v>
+        <v>7067886</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123929190</v>
+        <v>123928327</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1270,41 +1270,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497832</v>
+        <v>497712</v>
       </c>
       <c r="R6" t="n">
-        <v>7067981</v>
+        <v>7068103</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,7 +1343,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1343,12 +1353,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1363,26 +1373,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1537,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123928379</v>
+        <v>123929459</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1553,34 +1543,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497732</v>
+        <v>497843</v>
       </c>
       <c r="R8" t="n">
-        <v>7068101</v>
+        <v>7067903</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1622,7 +1622,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1651,12 +1656,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123929301</v>
+        <v>123932552</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1690,27 +1695,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497846</v>
+        <v>497461</v>
       </c>
       <c r="R9" t="n">
-        <v>7067985</v>
+        <v>7067890</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1754,7 +1759,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,12 +1769,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1798,12 +1803,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,7 +1826,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123928831</v>
+        <v>123928574</v>
       </c>
       <c r="B10" t="n">
         <v>79897</v>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497927</v>
+        <v>497848</v>
       </c>
       <c r="R10" t="n">
-        <v>7068210</v>
+        <v>7068101</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1896,7 +1901,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1906,7 +1911,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1938,7 +1943,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123927991</v>
+        <v>123931338</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1974,7 +1979,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1988,13 +1993,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497659</v>
+        <v>497552</v>
       </c>
       <c r="R11" t="n">
-        <v>7068053</v>
+        <v>7067881</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,12 +2038,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2052,7 +2057,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2067,12 +2072,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2090,10 +2095,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123932969</v>
+        <v>123927793</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2106,47 +2111,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497236</v>
+        <v>497653</v>
       </c>
       <c r="R12" t="n">
-        <v>7067739</v>
+        <v>7068061</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2175,7 +2184,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2185,12 +2194,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2204,7 +2213,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2222,10 +2251,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123934404</v>
+        <v>123929190</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2238,47 +2267,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496972</v>
+        <v>497832</v>
       </c>
       <c r="R13" t="n">
-        <v>7067780</v>
+        <v>7067981</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2326,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,12 +2336,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2351,12 +2370,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2374,10 +2393,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123932552</v>
+        <v>123929267</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2390,27 +2409,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2419,13 +2438,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497461</v>
+        <v>497833</v>
       </c>
       <c r="R14" t="n">
-        <v>7067890</v>
+        <v>7067988</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2454,7 +2473,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2464,12 +2483,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2488,22 +2507,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2521,10 +2540,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123934255</v>
+        <v>123935093</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2537,37 +2556,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496932</v>
+        <v>497438</v>
       </c>
       <c r="R15" t="n">
-        <v>7067736</v>
+        <v>7067653</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,7 +2620,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2606,7 +2630,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2635,12 +2659,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2658,10 +2682,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123934908</v>
+        <v>123929497</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2674,39 +2698,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497399</v>
+        <v>497846</v>
       </c>
       <c r="R16" t="n">
-        <v>7067620</v>
+        <v>7067895</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2738,7 +2767,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2748,7 +2777,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2777,12 +2811,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2800,10 +2834,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123925387</v>
+        <v>123932969</v>
       </c>
       <c r="B17" t="n">
-        <v>57861</v>
+        <v>56692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2812,20 +2846,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2833,19 +2867,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2855,17 +2880,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497600</v>
+        <v>497236</v>
       </c>
       <c r="R17" t="n">
-        <v>7067872</v>
+        <v>7067739</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2892,14 +2917,24 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2931,10 +2966,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123929067</v>
+        <v>123927679</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2943,20 +2978,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2964,10 +2999,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2981,13 +3025,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497903</v>
+        <v>497679</v>
       </c>
       <c r="R18" t="n">
-        <v>7068110</v>
+        <v>7068046</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3016,7 +3060,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3026,12 +3070,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3046,26 +3090,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3083,10 +3107,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123933712</v>
+        <v>123932201</v>
       </c>
       <c r="B19" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,51 +3119,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497111</v>
+        <v>497553</v>
       </c>
       <c r="R19" t="n">
-        <v>7067721</v>
+        <v>7068083</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3168,7 +3196,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3178,12 +3206,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3194,11 +3222,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3215,10 +3238,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123933127</v>
+        <v>123928831</v>
       </c>
       <c r="B20" t="n">
-        <v>79870</v>
+        <v>79897</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3227,46 +3250,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497133</v>
+        <v>497927</v>
       </c>
       <c r="R20" t="n">
-        <v>7067678</v>
+        <v>7068210</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3295,7 +3313,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3305,7 +3323,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3320,26 +3338,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3357,10 +3355,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123929267</v>
+        <v>123934404</v>
       </c>
       <c r="B21" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3373,42 +3371,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497833</v>
+        <v>496972</v>
       </c>
       <c r="R21" t="n">
-        <v>7067988</v>
+        <v>7067780</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3437,7 +3440,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3447,12 +3450,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3471,22 +3474,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3504,10 +3507,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123931684</v>
+        <v>123929370</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>79904</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3516,36 +3519,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3554,13 +3552,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497576</v>
+        <v>497852</v>
       </c>
       <c r="R22" t="n">
-        <v>7067995</v>
+        <v>7067984</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3589,7 +3587,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3599,12 +3597,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3623,22 +3616,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3656,10 +3649,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123929497</v>
+        <v>123934022</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3672,47 +3665,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497846</v>
+        <v>496970</v>
       </c>
       <c r="R23" t="n">
-        <v>7067895</v>
+        <v>7067716</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3741,7 +3724,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3751,12 +3734,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3785,12 +3768,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3808,10 +3791,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123929700</v>
+        <v>123925768</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3824,47 +3807,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497829</v>
+        <v>497652</v>
       </c>
       <c r="R24" t="n">
-        <v>7067835</v>
+        <v>7067869</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3893,7 +3866,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3903,12 +3876,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3922,7 +3890,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3937,12 +3905,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3960,10 +3928,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931433</v>
+        <v>123926766</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3976,32 +3944,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4010,13 +3973,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497554</v>
+        <v>497661</v>
       </c>
       <c r="R25" t="n">
-        <v>7067886</v>
+        <v>7067931</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -4045,7 +4008,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4055,12 +4018,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4089,12 +4052,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4112,7 +4075,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123926190</v>
+        <v>123928803</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -4152,13 +4115,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497654</v>
+        <v>497932</v>
       </c>
       <c r="R26" t="n">
-        <v>7067926</v>
+        <v>7068202</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4187,7 +4150,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4197,7 +4160,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4249,10 +4217,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123932385</v>
+        <v>123933712</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4261,41 +4229,51 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497528</v>
+        <v>497111</v>
       </c>
       <c r="R27" t="n">
-        <v>7067930</v>
+        <v>7067721</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4324,7 +4302,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4334,7 +4312,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4348,27 +4331,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4386,10 +4349,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123932682</v>
+        <v>123925856</v>
       </c>
       <c r="B28" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4402,42 +4365,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497368</v>
+        <v>497652</v>
       </c>
       <c r="R28" t="n">
-        <v>7067763</v>
+        <v>7067886</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4466,7 +4424,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4476,7 +4434,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4495,22 +4453,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4528,7 +4486,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123927550</v>
+        <v>123933774</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -4564,14 +4522,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497670</v>
+        <v>497066</v>
       </c>
       <c r="R29" t="n">
-        <v>7068014</v>
+        <v>7067728</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -4603,7 +4561,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4613,7 +4571,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4627,7 +4585,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4665,7 +4623,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123933492</v>
+        <v>123927550</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -4701,17 +4659,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497103</v>
+        <v>497670</v>
       </c>
       <c r="R30" t="n">
-        <v>7067696</v>
+        <v>7068014</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4740,7 +4698,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4750,7 +4708,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4802,10 +4760,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123928574</v>
+        <v>123929700</v>
       </c>
       <c r="B31" t="n">
-        <v>79897</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4814,38 +4772,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497848</v>
+        <v>497829</v>
       </c>
       <c r="R31" t="n">
-        <v>7068101</v>
+        <v>7067835</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4877,7 +4845,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4887,7 +4855,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4901,7 +4874,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4919,10 +4912,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123935202</v>
+        <v>123929067</v>
       </c>
       <c r="B32" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4935,27 +4928,32 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4964,13 +4962,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497524</v>
+        <v>497903</v>
       </c>
       <c r="R32" t="n">
-        <v>7067827</v>
+        <v>7068110</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4999,7 +4997,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5009,7 +5007,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5061,10 +5064,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123928327</v>
+        <v>123926190</v>
       </c>
       <c r="B33" t="n">
-        <v>56703</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5073,51 +5076,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497712</v>
+        <v>497654</v>
       </c>
       <c r="R33" t="n">
-        <v>7068103</v>
+        <v>7067926</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5146,7 +5139,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5156,12 +5149,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5176,6 +5164,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5193,7 +5201,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123933086</v>
+        <v>123928379</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -5229,17 +5237,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497126</v>
+        <v>497732</v>
       </c>
       <c r="R34" t="n">
-        <v>7067709</v>
+        <v>7068101</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5268,7 +5276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5278,7 +5286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5330,10 +5338,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123933142</v>
+        <v>123933962</v>
       </c>
       <c r="B35" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5342,43 +5350,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497133</v>
+        <v>496999</v>
       </c>
       <c r="R35" t="n">
-        <v>7067678</v>
+        <v>7067688</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
@@ -5410,7 +5413,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5420,7 +5423,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5439,22 +5442,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5472,10 +5475,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123934695</v>
+        <v>123933650</v>
       </c>
       <c r="B36" t="n">
-        <v>79773</v>
+        <v>91008</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5484,31 +5487,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5517,10 +5520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497164</v>
+        <v>497112</v>
       </c>
       <c r="R36" t="n">
-        <v>7067665</v>
+        <v>7067726</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5552,7 +5555,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5562,12 +5565,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5586,22 +5584,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5619,10 +5617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123925602</v>
+        <v>123931528</v>
       </c>
       <c r="B37" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5635,16 +5633,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5669,13 +5667,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497599</v>
+        <v>497563</v>
       </c>
       <c r="R37" t="n">
-        <v>7067878</v>
+        <v>7067965</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5704,7 +5702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5714,12 +5712,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5771,10 +5769,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123928438</v>
+        <v>123934742</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5787,37 +5785,47 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497801</v>
+        <v>497184</v>
       </c>
       <c r="R38" t="n">
-        <v>7068154</v>
+        <v>7067677</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5846,7 +5854,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5856,7 +5864,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5870,27 +5883,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5908,7 +5901,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123931616</v>
+        <v>123932608</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -5948,13 +5941,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497562</v>
+        <v>497492</v>
       </c>
       <c r="R39" t="n">
-        <v>7067959</v>
+        <v>7067833</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5983,7 +5976,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5993,7 +5986,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6045,10 +6038,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123929459</v>
+        <v>123929282</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>79870</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6061,47 +6054,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497843</v>
+        <v>497853</v>
       </c>
       <c r="R40" t="n">
-        <v>7067903</v>
+        <v>7067970</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6130,7 +6113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6140,12 +6123,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6164,22 +6147,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6197,10 +6180,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123929282</v>
+        <v>123929301</v>
       </c>
       <c r="B41" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6213,37 +6196,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497853</v>
+        <v>497846</v>
       </c>
       <c r="R41" t="n">
-        <v>7067970</v>
+        <v>7067985</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6272,7 +6260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6282,12 +6270,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6306,22 +6294,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6339,10 +6327,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123934742</v>
+        <v>123932710</v>
       </c>
       <c r="B42" t="n">
-        <v>56692</v>
+        <v>79870</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6355,47 +6343,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497184</v>
+        <v>497376</v>
       </c>
       <c r="R42" t="n">
-        <v>7067677</v>
+        <v>7067768</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6424,7 +6402,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6434,12 +6412,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6453,7 +6426,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6471,10 +6464,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123933774</v>
+        <v>123925387</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6483,41 +6476,60 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497066</v>
+        <v>497600</v>
       </c>
       <c r="R43" t="n">
-        <v>7067728</v>
+        <v>7067872</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6544,19 +6556,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:57</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6570,27 +6577,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6608,10 +6595,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123933962</v>
+        <v>123928741</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6620,41 +6607,60 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496999</v>
+        <v>497907</v>
       </c>
       <c r="R44" t="n">
-        <v>7067688</v>
+        <v>7068146</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6683,7 +6689,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6693,7 +6699,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6708,26 +6719,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6745,10 +6736,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123927679</v>
+        <v>123933492</v>
       </c>
       <c r="B45" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6757,60 +6748,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497679</v>
+        <v>497103</v>
       </c>
       <c r="R45" t="n">
-        <v>7068046</v>
+        <v>7067696</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6839,7 +6811,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6849,12 +6821,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6869,6 +6836,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6886,10 +6873,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123934085</v>
+        <v>123927991</v>
       </c>
       <c r="B46" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6898,20 +6885,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6919,19 +6906,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6941,17 +6919,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496980</v>
+        <v>497659</v>
       </c>
       <c r="R46" t="n">
-        <v>7067690</v>
+        <v>7068053</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6980,7 +6958,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6990,12 +6968,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7009,7 +6987,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7027,7 +7025,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123933859</v>
+        <v>123934255</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -7067,13 +7065,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497016</v>
+        <v>496932</v>
       </c>
       <c r="R47" t="n">
-        <v>7067743</v>
+        <v>7067736</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7102,7 +7100,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7112,12 +7110,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7131,7 +7124,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7169,10 +7162,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123931528</v>
+        <v>123934569</v>
       </c>
       <c r="B48" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7185,44 +7178,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497563</v>
+        <v>497124</v>
       </c>
       <c r="R48" t="n">
-        <v>7067965</v>
+        <v>7067682</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7254,7 +7237,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7264,12 +7247,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7283,27 +7261,27 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7321,10 +7299,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123928741</v>
+        <v>123931684</v>
       </c>
       <c r="B49" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7333,20 +7311,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7354,19 +7332,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7380,13 +7349,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497907</v>
+        <v>497576</v>
       </c>
       <c r="R49" t="n">
-        <v>7068146</v>
+        <v>7067995</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7415,7 +7384,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7425,12 +7394,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7445,6 +7414,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7462,7 +7451,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123925995</v>
+        <v>123933086</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -7498,17 +7487,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497628</v>
+        <v>497126</v>
       </c>
       <c r="R50" t="n">
-        <v>7067895</v>
+        <v>7067709</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7537,7 +7526,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7547,7 +7536,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7599,7 +7588,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123932608</v>
+        <v>123925995</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -7639,13 +7628,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497492</v>
+        <v>497628</v>
       </c>
       <c r="R51" t="n">
-        <v>7067833</v>
+        <v>7067895</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7674,7 +7663,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7684,7 +7673,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7736,10 +7725,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123934569</v>
+        <v>123931616</v>
       </c>
       <c r="B52" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7752,37 +7741,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497124</v>
+        <v>497562</v>
       </c>
       <c r="R52" t="n">
-        <v>7067682</v>
+        <v>7067959</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7811,7 +7800,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7821,7 +7810,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7835,27 +7824,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7873,10 +7862,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123925856</v>
+        <v>123935202</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7889,37 +7878,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497652</v>
+        <v>497524</v>
       </c>
       <c r="R53" t="n">
-        <v>7067886</v>
+        <v>7067827</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7948,7 +7942,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7958,7 +7952,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7987,12 +7981,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8010,10 +8004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123925768</v>
+        <v>123934085</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8022,38 +8016,57 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497652</v>
+        <v>496980</v>
       </c>
       <c r="R54" t="n">
-        <v>7067869</v>
+        <v>7067690</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -8085,7 +8098,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8095,7 +8108,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8110,26 +8128,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8147,10 +8145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123935093</v>
+        <v>123933142</v>
       </c>
       <c r="B55" t="n">
-        <v>90986</v>
+        <v>79905</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8159,31 +8157,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8192,13 +8190,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497438</v>
+        <v>497133</v>
       </c>
       <c r="R55" t="n">
-        <v>7067653</v>
+        <v>7067678</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8227,7 +8225,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8237,7 +8235,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8251,27 +8249,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8289,10 +8287,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123932710</v>
+        <v>123928438</v>
       </c>
       <c r="B56" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8305,34 +8303,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497376</v>
+        <v>497801</v>
       </c>
       <c r="R56" t="n">
-        <v>7067768</v>
+        <v>7068154</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -8364,7 +8362,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8374,7 +8372,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8426,10 +8424,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123928858</v>
+        <v>123934695</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8438,38 +8436,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497900</v>
+        <v>497164</v>
       </c>
       <c r="R57" t="n">
-        <v>7068251</v>
+        <v>7067665</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -8501,7 +8504,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8511,12 +8514,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8530,27 +8533,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123928514</v>
+        <v>123928858</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -8608,13 +8611,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497851</v>
+        <v>497900</v>
       </c>
       <c r="R58" t="n">
-        <v>7068090</v>
+        <v>7068251</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8643,7 +8646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8653,7 +8656,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8705,7 +8713,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123934442</v>
+        <v>123928514</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -8741,14 +8749,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496964</v>
+        <v>497851</v>
       </c>
       <c r="R59" t="n">
-        <v>7067764</v>
+        <v>7068090</v>
       </c>
       <c r="S59" t="n">
         <v>8</v>
@@ -8780,7 +8788,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8790,7 +8798,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8842,7 +8850,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123934022</v>
+        <v>123933859</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -8882,13 +8890,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496970</v>
+        <v>497016</v>
       </c>
       <c r="R60" t="n">
-        <v>7067716</v>
+        <v>7067743</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8917,7 +8925,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8927,7 +8935,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8984,10 +8992,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123932201</v>
+        <v>123933127</v>
       </c>
       <c r="B61" t="n">
-        <v>98079</v>
+        <v>79870</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8996,55 +9004,46 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497553</v>
+        <v>497133</v>
       </c>
       <c r="R61" t="n">
-        <v>7068083</v>
+        <v>7067678</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -9073,7 +9072,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9083,12 +9082,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9099,6 +9093,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -9115,10 +9134,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123929370</v>
+        <v>123934908</v>
       </c>
       <c r="B62" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9127,46 +9146,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497852</v>
+        <v>497399</v>
       </c>
       <c r="R62" t="n">
-        <v>7067984</v>
+        <v>7067620</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -9195,7 +9214,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9205,7 +9224,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9224,22 +9243,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9257,7 +9276,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123928803</v>
+        <v>123934442</v>
       </c>
       <c r="B63" t="n">
         <v>78788</v>
@@ -9293,17 +9312,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497932</v>
+        <v>496964</v>
       </c>
       <c r="R63" t="n">
-        <v>7068202</v>
+        <v>7067764</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -9332,7 +9351,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9342,12 +9361,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9399,10 +9413,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123927793</v>
+        <v>123933422</v>
       </c>
       <c r="B64" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9415,33 +9429,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -9449,17 +9454,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497653</v>
+        <v>497077</v>
       </c>
       <c r="R64" t="n">
-        <v>7068061</v>
+        <v>7067679</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9488,7 +9493,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9498,12 +9503,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -9555,10 +9555,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123933422</v>
+        <v>123932682</v>
       </c>
       <c r="B65" t="n">
-        <v>90986</v>
+        <v>79869</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9571,27 +9571,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497077</v>
+        <v>497368</v>
       </c>
       <c r="R65" t="n">
-        <v>7067679</v>
+        <v>7067763</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9664,22 +9664,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9697,7 +9697,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948074</v>
+        <v>123948061</v>
       </c>
       <c r="B66" t="n">
         <v>57491</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497809</v>
+        <v>497152</v>
       </c>
       <c r="R66" t="n">
-        <v>7068221</v>
+        <v>7067720</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948076</v>
+        <v>123948085</v>
       </c>
       <c r="B67" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9820,21 +9820,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497599</v>
+        <v>497243</v>
       </c>
       <c r="R67" t="n">
-        <v>7068342</v>
+        <v>7067786</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9880,11 +9880,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9911,10 +9906,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948037</v>
+        <v>123948064</v>
       </c>
       <c r="B68" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9927,21 +9922,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9951,10 +9946,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497443</v>
+        <v>497471</v>
       </c>
       <c r="R68" t="n">
-        <v>7067840</v>
+        <v>7067944</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9987,6 +9982,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10013,7 +10013,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948073</v>
+        <v>123948068</v>
       </c>
       <c r="B69" t="n">
         <v>57491</v>
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497810</v>
+        <v>497549</v>
       </c>
       <c r="R69" t="n">
-        <v>7068216</v>
+        <v>7067939</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10120,10 +10120,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948066</v>
+        <v>123948037</v>
       </c>
       <c r="B70" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10136,21 +10136,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -10160,10 +10160,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497568</v>
+        <v>497443</v>
       </c>
       <c r="R70" t="n">
-        <v>7067974</v>
+        <v>7067840</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10196,11 +10196,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10227,7 +10222,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948077</v>
+        <v>123948048</v>
       </c>
       <c r="B71" t="n">
         <v>57491</v>
@@ -10267,10 +10262,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497583</v>
+        <v>497417</v>
       </c>
       <c r="R71" t="n">
-        <v>7068342</v>
+        <v>7067613</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10307,7 +10302,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10334,7 +10329,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948048</v>
+        <v>123948065</v>
       </c>
       <c r="B72" t="n">
         <v>57491</v>
@@ -10374,10 +10369,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497417</v>
+        <v>497547</v>
       </c>
       <c r="R72" t="n">
-        <v>7067613</v>
+        <v>7068008</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10414,7 +10409,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10441,7 +10436,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948069</v>
+        <v>123948049</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -10481,10 +10476,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497544</v>
+        <v>496958</v>
       </c>
       <c r="R73" t="n">
-        <v>7067872</v>
+        <v>7067783</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10521,7 +10516,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10548,10 +10543,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948083</v>
+        <v>123948079</v>
       </c>
       <c r="B74" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10564,21 +10559,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10588,10 +10583,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497012</v>
+        <v>497614</v>
       </c>
       <c r="R74" t="n">
-        <v>7067783</v>
+        <v>7067898</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10624,6 +10619,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10650,7 +10650,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948075</v>
+        <v>123948059</v>
       </c>
       <c r="B75" t="n">
         <v>57491</v>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497629</v>
+        <v>497338</v>
       </c>
       <c r="R75" t="n">
-        <v>7068330</v>
+        <v>7068065</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10757,7 +10757,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948052</v>
+        <v>123948058</v>
       </c>
       <c r="B76" t="n">
         <v>57491</v>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496977</v>
+        <v>497156</v>
       </c>
       <c r="R76" t="n">
-        <v>7067794</v>
+        <v>7067976</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10864,7 +10864,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948058</v>
+        <v>123948056</v>
       </c>
       <c r="B77" t="n">
         <v>57491</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497156</v>
+        <v>497093</v>
       </c>
       <c r="R77" t="n">
-        <v>7067976</v>
+        <v>7068094</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948071</v>
+        <v>123948070</v>
       </c>
       <c r="B78" t="n">
         <v>57491</v>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497830</v>
+        <v>497876</v>
       </c>
       <c r="R78" t="n">
-        <v>7068267</v>
+        <v>7068110</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -11078,7 +11078,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948062</v>
+        <v>123948041</v>
       </c>
       <c r="B79" t="n">
         <v>57491</v>
@@ -11118,10 +11118,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497431</v>
+        <v>497578</v>
       </c>
       <c r="R79" t="n">
-        <v>7067834</v>
+        <v>7067475</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11185,7 +11185,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948053</v>
+        <v>123948050</v>
       </c>
       <c r="B80" t="n">
         <v>57491</v>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497052</v>
+        <v>496963</v>
       </c>
       <c r="R80" t="n">
-        <v>7067797</v>
+        <v>7067823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11292,10 +11292,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948082</v>
+        <v>123948052</v>
       </c>
       <c r="B81" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11304,25 +11304,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497300</v>
+        <v>496977</v>
       </c>
       <c r="R81" t="n">
-        <v>7068117</v>
+        <v>7067794</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11368,6 +11368,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11394,7 +11399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948063</v>
+        <v>123948073</v>
       </c>
       <c r="B82" t="n">
         <v>57491</v>
@@ -11434,10 +11439,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497448</v>
+        <v>497810</v>
       </c>
       <c r="R82" t="n">
-        <v>7067857</v>
+        <v>7068216</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11501,10 +11506,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948084</v>
+        <v>123948081</v>
       </c>
       <c r="B83" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11513,25 +11518,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -11541,10 +11546,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497101</v>
+        <v>497267</v>
       </c>
       <c r="R83" t="n">
-        <v>7067728</v>
+        <v>7068098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11603,10 +11608,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948070</v>
+        <v>123948082</v>
       </c>
       <c r="B84" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11615,25 +11620,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11643,10 +11648,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497876</v>
+        <v>497300</v>
       </c>
       <c r="R84" t="n">
-        <v>7068110</v>
+        <v>7068117</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11679,11 +11684,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11710,10 +11710,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948041</v>
+        <v>123948084</v>
       </c>
       <c r="B85" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11726,21 +11726,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11750,10 +11750,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497578</v>
+        <v>497101</v>
       </c>
       <c r="R85" t="n">
-        <v>7067475</v>
+        <v>7067728</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11786,11 +11786,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11817,7 +11812,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948057</v>
+        <v>123948055</v>
       </c>
       <c r="B86" t="n">
         <v>57491</v>
@@ -11857,10 +11852,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497142</v>
+        <v>497062</v>
       </c>
       <c r="R86" t="n">
-        <v>7068071</v>
+        <v>7068109</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12031,7 +12026,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948059</v>
+        <v>123948077</v>
       </c>
       <c r="B88" t="n">
         <v>57491</v>
@@ -12071,10 +12066,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497338</v>
+        <v>497583</v>
       </c>
       <c r="R88" t="n">
-        <v>7068065</v>
+        <v>7068342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12111,7 +12106,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12138,7 +12133,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948055</v>
+        <v>123948051</v>
       </c>
       <c r="B89" t="n">
         <v>57491</v>
@@ -12178,10 +12173,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497062</v>
+        <v>496962</v>
       </c>
       <c r="R89" t="n">
-        <v>7068109</v>
+        <v>7067810</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12245,7 +12240,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948056</v>
+        <v>123948066</v>
       </c>
       <c r="B90" t="n">
         <v>57491</v>
@@ -12285,10 +12280,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497093</v>
+        <v>497568</v>
       </c>
       <c r="R90" t="n">
-        <v>7068094</v>
+        <v>7067974</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12352,7 +12347,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948054</v>
+        <v>123948071</v>
       </c>
       <c r="B91" t="n">
         <v>57491</v>
@@ -12392,10 +12387,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497062</v>
+        <v>497830</v>
       </c>
       <c r="R91" t="n">
-        <v>7068118</v>
+        <v>7068267</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12459,7 +12454,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948049</v>
+        <v>123948074</v>
       </c>
       <c r="B92" t="n">
         <v>57491</v>
@@ -12499,10 +12494,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496958</v>
+        <v>497809</v>
       </c>
       <c r="R92" t="n">
-        <v>7067783</v>
+        <v>7068221</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12539,7 +12534,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12566,7 +12561,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948051</v>
+        <v>123948057</v>
       </c>
       <c r="B93" t="n">
         <v>57491</v>
@@ -12606,10 +12601,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496962</v>
+        <v>497142</v>
       </c>
       <c r="R93" t="n">
-        <v>7067810</v>
+        <v>7068071</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12673,10 +12668,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948081</v>
+        <v>123948053</v>
       </c>
       <c r="B94" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12685,25 +12680,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12713,10 +12708,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497267</v>
+        <v>497052</v>
       </c>
       <c r="R94" t="n">
-        <v>7068098</v>
+        <v>7067797</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12749,6 +12744,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12775,10 +12775,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123948085</v>
+        <v>123948060</v>
       </c>
       <c r="B95" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12791,21 +12791,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12815,10 +12815,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497243</v>
+        <v>497140</v>
       </c>
       <c r="R95" t="n">
-        <v>7067786</v>
+        <v>7067713</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12851,6 +12851,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12877,7 +12882,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123948079</v>
+        <v>123948076</v>
       </c>
       <c r="B96" t="n">
         <v>57491</v>
@@ -12917,10 +12922,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497614</v>
+        <v>497599</v>
       </c>
       <c r="R96" t="n">
-        <v>7067898</v>
+        <v>7068342</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12984,7 +12989,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123948060</v>
+        <v>123948062</v>
       </c>
       <c r="B97" t="n">
         <v>57491</v>
@@ -13024,10 +13029,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497140</v>
+        <v>497431</v>
       </c>
       <c r="R97" t="n">
-        <v>7067713</v>
+        <v>7067834</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13091,7 +13096,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123948065</v>
+        <v>123948063</v>
       </c>
       <c r="B98" t="n">
         <v>57491</v>
@@ -13131,10 +13136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497547</v>
+        <v>497448</v>
       </c>
       <c r="R98" t="n">
-        <v>7068008</v>
+        <v>7067857</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13171,7 +13176,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13198,7 +13203,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123948061</v>
+        <v>123948054</v>
       </c>
       <c r="B99" t="n">
         <v>57491</v>
@@ -13238,10 +13243,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497152</v>
+        <v>497062</v>
       </c>
       <c r="R99" t="n">
-        <v>7067720</v>
+        <v>7068118</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13305,10 +13310,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123948068</v>
+        <v>123948083</v>
       </c>
       <c r="B100" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13321,21 +13326,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13345,10 +13350,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497549</v>
+        <v>497012</v>
       </c>
       <c r="R100" t="n">
-        <v>7067939</v>
+        <v>7067783</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13381,11 +13386,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13412,7 +13412,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123948050</v>
+        <v>123948069</v>
       </c>
       <c r="B101" t="n">
         <v>57491</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496963</v>
+        <v>497544</v>
       </c>
       <c r="R101" t="n">
-        <v>7067823</v>
+        <v>7067872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13519,7 +13519,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123948078</v>
+        <v>123948075</v>
       </c>
       <c r="B102" t="n">
         <v>57491</v>
@@ -13559,10 +13559,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497569</v>
+        <v>497629</v>
       </c>
       <c r="R102" t="n">
-        <v>7068352</v>
+        <v>7068330</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13626,7 +13626,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123948064</v>
+        <v>123948078</v>
       </c>
       <c r="B103" t="n">
         <v>57491</v>
@@ -13666,10 +13666,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497471</v>
+        <v>497569</v>
       </c>
       <c r="R103" t="n">
-        <v>7067944</v>
+        <v>7068352</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935511</v>
+        <v>123935971</v>
       </c>
       <c r="B105" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,44 +13886,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497429</v>
+        <v>497477</v>
       </c>
       <c r="R105" t="n">
-        <v>7067368</v>
+        <v>7067373</v>
       </c>
       <c r="S105" t="n">
         <v>9</v>
@@ -13955,7 +13945,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13965,7 +13955,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13994,12 +13984,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14017,10 +14007,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935623</v>
+        <v>123936336</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14033,37 +14023,47 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497400</v>
+        <v>497296</v>
       </c>
       <c r="R106" t="n">
-        <v>7067320</v>
+        <v>7067024</v>
       </c>
       <c r="S106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14102,7 +14102,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14131,12 +14136,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14154,7 +14159,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935469</v>
+        <v>123935892</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -14194,13 +14199,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497429</v>
+        <v>497488</v>
       </c>
       <c r="R107" t="n">
-        <v>7067378</v>
+        <v>7067338</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14229,7 +14234,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14239,7 +14244,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14291,7 +14296,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123935971</v>
+        <v>123935662</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -14331,13 +14336,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497477</v>
+        <v>497407</v>
       </c>
       <c r="R108" t="n">
-        <v>7067373</v>
+        <v>7067289</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14366,7 +14371,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14376,7 +14381,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14428,10 +14433,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123936388</v>
+        <v>123935511</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14444,37 +14449,47 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497347</v>
+        <v>497429</v>
       </c>
       <c r="R109" t="n">
-        <v>7067031</v>
+        <v>7067368</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14503,7 +14518,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14513,7 +14528,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14542,12 +14557,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14565,7 +14580,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935892</v>
+        <v>123935623</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -14605,10 +14620,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497488</v>
+        <v>497400</v>
       </c>
       <c r="R110" t="n">
-        <v>7067338</v>
+        <v>7067320</v>
       </c>
       <c r="S110" t="n">
         <v>8</v>
@@ -14640,7 +14655,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14650,7 +14665,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14702,10 +14717,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123936336</v>
+        <v>123935469</v>
       </c>
       <c r="B111" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -14718,47 +14733,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497296</v>
+        <v>497429</v>
       </c>
       <c r="R111" t="n">
-        <v>7067024</v>
+        <v>7067378</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14787,7 +14792,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14797,12 +14802,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14831,12 +14831,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14854,7 +14854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123935662</v>
+        <v>123936388</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -14894,13 +14894,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497407</v>
+        <v>497347</v>
       </c>
       <c r="R112" t="n">
-        <v>7067289</v>
+        <v>7067031</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14991,7 +14991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948040</v>
+        <v>123948045</v>
       </c>
       <c r="B113" t="n">
         <v>57491</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497269</v>
+        <v>497439</v>
       </c>
       <c r="R113" t="n">
-        <v>7067065</v>
+        <v>7067336</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15205,10 +15205,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948038</v>
+        <v>123948080</v>
       </c>
       <c r="B115" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15221,16 +15221,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497227</v>
+        <v>497370</v>
       </c>
       <c r="R115" t="n">
-        <v>7067047</v>
+        <v>7067042</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15312,10 +15312,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948080</v>
+        <v>123948039</v>
       </c>
       <c r="B116" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15328,16 +15328,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497370</v>
+        <v>497241</v>
       </c>
       <c r="R116" t="n">
-        <v>7067042</v>
+        <v>7067063</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948045</v>
+        <v>123948040</v>
       </c>
       <c r="B117" t="n">
         <v>57491</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497439</v>
+        <v>497269</v>
       </c>
       <c r="R117" t="n">
-        <v>7067336</v>
+        <v>7067065</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948039</v>
+        <v>123948047</v>
       </c>
       <c r="B118" t="n">
         <v>57491</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497241</v>
+        <v>497422</v>
       </c>
       <c r="R118" t="n">
-        <v>7067063</v>
+        <v>7067360</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15633,7 +15633,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948047</v>
+        <v>123948038</v>
       </c>
       <c r="B119" t="n">
         <v>57491</v>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497422</v>
+        <v>497227</v>
       </c>
       <c r="R119" t="n">
-        <v>7067360</v>
+        <v>7067047</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123932969</v>
+        <v>123925387</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -721,17 +730,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497236</v>
+        <v>497600</v>
       </c>
       <c r="R2" t="n">
-        <v>7067739</v>
+        <v>7067872</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,24 +767,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123934742</v>
+        <v>123935093</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,32 +822,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497184</v>
+        <v>497438</v>
       </c>
       <c r="R3" t="n">
-        <v>7067677</v>
+        <v>7067653</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,6 +911,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1081,10 +1090,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933422</v>
+        <v>123925856</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,39 +1106,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497077</v>
+        <v>497652</v>
       </c>
       <c r="R5" t="n">
-        <v>7067679</v>
+        <v>7067886</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1161,7 +1165,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,12 +1204,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933650</v>
+        <v>123928327</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,43 +1239,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497112</v>
+        <v>497712</v>
       </c>
       <c r="R6" t="n">
-        <v>7067726</v>
+        <v>7068103</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1313,7 +1322,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,27 +1341,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1359,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123932682</v>
+        <v>123933142</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,31 +1371,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1410,13 +1404,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497368</v>
+        <v>497133</v>
       </c>
       <c r="R7" t="n">
-        <v>7067763</v>
+        <v>7067678</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1445,7 +1439,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1455,7 +1449,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1507,7 +1501,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123927550</v>
+        <v>123928858</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1547,13 +1541,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497670</v>
+        <v>497900</v>
       </c>
       <c r="R8" t="n">
-        <v>7068014</v>
+        <v>7068251</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1582,7 +1576,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1592,7 +1586,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1644,7 +1643,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123929190</v>
+        <v>123931616</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1684,13 +1683,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497832</v>
+        <v>497562</v>
       </c>
       <c r="R9" t="n">
-        <v>7067981</v>
+        <v>7067959</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1719,7 +1718,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1729,12 +1728,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,10 +1780,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123925387</v>
+        <v>123928379</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1798,60 +1792,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497600</v>
+        <v>497732</v>
       </c>
       <c r="R10" t="n">
-        <v>7067872</v>
+        <v>7068101</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1878,14 +1853,19 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1900,6 +1880,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123928741</v>
+        <v>123928803</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1929,60 +1929,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497907</v>
+        <v>497932</v>
       </c>
       <c r="R11" t="n">
-        <v>7068146</v>
+        <v>7068202</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2011,7 +1992,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2021,12 +2002,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2041,6 +2022,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2058,10 +2059,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123933492</v>
+        <v>123934742</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2074,37 +2075,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497103</v>
+        <v>497184</v>
       </c>
       <c r="R12" t="n">
-        <v>7067696</v>
+        <v>7067677</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2133,7 +2144,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2143,7 +2154,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2157,27 +2173,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2195,10 +2191,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123933774</v>
+        <v>123927679</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2207,41 +2203,60 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497066</v>
+        <v>497679</v>
       </c>
       <c r="R13" t="n">
-        <v>7067728</v>
+        <v>7068046</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2270,7 +2285,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2280,7 +2295,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2294,27 +2314,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123934085</v>
+        <v>123934022</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2344,60 +2344,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496980</v>
+        <v>496970</v>
       </c>
       <c r="R14" t="n">
-        <v>7067690</v>
+        <v>7067716</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2426,7 +2407,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2436,12 +2417,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2456,6 +2437,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2473,10 +2474,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123934908</v>
+        <v>123927991</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2489,42 +2490,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497399</v>
+        <v>497659</v>
       </c>
       <c r="R15" t="n">
-        <v>7067620</v>
+        <v>7068053</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2553,7 +2559,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2563,7 +2569,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2577,7 +2588,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2592,12 +2603,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2615,10 +2626,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123928831</v>
+        <v>123931528</v>
       </c>
       <c r="B16" t="n">
-        <v>79919</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2627,38 +2638,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497927</v>
+        <v>497563</v>
       </c>
       <c r="R16" t="n">
-        <v>7068210</v>
+        <v>7067965</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2690,7 +2711,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2700,7 +2721,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2715,6 +2741,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2732,10 +2778,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123933142</v>
+        <v>123934255</v>
       </c>
       <c r="B17" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2744,46 +2790,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497133</v>
+        <v>496932</v>
       </c>
       <c r="R17" t="n">
-        <v>7067678</v>
+        <v>7067736</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2812,7 +2853,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2822,7 +2863,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2836,27 +2877,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2874,7 +2915,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123925995</v>
+        <v>123933962</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2910,17 +2951,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497628</v>
+        <v>496999</v>
       </c>
       <c r="R18" t="n">
-        <v>7067895</v>
+        <v>7067688</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2949,7 +2990,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2959,7 +3000,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3011,7 +3052,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123928514</v>
+        <v>123926190</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3051,13 +3092,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497851</v>
+        <v>497654</v>
       </c>
       <c r="R19" t="n">
-        <v>7068090</v>
+        <v>7067926</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3086,7 +3127,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3096,7 +3137,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,10 +3189,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123929370</v>
+        <v>123929190</v>
       </c>
       <c r="B20" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3160,20 +3201,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3182,24 +3223,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497852</v>
+        <v>497832</v>
       </c>
       <c r="R20" t="n">
-        <v>7067984</v>
+        <v>7067981</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3228,7 +3264,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3238,7 +3274,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3257,22 +3298,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3290,10 +3331,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123934569</v>
+        <v>123925995</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3306,37 +3347,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497124</v>
+        <v>497628</v>
       </c>
       <c r="R21" t="n">
-        <v>7067682</v>
+        <v>7067895</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3365,7 +3406,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3375,7 +3416,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3389,27 +3430,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3427,10 +3468,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123934255</v>
+        <v>123935202</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3443,37 +3484,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496932</v>
+        <v>497524</v>
       </c>
       <c r="R22" t="n">
-        <v>7067736</v>
+        <v>7067827</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3502,7 +3548,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3512,7 +3558,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3526,7 +3572,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3541,12 +3587,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3564,7 +3610,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123933859</v>
+        <v>123925768</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3600,17 +3646,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497016</v>
+        <v>497652</v>
       </c>
       <c r="R23" t="n">
-        <v>7067743</v>
+        <v>7067869</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3639,7 +3685,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3649,12 +3695,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3706,10 +3747,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932608</v>
+        <v>123929459</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3722,37 +3763,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497492</v>
+        <v>497843</v>
       </c>
       <c r="R24" t="n">
-        <v>7067833</v>
+        <v>7067903</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3781,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3791,7 +3842,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3820,12 +3876,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3843,10 +3899,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123929282</v>
+        <v>123931684</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3859,37 +3915,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497853</v>
+        <v>497576</v>
       </c>
       <c r="R25" t="n">
-        <v>7067970</v>
+        <v>7067995</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3918,7 +3984,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3928,12 +3994,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3952,22 +4018,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3985,10 +4051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123932710</v>
+        <v>123932969</v>
       </c>
       <c r="B26" t="n">
-        <v>79892</v>
+        <v>56714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4001,37 +4067,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497376</v>
+        <v>497236</v>
       </c>
       <c r="R26" t="n">
-        <v>7067768</v>
+        <v>7067739</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4060,7 +4136,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4070,7 +4146,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4085,26 +4166,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4122,10 +4183,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123925602</v>
+        <v>123934908</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4138,47 +4199,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497599</v>
+        <v>497399</v>
       </c>
       <c r="R27" t="n">
-        <v>7067878</v>
+        <v>7067620</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4207,7 +4263,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4217,12 +4273,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4251,12 +4302,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4274,10 +4325,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123928438</v>
+        <v>123928741</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4286,41 +4337,60 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497801</v>
+        <v>497907</v>
       </c>
       <c r="R28" t="n">
-        <v>7068154</v>
+        <v>7068146</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4349,7 +4419,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4359,7 +4429,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4374,26 +4449,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4411,10 +4466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123926190</v>
+        <v>123934085</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4423,41 +4478,60 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497654</v>
+        <v>496980</v>
       </c>
       <c r="R29" t="n">
-        <v>7067926</v>
+        <v>7067690</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4486,7 +4560,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4496,7 +4570,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4511,26 +4590,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4548,7 +4607,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123934022</v>
+        <v>123933492</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -4588,13 +4647,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496970</v>
+        <v>497103</v>
       </c>
       <c r="R30" t="n">
-        <v>7067716</v>
+        <v>7067696</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4623,7 +4682,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4633,12 +4692,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4690,7 +4744,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123933086</v>
+        <v>123932385</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4726,17 +4780,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497126</v>
+        <v>497528</v>
       </c>
       <c r="R31" t="n">
-        <v>7067709</v>
+        <v>7067930</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4765,7 +4819,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4775,7 +4829,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,10 +4881,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123929459</v>
+        <v>123932682</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4843,47 +4897,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497843</v>
+        <v>497368</v>
       </c>
       <c r="R32" t="n">
-        <v>7067903</v>
+        <v>7067763</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4912,7 +4961,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4922,12 +4971,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4946,22 +4990,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4979,10 +5023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123925768</v>
+        <v>123933712</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4991,41 +5035,51 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497652</v>
+        <v>497111</v>
       </c>
       <c r="R33" t="n">
-        <v>7067869</v>
+        <v>7067721</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5054,7 +5108,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5064,7 +5118,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5078,27 +5137,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5116,10 +5155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123933712</v>
+        <v>123925602</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5128,31 +5167,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5162,17 +5201,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497111</v>
+        <v>497599</v>
       </c>
       <c r="R34" t="n">
-        <v>7067721</v>
+        <v>7067878</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5201,7 +5240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5211,12 +5250,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5230,7 +5269,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5248,10 +5307,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123928379</v>
+        <v>123933127</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5264,37 +5323,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497732</v>
+        <v>497133</v>
       </c>
       <c r="R35" t="n">
-        <v>7068101</v>
+        <v>7067678</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5323,7 +5387,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5333,7 +5397,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5352,22 +5416,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5385,10 +5449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123927793</v>
+        <v>123929370</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>79926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5397,40 +5461,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5439,10 +5494,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497653</v>
+        <v>497852</v>
       </c>
       <c r="R36" t="n">
-        <v>7068061</v>
+        <v>7067984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5474,7 +5529,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5484,12 +5539,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5503,27 +5553,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5541,10 +5591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123929497</v>
+        <v>123933859</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5557,47 +5607,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497846</v>
+        <v>497016</v>
       </c>
       <c r="R37" t="n">
-        <v>7067895</v>
+        <v>7067743</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5626,7 +5666,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5636,12 +5676,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5670,12 +5710,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5693,10 +5733,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123935093</v>
+        <v>123929497</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5709,42 +5749,47 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497438</v>
+        <v>497846</v>
       </c>
       <c r="R38" t="n">
-        <v>7067653</v>
+        <v>7067895</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5773,7 +5818,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5783,7 +5828,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5797,7 +5847,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5812,12 +5862,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5835,10 +5885,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123931616</v>
+        <v>123927793</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5851,37 +5901,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497562</v>
+        <v>497653</v>
       </c>
       <c r="R39" t="n">
-        <v>7067959</v>
+        <v>7068061</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5910,7 +5974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5920,7 +5984,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5934,7 +6003,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5949,12 +6018,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5972,10 +6041,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123929301</v>
+        <v>123932710</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5988,42 +6057,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497846</v>
+        <v>497376</v>
       </c>
       <c r="R40" t="n">
-        <v>7067985</v>
+        <v>7067768</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6052,7 +6116,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6062,12 +6126,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6119,10 +6178,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123934442</v>
+        <v>123929282</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6135,37 +6194,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496964</v>
+        <v>497853</v>
       </c>
       <c r="R41" t="n">
-        <v>7067764</v>
+        <v>7067970</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6194,7 +6253,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6204,7 +6263,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6223,22 +6287,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6256,10 +6320,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123933127</v>
+        <v>123928574</v>
       </c>
       <c r="B42" t="n">
-        <v>79892</v>
+        <v>79919</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6268,46 +6332,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497133</v>
+        <v>497848</v>
       </c>
       <c r="R42" t="n">
-        <v>7067678</v>
+        <v>7068101</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6336,7 +6395,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6346,7 +6405,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6361,26 +6420,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6398,10 +6437,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123927991</v>
+        <v>123934349</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6414,44 +6453,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497659</v>
+        <v>496957</v>
       </c>
       <c r="R43" t="n">
-        <v>7068053</v>
+        <v>7067780</v>
       </c>
       <c r="S43" t="n">
         <v>7</v>
@@ -6483,7 +6512,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6493,12 +6522,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6512,7 +6536,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6527,12 +6551,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6550,7 +6574,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123928803</v>
+        <v>123926766</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -6584,19 +6608,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497932</v>
+        <v>497661</v>
       </c>
       <c r="R44" t="n">
-        <v>7068202</v>
+        <v>7067931</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6625,7 +6654,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6635,12 +6664,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6692,10 +6721,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123927679</v>
+        <v>123933650</v>
       </c>
       <c r="B45" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6704,60 +6733,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497679</v>
+        <v>497112</v>
       </c>
       <c r="R45" t="n">
-        <v>7068046</v>
+        <v>7067726</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6786,7 +6801,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6796,12 +6811,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6815,7 +6825,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6833,10 +6863,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123935202</v>
+        <v>123929301</v>
       </c>
       <c r="B46" t="n">
-        <v>91008</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6849,27 +6879,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6878,13 +6908,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497524</v>
+        <v>497846</v>
       </c>
       <c r="R46" t="n">
-        <v>7067827</v>
+        <v>7067985</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6913,7 +6943,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6923,7 +6953,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6952,12 +6987,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6975,7 +7010,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123932385</v>
+        <v>123928438</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -7015,13 +7050,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497528</v>
+        <v>497801</v>
       </c>
       <c r="R47" t="n">
-        <v>7067930</v>
+        <v>7068154</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7050,7 +7085,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7060,7 +7095,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7112,7 +7147,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123933962</v>
+        <v>123928514</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -7148,14 +7183,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496999</v>
+        <v>497851</v>
       </c>
       <c r="R48" t="n">
-        <v>7067688</v>
+        <v>7068090</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7187,7 +7222,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7197,7 +7232,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7249,7 +7284,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123928858</v>
+        <v>123934442</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -7285,17 +7320,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497900</v>
+        <v>496964</v>
       </c>
       <c r="R49" t="n">
-        <v>7068251</v>
+        <v>7067764</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7324,7 +7359,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7334,12 +7369,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7391,10 +7421,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123928574</v>
+        <v>123927550</v>
       </c>
       <c r="B50" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7403,25 +7433,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7431,13 +7461,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497848</v>
+        <v>497670</v>
       </c>
       <c r="R50" t="n">
-        <v>7068101</v>
+        <v>7068014</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7466,7 +7496,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7476,7 +7506,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7491,6 +7521,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7508,10 +7558,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123931684</v>
+        <v>123928831</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>79919</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7520,51 +7570,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497576</v>
+        <v>497927</v>
       </c>
       <c r="R51" t="n">
-        <v>7067995</v>
+        <v>7068210</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7593,7 +7633,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7603,12 +7643,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7623,26 +7658,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7660,10 +7675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123925856</v>
+        <v>123934569</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7676,37 +7691,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497652</v>
+        <v>497124</v>
       </c>
       <c r="R52" t="n">
-        <v>7067886</v>
+        <v>7067682</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7735,7 +7750,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7745,7 +7760,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7759,27 +7774,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7797,10 +7812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123931528</v>
+        <v>123933086</v>
       </c>
       <c r="B53" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7813,47 +7828,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497563</v>
+        <v>497126</v>
       </c>
       <c r="R53" t="n">
-        <v>7067965</v>
+        <v>7067709</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7882,7 +7887,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7892,12 +7897,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123934349</v>
+        <v>123932608</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -7985,17 +7985,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496957</v>
+        <v>497492</v>
       </c>
       <c r="R54" t="n">
-        <v>7067780</v>
+        <v>7067833</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8086,7 +8086,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123926766</v>
+        <v>123933774</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -8120,24 +8120,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497661</v>
+        <v>497066</v>
       </c>
       <c r="R55" t="n">
-        <v>7067931</v>
+        <v>7067728</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8166,7 +8161,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8176,12 +8171,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8195,7 +8185,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -8233,10 +8223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123928327</v>
+        <v>123933422</v>
       </c>
       <c r="B56" t="n">
-        <v>56725</v>
+        <v>91008</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8245,48 +8235,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102613</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497712</v>
+        <v>497077</v>
       </c>
       <c r="R56" t="n">
-        <v>7068103</v>
+        <v>7067679</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -8318,7 +8303,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8328,12 +8313,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8348,6 +8328,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123948061</v>
+        <v>123948084</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497152</v>
+        <v>497101</v>
       </c>
       <c r="R57" t="n">
-        <v>7067720</v>
+        <v>7067728</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8441,11 +8441,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8472,7 +8467,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123948058</v>
+        <v>123948079</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8512,10 +8507,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497156</v>
+        <v>497614</v>
       </c>
       <c r="R58" t="n">
-        <v>7067976</v>
+        <v>7067898</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8552,7 +8547,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8579,7 +8574,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123948060</v>
+        <v>123948050</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8619,10 +8614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497140</v>
+        <v>496963</v>
       </c>
       <c r="R59" t="n">
-        <v>7067713</v>
+        <v>7067823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8659,7 +8654,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8686,7 +8681,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123948075</v>
+        <v>123948057</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -8726,10 +8721,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497629</v>
+        <v>497142</v>
       </c>
       <c r="R60" t="n">
-        <v>7068330</v>
+        <v>7068071</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8766,7 +8761,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8793,7 +8788,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123948051</v>
+        <v>123948069</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -8833,10 +8828,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496962</v>
+        <v>497544</v>
       </c>
       <c r="R61" t="n">
-        <v>7067810</v>
+        <v>7067872</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8900,7 +8895,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123948076</v>
+        <v>123948059</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497599</v>
+        <v>497338</v>
       </c>
       <c r="R62" t="n">
-        <v>7068342</v>
+        <v>7068065</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8980,7 +8975,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9007,10 +9002,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123948037</v>
+        <v>123948053</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9023,21 +9018,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9047,10 +9042,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497443</v>
+        <v>497052</v>
       </c>
       <c r="R63" t="n">
-        <v>7067840</v>
+        <v>7067797</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9083,6 +9078,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9109,7 +9109,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948074</v>
+        <v>123948054</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497809</v>
+        <v>497062</v>
       </c>
       <c r="R64" t="n">
-        <v>7068221</v>
+        <v>7068118</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948059</v>
+        <v>123948085</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9232,21 +9232,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497338</v>
+        <v>497243</v>
       </c>
       <c r="R65" t="n">
-        <v>7068065</v>
+        <v>7067786</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9292,11 +9292,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9323,10 +9318,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948085</v>
+        <v>123948055</v>
       </c>
       <c r="B66" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9339,21 +9334,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9363,10 +9358,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497243</v>
+        <v>497062</v>
       </c>
       <c r="R66" t="n">
-        <v>7067786</v>
+        <v>7068109</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9399,6 +9394,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9425,7 +9425,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948041</v>
+        <v>123948068</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497578</v>
+        <v>497549</v>
       </c>
       <c r="R67" t="n">
-        <v>7067475</v>
+        <v>7067939</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948055</v>
+        <v>123948077</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -9572,10 +9572,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497062</v>
+        <v>497583</v>
       </c>
       <c r="R68" t="n">
-        <v>7068109</v>
+        <v>7068342</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9639,7 +9639,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948073</v>
+        <v>123948076</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497810</v>
+        <v>497599</v>
       </c>
       <c r="R69" t="n">
-        <v>7068216</v>
+        <v>7068342</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9746,7 +9746,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948071</v>
+        <v>123948065</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -9786,10 +9786,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497830</v>
+        <v>497547</v>
       </c>
       <c r="R70" t="n">
-        <v>7068267</v>
+        <v>7068008</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948084</v>
+        <v>123948082</v>
       </c>
       <c r="B71" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9865,25 +9865,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497101</v>
+        <v>497300</v>
       </c>
       <c r="R71" t="n">
-        <v>7067728</v>
+        <v>7068117</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948049</v>
+        <v>123948064</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496958</v>
+        <v>497471</v>
       </c>
       <c r="R72" t="n">
-        <v>7067783</v>
+        <v>7067944</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10062,7 +10062,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948079</v>
+        <v>123948071</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497614</v>
+        <v>497830</v>
       </c>
       <c r="R73" t="n">
-        <v>7067898</v>
+        <v>7068267</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10169,7 +10169,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948048</v>
+        <v>123948070</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497417</v>
+        <v>497876</v>
       </c>
       <c r="R74" t="n">
-        <v>7067613</v>
+        <v>7068110</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948083</v>
+        <v>123948041</v>
       </c>
       <c r="B75" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10292,21 +10292,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497012</v>
+        <v>497578</v>
       </c>
       <c r="R75" t="n">
-        <v>7067783</v>
+        <v>7067475</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10352,6 +10352,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10378,7 +10383,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948065</v>
+        <v>123948056</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -10418,10 +10423,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497547</v>
+        <v>497093</v>
       </c>
       <c r="R76" t="n">
-        <v>7068008</v>
+        <v>7068094</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10458,7 +10463,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10485,10 +10490,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948070</v>
+        <v>123948081</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10497,25 +10502,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10525,10 +10530,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497876</v>
+        <v>497267</v>
       </c>
       <c r="R77" t="n">
-        <v>7068110</v>
+        <v>7068098</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10561,11 +10566,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10592,7 +10592,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948069</v>
+        <v>123948052</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497544</v>
+        <v>496977</v>
       </c>
       <c r="R78" t="n">
-        <v>7067872</v>
+        <v>7067794</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948053</v>
+        <v>123948067</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497052</v>
+        <v>497567</v>
       </c>
       <c r="R79" t="n">
-        <v>7067797</v>
+        <v>7067939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10913,10 +10913,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948081</v>
+        <v>123948066</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10925,25 +10925,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10953,10 +10953,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497267</v>
+        <v>497568</v>
       </c>
       <c r="R81" t="n">
-        <v>7068098</v>
+        <v>7067974</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10989,6 +10989,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11015,10 +11020,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948082</v>
+        <v>123948062</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11027,25 +11032,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11055,10 +11060,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497300</v>
+        <v>497431</v>
       </c>
       <c r="R82" t="n">
-        <v>7068117</v>
+        <v>7067834</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11091,6 +11096,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11117,7 +11127,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948077</v>
+        <v>123948051</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11157,10 +11167,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497583</v>
+        <v>496962</v>
       </c>
       <c r="R83" t="n">
-        <v>7068342</v>
+        <v>7067810</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11197,7 +11207,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11224,7 +11234,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948056</v>
+        <v>123948061</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11264,10 +11274,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497093</v>
+        <v>497152</v>
       </c>
       <c r="R84" t="n">
-        <v>7068094</v>
+        <v>7067720</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11331,10 +11341,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948054</v>
+        <v>123948083</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11347,21 +11357,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11371,10 +11381,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497062</v>
+        <v>497012</v>
       </c>
       <c r="R85" t="n">
-        <v>7068118</v>
+        <v>7067783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11407,11 +11417,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11438,7 +11443,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948050</v>
+        <v>123948060</v>
       </c>
       <c r="B86" t="n">
         <v>57513</v>
@@ -11478,10 +11483,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496963</v>
+        <v>497140</v>
       </c>
       <c r="R86" t="n">
-        <v>7067823</v>
+        <v>7067713</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11518,7 +11523,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11545,7 +11550,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948052</v>
+        <v>123948048</v>
       </c>
       <c r="B87" t="n">
         <v>57513</v>
@@ -11585,10 +11590,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>496977</v>
+        <v>497417</v>
       </c>
       <c r="R87" t="n">
-        <v>7067794</v>
+        <v>7067613</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11652,7 +11657,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948062</v>
+        <v>123948075</v>
       </c>
       <c r="B88" t="n">
         <v>57513</v>
@@ -11692,10 +11697,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497431</v>
+        <v>497629</v>
       </c>
       <c r="R88" t="n">
-        <v>7067834</v>
+        <v>7068330</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11732,7 +11737,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11759,7 +11764,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948063</v>
+        <v>123948058</v>
       </c>
       <c r="B89" t="n">
         <v>57513</v>
@@ -11799,10 +11804,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497448</v>
+        <v>497156</v>
       </c>
       <c r="R89" t="n">
-        <v>7067857</v>
+        <v>7067976</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11839,7 +11844,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11866,10 +11871,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948066</v>
+        <v>123948037</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11882,21 +11887,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11906,10 +11911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497568</v>
+        <v>497443</v>
       </c>
       <c r="R90" t="n">
-        <v>7067974</v>
+        <v>7067840</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11942,11 +11947,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11973,7 +11973,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948064</v>
+        <v>123948074</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497471</v>
+        <v>497809</v>
       </c>
       <c r="R91" t="n">
-        <v>7067944</v>
+        <v>7068221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12080,7 +12080,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948057</v>
+        <v>123948049</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497142</v>
+        <v>496958</v>
       </c>
       <c r="R92" t="n">
-        <v>7068071</v>
+        <v>7067783</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12187,7 +12187,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948067</v>
+        <v>123948063</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497567</v>
+        <v>497448</v>
       </c>
       <c r="R93" t="n">
-        <v>7067939</v>
+        <v>7067857</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12294,7 +12294,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948068</v>
+        <v>123948073</v>
       </c>
       <c r="B94" t="n">
         <v>57513</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497549</v>
+        <v>497810</v>
       </c>
       <c r="R94" t="n">
-        <v>7067939</v>
+        <v>7068216</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123929067</v>
+        <v>123934404</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12447,17 +12447,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497903</v>
+        <v>496972</v>
       </c>
       <c r="R95" t="n">
-        <v>7068110</v>
+        <v>7067780</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12553,7 +12553,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123929700</v>
+        <v>123929067</v>
       </c>
       <c r="B96" t="n">
         <v>57513</v>
@@ -12589,7 +12589,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -12599,17 +12599,17 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497829</v>
+        <v>497903</v>
       </c>
       <c r="R96" t="n">
-        <v>7067835</v>
+        <v>7068110</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -12705,10 +12705,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123931433</v>
+        <v>123934695</v>
       </c>
       <c r="B97" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12717,51 +12717,46 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497554</v>
+        <v>497164</v>
       </c>
       <c r="R97" t="n">
-        <v>7067886</v>
+        <v>7067665</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12790,7 +12785,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12800,12 +12795,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12819,27 +12814,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12857,7 +12852,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123934404</v>
+        <v>123931433</v>
       </c>
       <c r="B98" t="n">
         <v>57513</v>
@@ -12903,17 +12898,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496972</v>
+        <v>497554</v>
       </c>
       <c r="R98" t="n">
-        <v>7067780</v>
+        <v>7067886</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12942,7 +12937,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12952,12 +12947,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13009,10 +13004,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123934695</v>
+        <v>123931338</v>
       </c>
       <c r="B99" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13021,43 +13016,48 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497164</v>
+        <v>497552</v>
       </c>
       <c r="R99" t="n">
-        <v>7067665</v>
+        <v>7067881</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13118,27 +13118,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123929267</v>
+        <v>123929700</v>
       </c>
       <c r="B101" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13303,42 +13303,47 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497833</v>
+        <v>497829</v>
       </c>
       <c r="R101" t="n">
-        <v>7067988</v>
+        <v>7067835</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13367,7 +13372,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13377,12 +13382,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13396,27 +13401,27 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13434,10 +13439,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123932552</v>
+        <v>123929267</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13450,27 +13455,27 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13479,13 +13484,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497461</v>
+        <v>497833</v>
       </c>
       <c r="R102" t="n">
-        <v>7067890</v>
+        <v>7067988</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13514,7 +13519,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13524,12 +13529,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13548,22 +13553,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13581,7 +13586,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123931338</v>
+        <v>123932552</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13620,24 +13625,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497552</v>
+        <v>497461</v>
       </c>
       <c r="R103" t="n">
-        <v>7067881</v>
+        <v>7067890</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13870,7 +13870,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935511</v>
+        <v>123936336</v>
       </c>
       <c r="B105" t="n">
         <v>57513</v>
@@ -13906,7 +13906,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -13920,13 +13920,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497429</v>
+        <v>497296</v>
       </c>
       <c r="R105" t="n">
-        <v>7067368</v>
+        <v>7067024</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13965,7 +13965,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14017,7 +14022,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935971</v>
+        <v>123935469</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -14057,13 +14062,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497477</v>
+        <v>497429</v>
       </c>
       <c r="R106" t="n">
-        <v>7067373</v>
+        <v>7067378</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14092,7 +14097,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14102,7 +14107,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14154,10 +14159,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935892</v>
+        <v>123935511</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14170,37 +14175,47 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497488</v>
+        <v>497429</v>
       </c>
       <c r="R107" t="n">
-        <v>7067338</v>
+        <v>7067368</v>
       </c>
       <c r="S107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14229,7 +14244,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14239,7 +14254,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14268,12 +14283,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14428,7 +14443,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123935662</v>
+        <v>123935971</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -14468,13 +14483,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497407</v>
+        <v>497477</v>
       </c>
       <c r="R109" t="n">
-        <v>7067289</v>
+        <v>7067373</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14503,7 +14518,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14513,7 +14528,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14565,7 +14580,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935623</v>
+        <v>123935892</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -14605,10 +14620,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497400</v>
+        <v>497488</v>
       </c>
       <c r="R110" t="n">
-        <v>7067320</v>
+        <v>7067338</v>
       </c>
       <c r="S110" t="n">
         <v>8</v>
@@ -14640,7 +14655,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14650,7 +14665,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14702,7 +14717,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935469</v>
+        <v>123935623</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -14742,13 +14757,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497429</v>
+        <v>497400</v>
       </c>
       <c r="R111" t="n">
-        <v>7067378</v>
+        <v>7067320</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14777,7 +14792,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14787,7 +14802,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14839,10 +14854,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123936336</v>
+        <v>123935662</v>
       </c>
       <c r="B112" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14855,47 +14870,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497296</v>
+        <v>497407</v>
       </c>
       <c r="R112" t="n">
-        <v>7067024</v>
+        <v>7067289</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14924,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14934,12 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14991,10 +14991,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948042</v>
+        <v>123948080</v>
       </c>
       <c r="B113" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15007,16 +15007,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497448</v>
+        <v>497370</v>
       </c>
       <c r="R113" t="n">
-        <v>7067435</v>
+        <v>7067042</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948038</v>
+        <v>123948042</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497227</v>
+        <v>497448</v>
       </c>
       <c r="R114" t="n">
-        <v>7067047</v>
+        <v>7067435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948047</v>
+        <v>123948040</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497422</v>
+        <v>497269</v>
       </c>
       <c r="R116" t="n">
-        <v>7067360</v>
+        <v>7067065</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15419,10 +15419,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948080</v>
+        <v>123948047</v>
       </c>
       <c r="B117" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15435,16 +15435,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497370</v>
+        <v>497422</v>
       </c>
       <c r="R117" t="n">
-        <v>7067042</v>
+        <v>7067360</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15526,7 +15526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948040</v>
+        <v>123948038</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497269</v>
+        <v>497227</v>
       </c>
       <c r="R118" t="n">
-        <v>7067065</v>
+        <v>7067047</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123925387</v>
+        <v>123929459</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497600</v>
+        <v>497843</v>
       </c>
       <c r="R2" t="n">
-        <v>7067872</v>
+        <v>7067903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,14 +758,24 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +790,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123935093</v>
+        <v>123929301</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,42 +843,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497438</v>
+        <v>497846</v>
       </c>
       <c r="R3" t="n">
-        <v>7067653</v>
+        <v>7067985</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +917,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +936,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -925,12 +951,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -948,10 +974,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123932697</v>
+        <v>123928831</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>79919</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,46 +986,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497385</v>
+        <v>497927</v>
       </c>
       <c r="R4" t="n">
-        <v>7067784</v>
+        <v>7068210</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1038,7 +1059,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,26 +1074,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1091,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123925856</v>
+        <v>123932385</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1130,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497652</v>
+        <v>497528</v>
       </c>
       <c r="R5" t="n">
-        <v>7067886</v>
+        <v>7067930</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1165,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,7 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1227,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123928327</v>
+        <v>123933962</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,51 +1240,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497712</v>
+        <v>496999</v>
       </c>
       <c r="R6" t="n">
-        <v>7068103</v>
+        <v>7067688</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1322,12 +1313,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1342,6 +1328,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1359,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933142</v>
+        <v>123929497</v>
       </c>
       <c r="B7" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1371,43 +1377,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497133</v>
+        <v>497846</v>
       </c>
       <c r="R7" t="n">
-        <v>7067678</v>
+        <v>7067895</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1439,7 +1450,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,7 +1460,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,22 +1484,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1501,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123928858</v>
+        <v>123927793</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,37 +1533,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497900</v>
+        <v>497653</v>
       </c>
       <c r="R8" t="n">
-        <v>7068251</v>
+        <v>7068061</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1576,7 +1606,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1586,12 +1616,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,7 +1635,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1620,12 +1650,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1643,10 +1673,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123931616</v>
+        <v>123929370</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1655,20 +1685,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1677,19 +1707,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497562</v>
+        <v>497852</v>
       </c>
       <c r="R9" t="n">
-        <v>7067959</v>
+        <v>7067984</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1718,7 +1753,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1728,7 +1763,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1747,22 +1782,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1780,7 +1815,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123928379</v>
+        <v>123933492</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1816,14 +1851,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497732</v>
+        <v>497103</v>
       </c>
       <c r="R10" t="n">
-        <v>7068101</v>
+        <v>7067696</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1855,7 +1890,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1865,7 +1900,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1917,7 +1952,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123928803</v>
+        <v>123934255</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1953,17 +1988,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497932</v>
+        <v>496932</v>
       </c>
       <c r="R11" t="n">
-        <v>7068202</v>
+        <v>7067736</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1992,7 +2027,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2002,12 +2037,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2021,7 +2051,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2059,10 +2089,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123934742</v>
+        <v>123926190</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2075,47 +2105,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497184</v>
+        <v>497654</v>
       </c>
       <c r="R12" t="n">
-        <v>7067677</v>
+        <v>7067926</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2144,7 +2164,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2154,12 +2174,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2173,7 +2188,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2191,7 +2226,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123927679</v>
+        <v>123934085</v>
       </c>
       <c r="B13" t="n">
         <v>57883</v>
@@ -2246,14 +2281,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497679</v>
+        <v>496980</v>
       </c>
       <c r="R13" t="n">
-        <v>7068046</v>
+        <v>7067690</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -2285,7 +2320,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2295,12 +2330,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2332,7 +2367,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123934022</v>
+        <v>123933086</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2372,13 +2407,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496970</v>
+        <v>497126</v>
       </c>
       <c r="R14" t="n">
-        <v>7067716</v>
+        <v>7067709</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2407,7 +2442,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2417,12 +2452,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2474,10 +2504,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123927991</v>
+        <v>123933142</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2486,51 +2516,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497659</v>
+        <v>497133</v>
       </c>
       <c r="R15" t="n">
-        <v>7068053</v>
+        <v>7067678</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2559,7 +2584,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2569,12 +2594,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2588,27 +2608,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2626,10 +2646,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123931528</v>
+        <v>123933859</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2642,47 +2662,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497563</v>
+        <v>497016</v>
       </c>
       <c r="R16" t="n">
-        <v>7067965</v>
+        <v>7067743</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2711,7 +2721,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2721,12 +2731,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2755,12 +2765,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2778,10 +2788,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123934255</v>
+        <v>123927991</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2794,37 +2804,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496932</v>
+        <v>497659</v>
       </c>
       <c r="R17" t="n">
-        <v>7067736</v>
+        <v>7068053</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2853,7 +2873,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2863,7 +2883,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2892,12 +2917,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2915,7 +2940,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123933962</v>
+        <v>123933774</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2955,13 +2980,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496999</v>
+        <v>497066</v>
       </c>
       <c r="R18" t="n">
-        <v>7067688</v>
+        <v>7067728</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2990,7 +3015,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3000,7 +3025,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3014,7 +3039,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3052,7 +3077,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123926190</v>
+        <v>123928803</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3092,13 +3117,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497654</v>
+        <v>497932</v>
       </c>
       <c r="R19" t="n">
-        <v>7067926</v>
+        <v>7068202</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3127,7 +3152,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3137,7 +3162,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3189,10 +3219,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123929190</v>
+        <v>123932682</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3205,34 +3235,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497832</v>
+        <v>497368</v>
       </c>
       <c r="R20" t="n">
-        <v>7067981</v>
+        <v>7067763</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -3264,7 +3299,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3274,12 +3309,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3298,22 +3328,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3331,10 +3361,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123925995</v>
+        <v>123934742</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3347,37 +3377,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497628</v>
+        <v>497184</v>
       </c>
       <c r="R21" t="n">
-        <v>7067895</v>
+        <v>7067677</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3406,7 +3446,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3416,7 +3456,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3430,27 +3475,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3468,10 +3493,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123935202</v>
+        <v>123927679</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3480,31 +3505,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3513,13 +3552,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497524</v>
+        <v>497679</v>
       </c>
       <c r="R22" t="n">
-        <v>7067827</v>
+        <v>7068046</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3548,7 +3587,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3558,7 +3597,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3573,26 +3617,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3610,7 +3634,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123925768</v>
+        <v>123928438</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3650,13 +3674,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497652</v>
+        <v>497801</v>
       </c>
       <c r="R23" t="n">
-        <v>7067869</v>
+        <v>7068154</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3685,7 +3709,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,7 +3719,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3747,10 +3771,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123929459</v>
+        <v>123926766</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3763,32 +3787,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3797,13 +3816,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497843</v>
+        <v>497661</v>
       </c>
       <c r="R24" t="n">
-        <v>7067903</v>
+        <v>7067931</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3832,7 +3851,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,12 +3861,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3876,12 +3895,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3899,10 +3918,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931684</v>
+        <v>123927550</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3915,47 +3934,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497576</v>
+        <v>497670</v>
       </c>
       <c r="R25" t="n">
-        <v>7067995</v>
+        <v>7068014</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3984,7 +3993,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3994,12 +4003,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4028,12 +4032,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4051,10 +4055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123932969</v>
+        <v>123932608</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4067,47 +4071,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497236</v>
+        <v>497492</v>
       </c>
       <c r="R26" t="n">
-        <v>7067739</v>
+        <v>7067833</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4136,7 +4130,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4146,12 +4140,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4166,6 +4155,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4183,10 +4192,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123934908</v>
+        <v>123934349</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4199,42 +4208,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497399</v>
+        <v>496957</v>
       </c>
       <c r="R27" t="n">
-        <v>7067620</v>
+        <v>7067780</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4263,7 +4267,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4302,12 +4306,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4325,10 +4329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123928741</v>
+        <v>123925768</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4337,60 +4341,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497907</v>
+        <v>497652</v>
       </c>
       <c r="R28" t="n">
-        <v>7068146</v>
+        <v>7067869</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4419,7 +4404,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4429,12 +4414,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4449,6 +4429,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123934085</v>
+        <v>123928327</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>56725</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4499,19 +4499,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4521,17 +4512,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496980</v>
+        <v>497712</v>
       </c>
       <c r="R29" t="n">
-        <v>7067690</v>
+        <v>7068103</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4560,7 +4551,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4570,12 +4561,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4607,10 +4598,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123933492</v>
+        <v>123933127</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4623,37 +4614,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497103</v>
+        <v>497133</v>
       </c>
       <c r="R30" t="n">
-        <v>7067696</v>
+        <v>7067678</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4682,7 +4678,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4692,7 +4688,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4711,22 +4707,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4744,10 +4740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123932385</v>
+        <v>123932710</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4760,37 +4756,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497528</v>
+        <v>497376</v>
       </c>
       <c r="R31" t="n">
-        <v>7067930</v>
+        <v>7067768</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4819,7 +4815,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4829,7 +4825,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4881,10 +4877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123932682</v>
+        <v>123929190</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4897,39 +4893,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497368</v>
+        <v>497832</v>
       </c>
       <c r="R32" t="n">
-        <v>7067763</v>
+        <v>7067981</v>
       </c>
       <c r="S32" t="n">
         <v>7</v>
@@ -4961,7 +4952,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4971,7 +4962,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4990,22 +4986,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5023,10 +5019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123933712</v>
+        <v>123928574</v>
       </c>
       <c r="B33" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5039,47 +5035,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497111</v>
+        <v>497848</v>
       </c>
       <c r="R33" t="n">
-        <v>7067721</v>
+        <v>7068101</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5108,7 +5094,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5118,12 +5104,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5137,7 +5118,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5155,10 +5136,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123925602</v>
+        <v>123931684</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5171,16 +5152,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5205,10 +5186,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497599</v>
+        <v>497576</v>
       </c>
       <c r="R34" t="n">
-        <v>7067878</v>
+        <v>7067995</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -5240,7 +5221,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5250,12 +5231,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5284,12 +5265,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5307,10 +5288,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123933127</v>
+        <v>123928858</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5323,42 +5304,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497133</v>
+        <v>497900</v>
       </c>
       <c r="R35" t="n">
-        <v>7067678</v>
+        <v>7068251</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5387,7 +5363,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5397,7 +5373,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5416,22 +5397,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5449,10 +5430,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123929370</v>
+        <v>123928514</v>
       </c>
       <c r="B36" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5461,20 +5442,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5483,24 +5464,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497852</v>
+        <v>497851</v>
       </c>
       <c r="R36" t="n">
-        <v>7067984</v>
+        <v>7068090</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5529,7 +5505,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5539,7 +5515,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5558,22 +5534,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5591,7 +5567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123933859</v>
+        <v>123934442</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -5631,13 +5607,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497016</v>
+        <v>496964</v>
       </c>
       <c r="R37" t="n">
-        <v>7067743</v>
+        <v>7067764</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5666,7 +5642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5676,12 +5652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5733,10 +5704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123929497</v>
+        <v>123928741</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5745,20 +5716,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5766,10 +5737,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5783,13 +5763,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497846</v>
+        <v>497907</v>
       </c>
       <c r="R38" t="n">
-        <v>7067895</v>
+        <v>7068146</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5818,7 +5798,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5828,12 +5808,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5848,26 +5828,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5885,10 +5845,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123927793</v>
+        <v>123929282</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5901,51 +5861,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497653</v>
+        <v>497853</v>
       </c>
       <c r="R39" t="n">
-        <v>7068061</v>
+        <v>7067970</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5974,7 +5920,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5984,12 +5930,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6003,27 +5949,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6041,7 +5987,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123932710</v>
+        <v>123932697</v>
       </c>
       <c r="B40" t="n">
         <v>79892</v>
@@ -6075,19 +6021,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497376</v>
+        <v>497385</v>
       </c>
       <c r="R40" t="n">
-        <v>7067768</v>
+        <v>7067784</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6145,22 +6096,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6178,10 +6129,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123929282</v>
+        <v>123925995</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6194,21 +6145,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6218,13 +6169,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497853</v>
+        <v>497628</v>
       </c>
       <c r="R41" t="n">
-        <v>7067970</v>
+        <v>7067895</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6253,7 +6204,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6263,12 +6214,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6287,22 +6233,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6320,10 +6266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123928574</v>
+        <v>123934022</v>
       </c>
       <c r="B42" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6332,41 +6278,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497848</v>
+        <v>496970</v>
       </c>
       <c r="R42" t="n">
-        <v>7068101</v>
+        <v>7067716</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6395,7 +6341,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6405,7 +6351,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6420,6 +6371,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6437,10 +6408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123934349</v>
+        <v>123934569</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6453,21 +6424,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6477,13 +6448,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496957</v>
+        <v>497124</v>
       </c>
       <c r="R43" t="n">
-        <v>7067780</v>
+        <v>7067682</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6512,7 +6483,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6522,7 +6493,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6536,27 +6507,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6574,10 +6545,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123926766</v>
+        <v>123925387</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6586,31 +6557,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6619,13 +6604,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497661</v>
+        <v>497600</v>
       </c>
       <c r="R44" t="n">
-        <v>7067931</v>
+        <v>7067872</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6652,24 +6637,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6684,26 +6659,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6721,10 +6676,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123933650</v>
+        <v>123933422</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6737,21 +6692,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6766,10 +6721,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497112</v>
+        <v>497077</v>
       </c>
       <c r="R45" t="n">
-        <v>7067726</v>
+        <v>7067679</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6801,7 +6756,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6811,7 +6766,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6825,7 +6780,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6863,10 +6818,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123929301</v>
+        <v>123931616</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6879,42 +6834,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497846</v>
+        <v>497562</v>
       </c>
       <c r="R46" t="n">
-        <v>7067985</v>
+        <v>7067959</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6943,7 +6893,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6953,12 +6903,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7010,10 +6955,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123928438</v>
+        <v>123934908</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7026,37 +6971,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497801</v>
+        <v>497399</v>
       </c>
       <c r="R47" t="n">
-        <v>7068154</v>
+        <v>7067620</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7085,7 +7035,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7095,7 +7045,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7124,12 +7074,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7147,10 +7097,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123928514</v>
+        <v>123925602</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7163,37 +7113,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497851</v>
+        <v>497599</v>
       </c>
       <c r="R48" t="n">
-        <v>7068090</v>
+        <v>7067878</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7222,7 +7182,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7232,7 +7192,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7261,12 +7226,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7284,7 +7249,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123934442</v>
+        <v>123928379</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -7320,14 +7285,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496964</v>
+        <v>497732</v>
       </c>
       <c r="R49" t="n">
-        <v>7067764</v>
+        <v>7068101</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -7359,7 +7324,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7369,7 +7334,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7421,10 +7386,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123927550</v>
+        <v>123932969</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7437,37 +7402,47 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497670</v>
+        <v>497236</v>
       </c>
       <c r="R50" t="n">
-        <v>7068014</v>
+        <v>7067739</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7496,7 +7471,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7506,7 +7481,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7521,26 +7501,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7558,10 +7518,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123928831</v>
+        <v>123925856</v>
       </c>
       <c r="B51" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7570,25 +7530,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7598,13 +7558,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497927</v>
+        <v>497652</v>
       </c>
       <c r="R51" t="n">
-        <v>7068210</v>
+        <v>7067886</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7633,7 +7593,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7643,7 +7603,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7658,6 +7618,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7675,10 +7655,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123934569</v>
+        <v>123935093</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7691,37 +7671,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497124</v>
+        <v>497438</v>
       </c>
       <c r="R52" t="n">
-        <v>7067682</v>
+        <v>7067653</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7750,7 +7735,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7760,7 +7745,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7779,22 +7764,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7812,10 +7797,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123933086</v>
+        <v>123933650</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7828,37 +7813,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497126</v>
+        <v>497112</v>
       </c>
       <c r="R53" t="n">
-        <v>7067709</v>
+        <v>7067726</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7887,7 +7877,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7897,7 +7887,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7911,7 +7901,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7926,12 +7916,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7949,10 +7939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123932608</v>
+        <v>123933712</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7961,41 +7951,51 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497492</v>
+        <v>497111</v>
       </c>
       <c r="R54" t="n">
-        <v>7067833</v>
+        <v>7067721</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8034,7 +8034,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8048,27 +8053,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8086,10 +8071,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123933774</v>
+        <v>123931528</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8102,37 +8087,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497066</v>
+        <v>497563</v>
       </c>
       <c r="R55" t="n">
-        <v>7067728</v>
+        <v>7067965</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8161,7 +8156,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8171,7 +8166,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8223,7 +8223,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123933422</v>
+        <v>123935202</v>
       </c>
       <c r="B56" t="n">
         <v>91008</v>
@@ -8264,17 +8264,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497077</v>
+        <v>497524</v>
       </c>
       <c r="R56" t="n">
-        <v>7067679</v>
+        <v>7067827</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123948084</v>
+        <v>123948037</v>
       </c>
       <c r="B57" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497101</v>
+        <v>497443</v>
       </c>
       <c r="R57" t="n">
-        <v>7067728</v>
+        <v>7067840</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123948079</v>
+        <v>123948070</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497614</v>
+        <v>497876</v>
       </c>
       <c r="R58" t="n">
-        <v>7067898</v>
+        <v>7068110</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8574,7 +8574,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123948050</v>
+        <v>123948068</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496963</v>
+        <v>497549</v>
       </c>
       <c r="R59" t="n">
-        <v>7067823</v>
+        <v>7067939</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123948057</v>
+        <v>123948060</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497142</v>
+        <v>497140</v>
       </c>
       <c r="R60" t="n">
-        <v>7068071</v>
+        <v>7067713</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123948069</v>
+        <v>123948055</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -8828,10 +8828,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497544</v>
+        <v>497062</v>
       </c>
       <c r="R61" t="n">
-        <v>7067872</v>
+        <v>7068109</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123948059</v>
+        <v>123948056</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497338</v>
+        <v>497093</v>
       </c>
       <c r="R62" t="n">
-        <v>7068065</v>
+        <v>7068094</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9002,7 +9002,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123948053</v>
+        <v>123948061</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497052</v>
+        <v>497152</v>
       </c>
       <c r="R63" t="n">
-        <v>7067797</v>
+        <v>7067720</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9109,7 +9109,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948054</v>
+        <v>123948075</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497062</v>
+        <v>497629</v>
       </c>
       <c r="R64" t="n">
-        <v>7068118</v>
+        <v>7068330</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9216,10 +9216,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948085</v>
+        <v>123948053</v>
       </c>
       <c r="B65" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9232,21 +9232,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497243</v>
+        <v>497052</v>
       </c>
       <c r="R65" t="n">
-        <v>7067786</v>
+        <v>7067797</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9292,6 +9292,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9318,7 +9323,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948055</v>
+        <v>123948074</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -9358,10 +9363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497062</v>
+        <v>497809</v>
       </c>
       <c r="R66" t="n">
-        <v>7068109</v>
+        <v>7068221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9425,7 +9430,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948068</v>
+        <v>123948051</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -9465,10 +9470,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497549</v>
+        <v>496962</v>
       </c>
       <c r="R67" t="n">
-        <v>7067939</v>
+        <v>7067810</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9505,7 +9510,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9532,7 +9537,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948077</v>
+        <v>123948079</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -9572,10 +9577,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497583</v>
+        <v>497614</v>
       </c>
       <c r="R68" t="n">
-        <v>7068342</v>
+        <v>7067898</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9612,7 +9617,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9639,7 +9644,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948076</v>
+        <v>123948065</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -9679,10 +9684,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497599</v>
+        <v>497547</v>
       </c>
       <c r="R69" t="n">
-        <v>7068342</v>
+        <v>7068008</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9719,7 +9724,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9746,10 +9751,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948065</v>
+        <v>123948081</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9758,25 +9763,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9786,10 +9791,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497547</v>
+        <v>497267</v>
       </c>
       <c r="R70" t="n">
-        <v>7068008</v>
+        <v>7068098</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9822,11 +9827,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948082</v>
+        <v>123948083</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9865,25 +9865,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497300</v>
+        <v>497012</v>
       </c>
       <c r="R71" t="n">
-        <v>7068117</v>
+        <v>7067783</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948064</v>
+        <v>123948066</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497471</v>
+        <v>497568</v>
       </c>
       <c r="R72" t="n">
-        <v>7067944</v>
+        <v>7067974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10062,7 +10062,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948071</v>
+        <v>123948062</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497830</v>
+        <v>497431</v>
       </c>
       <c r="R73" t="n">
-        <v>7068267</v>
+        <v>7067834</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10169,7 +10169,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948070</v>
+        <v>123948048</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497876</v>
+        <v>497417</v>
       </c>
       <c r="R74" t="n">
-        <v>7068110</v>
+        <v>7067613</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10276,7 +10276,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948041</v>
+        <v>123948058</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497578</v>
+        <v>497156</v>
       </c>
       <c r="R75" t="n">
-        <v>7067475</v>
+        <v>7067976</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10383,7 +10383,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948056</v>
+        <v>123948059</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497093</v>
+        <v>497338</v>
       </c>
       <c r="R76" t="n">
-        <v>7068094</v>
+        <v>7068065</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10490,10 +10490,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948081</v>
+        <v>123948067</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10502,25 +10502,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497267</v>
+        <v>497567</v>
       </c>
       <c r="R77" t="n">
-        <v>7068098</v>
+        <v>7067939</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10566,6 +10566,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10699,7 +10704,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948067</v>
+        <v>123948057</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -10739,10 +10744,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497567</v>
+        <v>497142</v>
       </c>
       <c r="R79" t="n">
-        <v>7067939</v>
+        <v>7068071</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10779,7 +10784,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10806,7 +10811,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948078</v>
+        <v>123948063</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -10846,10 +10851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497569</v>
+        <v>497448</v>
       </c>
       <c r="R80" t="n">
-        <v>7068352</v>
+        <v>7067857</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10913,7 +10918,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948066</v>
+        <v>123948064</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -10953,10 +10958,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497568</v>
+        <v>497471</v>
       </c>
       <c r="R81" t="n">
-        <v>7067974</v>
+        <v>7067944</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10993,7 +10998,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11020,7 +11025,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948062</v>
+        <v>123948076</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11060,10 +11065,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497431</v>
+        <v>497599</v>
       </c>
       <c r="R82" t="n">
-        <v>7067834</v>
+        <v>7068342</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11127,7 +11132,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948051</v>
+        <v>123948073</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11167,10 +11172,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496962</v>
+        <v>497810</v>
       </c>
       <c r="R83" t="n">
-        <v>7067810</v>
+        <v>7068216</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11234,10 +11239,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948061</v>
+        <v>123948084</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11250,21 +11255,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11274,10 +11279,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497152</v>
+        <v>497101</v>
       </c>
       <c r="R84" t="n">
-        <v>7067720</v>
+        <v>7067728</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11310,11 +11315,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11341,10 +11341,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948083</v>
+        <v>123948050</v>
       </c>
       <c r="B85" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11357,21 +11357,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11381,10 +11381,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497012</v>
+        <v>496963</v>
       </c>
       <c r="R85" t="n">
-        <v>7067783</v>
+        <v>7067823</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11417,6 +11417,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11443,7 +11448,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948060</v>
+        <v>123948071</v>
       </c>
       <c r="B86" t="n">
         <v>57513</v>
@@ -11483,10 +11488,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497140</v>
+        <v>497830</v>
       </c>
       <c r="R86" t="n">
-        <v>7067713</v>
+        <v>7068267</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11550,10 +11555,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948048</v>
+        <v>123948085</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11566,21 +11571,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11590,10 +11595,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497417</v>
+        <v>497243</v>
       </c>
       <c r="R87" t="n">
-        <v>7067613</v>
+        <v>7067786</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11626,11 +11631,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948075</v>
+        <v>123948077</v>
       </c>
       <c r="B88" t="n">
         <v>57513</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497629</v>
+        <v>497583</v>
       </c>
       <c r="R88" t="n">
-        <v>7068330</v>
+        <v>7068342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11764,10 +11764,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948058</v>
+        <v>123948082</v>
       </c>
       <c r="B89" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11776,25 +11776,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497156</v>
+        <v>497300</v>
       </c>
       <c r="R89" t="n">
-        <v>7067976</v>
+        <v>7068117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11840,11 +11840,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11871,10 +11866,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948037</v>
+        <v>123948054</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11887,21 +11882,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11911,10 +11906,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497443</v>
+        <v>497062</v>
       </c>
       <c r="R90" t="n">
-        <v>7067840</v>
+        <v>7068118</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11947,6 +11942,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11973,7 +11973,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948074</v>
+        <v>123948078</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497809</v>
+        <v>497569</v>
       </c>
       <c r="R91" t="n">
-        <v>7068221</v>
+        <v>7068352</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12187,7 +12187,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948063</v>
+        <v>123948041</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497448</v>
+        <v>497578</v>
       </c>
       <c r="R93" t="n">
-        <v>7067857</v>
+        <v>7067475</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12294,7 +12294,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948073</v>
+        <v>123948069</v>
       </c>
       <c r="B94" t="n">
         <v>57513</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497810</v>
+        <v>497544</v>
       </c>
       <c r="R94" t="n">
-        <v>7068216</v>
+        <v>7067872</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123934404</v>
+        <v>123929700</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12437,7 +12437,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -12447,17 +12447,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>496972</v>
+        <v>497829</v>
       </c>
       <c r="R95" t="n">
-        <v>7067780</v>
+        <v>7067835</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -12705,10 +12705,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123934695</v>
+        <v>123934404</v>
       </c>
       <c r="B97" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12717,31 +12717,36 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12750,13 +12755,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497164</v>
+        <v>496972</v>
       </c>
       <c r="R97" t="n">
-        <v>7067665</v>
+        <v>7067780</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12785,7 +12790,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12795,12 +12800,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12814,27 +12819,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12852,7 +12857,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123931433</v>
+        <v>123931338</v>
       </c>
       <c r="B98" t="n">
         <v>57513</v>
@@ -12902,13 +12907,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497554</v>
+        <v>497552</v>
       </c>
       <c r="R98" t="n">
-        <v>7067886</v>
+        <v>7067881</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12937,7 +12942,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12947,12 +12952,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13004,7 +13009,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123931338</v>
+        <v>123932552</v>
       </c>
       <c r="B99" t="n">
         <v>57513</v>
@@ -13043,24 +13048,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497552</v>
+        <v>497461</v>
       </c>
       <c r="R99" t="n">
-        <v>7067881</v>
+        <v>7067890</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13287,10 +13287,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123929700</v>
+        <v>123929267</v>
       </c>
       <c r="B101" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13303,47 +13303,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497829</v>
+        <v>497833</v>
       </c>
       <c r="R101" t="n">
-        <v>7067835</v>
+        <v>7067988</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13372,7 +13367,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13382,12 +13377,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13401,27 +13396,27 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13439,10 +13434,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929267</v>
+        <v>123931433</v>
       </c>
       <c r="B102" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13455,27 +13450,32 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13484,13 +13484,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497833</v>
+        <v>497554</v>
       </c>
       <c r="R102" t="n">
-        <v>7067988</v>
+        <v>7067886</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13529,12 +13529,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13553,22 +13553,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13586,10 +13586,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123932552</v>
+        <v>123934695</v>
       </c>
       <c r="B103" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13598,46 +13598,46 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497461</v>
+        <v>497164</v>
       </c>
       <c r="R103" t="n">
-        <v>7067890</v>
+        <v>7067665</v>
       </c>
       <c r="S103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13695,27 +13695,27 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123936336</v>
+        <v>123935469</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,47 +13886,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497296</v>
+        <v>497429</v>
       </c>
       <c r="R105" t="n">
-        <v>7067024</v>
+        <v>7067378</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13955,7 +13945,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13965,12 +13955,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13999,12 +13984,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14022,7 +14007,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935469</v>
+        <v>123935971</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -14062,13 +14047,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497429</v>
+        <v>497477</v>
       </c>
       <c r="R106" t="n">
-        <v>7067378</v>
+        <v>7067373</v>
       </c>
       <c r="S106" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14097,7 +14082,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14107,7 +14092,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14159,10 +14144,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935511</v>
+        <v>123935623</v>
       </c>
       <c r="B107" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14175,47 +14160,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497429</v>
+        <v>497400</v>
       </c>
       <c r="R107" t="n">
-        <v>7067368</v>
+        <v>7067320</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14244,7 +14219,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14254,7 +14229,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14283,12 +14258,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14306,7 +14281,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123936388</v>
+        <v>123935892</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -14346,13 +14321,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497347</v>
+        <v>497488</v>
       </c>
       <c r="R108" t="n">
-        <v>7067031</v>
+        <v>7067338</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14381,7 +14356,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14391,7 +14366,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14443,10 +14418,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123935971</v>
+        <v>123936336</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14459,37 +14434,47 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497477</v>
+        <v>497296</v>
       </c>
       <c r="R109" t="n">
-        <v>7067373</v>
+        <v>7067024</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14518,7 +14503,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14528,7 +14513,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14557,12 +14547,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14580,10 +14570,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935892</v>
+        <v>123935511</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14596,37 +14586,47 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497488</v>
+        <v>497429</v>
       </c>
       <c r="R110" t="n">
-        <v>7067338</v>
+        <v>7067368</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14717,7 +14717,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935623</v>
+        <v>123935662</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -14757,13 +14757,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497400</v>
+        <v>497407</v>
       </c>
       <c r="R111" t="n">
-        <v>7067320</v>
+        <v>7067289</v>
       </c>
       <c r="S111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14854,7 +14854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123935662</v>
+        <v>123936388</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -14894,13 +14894,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497407</v>
+        <v>497347</v>
       </c>
       <c r="R112" t="n">
-        <v>7067289</v>
+        <v>7067031</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14991,10 +14991,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948080</v>
+        <v>123948045</v>
       </c>
       <c r="B113" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -15007,16 +15007,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497370</v>
+        <v>497439</v>
       </c>
       <c r="R113" t="n">
-        <v>7067042</v>
+        <v>7067336</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948042</v>
+        <v>123948039</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497448</v>
+        <v>497241</v>
       </c>
       <c r="R114" t="n">
-        <v>7067435</v>
+        <v>7067063</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,10 +15205,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948039</v>
+        <v>123948080</v>
       </c>
       <c r="B115" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15221,16 +15221,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497241</v>
+        <v>497370</v>
       </c>
       <c r="R115" t="n">
-        <v>7067063</v>
+        <v>7067042</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948047</v>
+        <v>123948042</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497422</v>
+        <v>497448</v>
       </c>
       <c r="R117" t="n">
-        <v>7067360</v>
+        <v>7067435</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948038</v>
+        <v>123948047</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497227</v>
+        <v>497422</v>
       </c>
       <c r="R118" t="n">
-        <v>7067047</v>
+        <v>7067360</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15633,7 +15633,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948045</v>
+        <v>123948038</v>
       </c>
       <c r="B119" t="n">
         <v>57513</v>
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497439</v>
+        <v>497227</v>
       </c>
       <c r="R119" t="n">
-        <v>7067336</v>
+        <v>7067047</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123929459</v>
+        <v>123928438</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497843</v>
+        <v>497801</v>
       </c>
       <c r="R2" t="n">
-        <v>7067903</v>
+        <v>7068154</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123929301</v>
+        <v>123925768</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497846</v>
+        <v>497652</v>
       </c>
       <c r="R3" t="n">
-        <v>7067985</v>
+        <v>7067869</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -974,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123928831</v>
+        <v>123929301</v>
       </c>
       <c r="B4" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,38 +961,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497927</v>
+        <v>497846</v>
       </c>
       <c r="R4" t="n">
-        <v>7068210</v>
+        <v>7067985</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -1049,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,6 +1059,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123932385</v>
+        <v>123928831</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,25 +1108,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1131,13 +1136,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497528</v>
+        <v>497927</v>
       </c>
       <c r="R5" t="n">
-        <v>7067930</v>
+        <v>7068210</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,26 +1196,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,7 +1213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933962</v>
+        <v>123926766</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1262,19 +1247,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496999</v>
+        <v>497661</v>
       </c>
       <c r="R6" t="n">
-        <v>7067688</v>
+        <v>7067931</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1303,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1313,7 +1303,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123929497</v>
+        <v>123927550</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,47 +1376,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497846</v>
+        <v>497670</v>
       </c>
       <c r="R7" t="n">
-        <v>7067895</v>
+        <v>7068014</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,7 +1435,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1460,12 +1445,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,12 +1474,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,10 +1497,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123927793</v>
+        <v>123934349</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1533,51 +1513,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497653</v>
+        <v>496957</v>
       </c>
       <c r="R8" t="n">
-        <v>7068061</v>
+        <v>7067780</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1606,7 +1572,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1616,12 +1582,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1635,7 +1596,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1650,12 +1611,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1673,10 +1634,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123929370</v>
+        <v>123934742</v>
       </c>
       <c r="B9" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1685,46 +1646,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497852</v>
+        <v>497184</v>
       </c>
       <c r="R9" t="n">
-        <v>7067984</v>
+        <v>7067677</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1753,7 +1719,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1763,7 +1729,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1777,27 +1748,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1815,10 +1766,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123933492</v>
+        <v>123935093</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1831,37 +1782,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497103</v>
+        <v>497438</v>
       </c>
       <c r="R10" t="n">
-        <v>7067696</v>
+        <v>7067653</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1890,7 +1846,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1900,7 +1856,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1914,7 +1870,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1929,12 +1885,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1952,10 +1908,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123934255</v>
+        <v>123933712</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1964,41 +1920,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496932</v>
+        <v>497111</v>
       </c>
       <c r="R11" t="n">
-        <v>7067736</v>
+        <v>7067721</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2027,7 +1993,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2037,7 +2003,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2052,26 +2023,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2089,10 +2040,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123926190</v>
+        <v>123928574</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2101,25 +2052,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2129,13 +2080,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497654</v>
+        <v>497848</v>
       </c>
       <c r="R12" t="n">
-        <v>7067926</v>
+        <v>7068101</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2164,7 +2115,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2174,7 +2125,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2189,26 +2140,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2226,10 +2157,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123934085</v>
+        <v>123932385</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2238,60 +2169,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496980</v>
+        <v>497528</v>
       </c>
       <c r="R13" t="n">
-        <v>7067690</v>
+        <v>7067930</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2320,7 +2232,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2330,12 +2242,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2350,6 +2257,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2367,10 +2294,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123933086</v>
+        <v>123929497</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2383,37 +2310,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497126</v>
+        <v>497846</v>
       </c>
       <c r="R14" t="n">
-        <v>7067709</v>
+        <v>7067895</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2442,7 +2379,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2452,7 +2389,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2481,12 +2423,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2504,10 +2446,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123933142</v>
+        <v>123928741</v>
       </c>
       <c r="B15" t="n">
-        <v>79927</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2520,42 +2462,56 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497133</v>
+        <v>497907</v>
       </c>
       <c r="R15" t="n">
-        <v>7067678</v>
+        <v>7068146</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2584,7 +2540,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2594,7 +2550,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2609,26 +2570,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2646,10 +2587,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123933859</v>
+        <v>123931684</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2662,37 +2603,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497016</v>
+        <v>497576</v>
       </c>
       <c r="R16" t="n">
-        <v>7067743</v>
+        <v>7067995</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2721,7 +2672,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2731,12 +2682,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2765,12 +2716,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2940,10 +2891,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123933774</v>
+        <v>123925387</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2952,41 +2903,60 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497066</v>
+        <v>497600</v>
       </c>
       <c r="R18" t="n">
-        <v>7067728</v>
+        <v>7067872</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3013,19 +2983,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:57</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3039,27 +3004,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3077,7 +3022,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123928803</v>
+        <v>123933086</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3113,17 +3058,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497932</v>
+        <v>497126</v>
       </c>
       <c r="R19" t="n">
-        <v>7068202</v>
+        <v>7067709</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3152,7 +3097,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3162,12 +3107,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3219,10 +3159,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123932682</v>
+        <v>123925995</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3235,42 +3175,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497368</v>
+        <v>497628</v>
       </c>
       <c r="R20" t="n">
-        <v>7067763</v>
+        <v>7067895</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3299,7 +3234,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3309,7 +3244,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3328,22 +3263,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3361,10 +3296,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123934742</v>
+        <v>123934022</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3377,47 +3312,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497184</v>
+        <v>496970</v>
       </c>
       <c r="R21" t="n">
-        <v>7067677</v>
+        <v>7067716</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3446,7 +3371,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3456,12 +3381,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3475,7 +3400,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3493,10 +3438,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123927679</v>
+        <v>123932682</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3505,60 +3450,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497679</v>
+        <v>497368</v>
       </c>
       <c r="R22" t="n">
-        <v>7068046</v>
+        <v>7067763</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3587,7 +3518,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3597,12 +3528,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3617,6 +3543,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3634,7 +3580,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123928438</v>
+        <v>123928379</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3674,13 +3620,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497801</v>
+        <v>497732</v>
       </c>
       <c r="R23" t="n">
-        <v>7068154</v>
+        <v>7068101</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3709,7 +3655,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3719,7 +3665,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3771,10 +3717,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123926766</v>
+        <v>123932697</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3787,42 +3733,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497661</v>
+        <v>497385</v>
       </c>
       <c r="R24" t="n">
-        <v>7067931</v>
+        <v>7067784</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3851,7 +3797,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3861,12 +3807,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3885,22 +3826,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3918,10 +3859,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123927550</v>
+        <v>123927793</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3934,37 +3875,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497670</v>
+        <v>497653</v>
       </c>
       <c r="R25" t="n">
-        <v>7068014</v>
+        <v>7068061</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3993,7 +3948,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4003,7 +3958,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4017,7 +3977,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4032,12 +3992,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4055,7 +4015,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123932608</v>
+        <v>123928514</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -4095,13 +4055,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497492</v>
+        <v>497851</v>
       </c>
       <c r="R26" t="n">
-        <v>7067833</v>
+        <v>7068090</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4130,7 +4090,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4140,7 +4100,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4192,10 +4152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123934349</v>
+        <v>123927679</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4204,41 +4164,60 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496957</v>
+        <v>497679</v>
       </c>
       <c r="R27" t="n">
-        <v>7067780</v>
+        <v>7068046</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4267,7 +4246,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4277,7 +4256,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4292,26 +4276,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4329,7 +4293,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123925768</v>
+        <v>123934255</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -4365,14 +4329,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497652</v>
+        <v>496932</v>
       </c>
       <c r="R28" t="n">
-        <v>7067869</v>
+        <v>7067736</v>
       </c>
       <c r="S28" t="n">
         <v>12</v>
@@ -4404,7 +4368,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4414,7 +4378,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4428,7 +4392,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4466,10 +4430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123928327</v>
+        <v>123929190</v>
       </c>
       <c r="B29" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4478,51 +4442,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497712</v>
+        <v>497832</v>
       </c>
       <c r="R29" t="n">
-        <v>7068103</v>
+        <v>7067981</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4551,7 +4505,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4561,12 +4515,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4581,6 +4535,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4740,7 +4714,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123932710</v>
+        <v>123929282</v>
       </c>
       <c r="B31" t="n">
         <v>79892</v>
@@ -4776,14 +4750,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497376</v>
+        <v>497853</v>
       </c>
       <c r="R31" t="n">
-        <v>7067768</v>
+        <v>7067970</v>
       </c>
       <c r="S31" t="n">
         <v>7</v>
@@ -4815,7 +4789,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4825,7 +4799,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4844,22 +4823,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4877,7 +4856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123929190</v>
+        <v>123925856</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4917,13 +4896,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497832</v>
+        <v>497652</v>
       </c>
       <c r="R32" t="n">
-        <v>7067981</v>
+        <v>7067886</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4952,7 +4931,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4962,12 +4941,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5019,10 +4993,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123928574</v>
+        <v>123932608</v>
       </c>
       <c r="B33" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5031,25 +5005,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5059,13 +5033,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497848</v>
+        <v>497492</v>
       </c>
       <c r="R33" t="n">
-        <v>7068101</v>
+        <v>7067833</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5094,7 +5068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5104,7 +5078,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5119,6 +5093,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5136,10 +5130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123931684</v>
+        <v>123931616</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5152,47 +5146,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497576</v>
+        <v>497562</v>
       </c>
       <c r="R34" t="n">
-        <v>7067995</v>
+        <v>7067959</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5221,7 +5205,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5231,12 +5215,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5265,12 +5244,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5288,10 +5267,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123928858</v>
+        <v>123933422</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5304,34 +5283,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497900</v>
+        <v>497077</v>
       </c>
       <c r="R35" t="n">
-        <v>7068251</v>
+        <v>7067679</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -5363,7 +5347,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5373,12 +5357,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5407,12 +5386,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5430,10 +5409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123928514</v>
+        <v>123931528</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5446,34 +5425,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497851</v>
+        <v>497563</v>
       </c>
       <c r="R36" t="n">
-        <v>7068090</v>
+        <v>7067965</v>
       </c>
       <c r="S36" t="n">
         <v>8</v>
@@ -5505,7 +5494,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5515,7 +5504,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5544,12 +5538,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5567,10 +5561,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123934442</v>
+        <v>123928327</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>56725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5579,41 +5573,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496964</v>
+        <v>497712</v>
       </c>
       <c r="R37" t="n">
-        <v>7067764</v>
+        <v>7068103</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5642,7 +5646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5652,7 +5656,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5667,26 +5676,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5704,10 +5693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123928741</v>
+        <v>123933650</v>
       </c>
       <c r="B38" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5716,60 +5705,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497907</v>
+        <v>497112</v>
       </c>
       <c r="R38" t="n">
-        <v>7068146</v>
+        <v>7067726</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5798,7 +5773,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5808,12 +5783,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5827,7 +5797,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5845,10 +5835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123929282</v>
+        <v>123928803</v>
       </c>
       <c r="B39" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5861,21 +5851,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5885,13 +5875,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497853</v>
+        <v>497932</v>
       </c>
       <c r="R39" t="n">
-        <v>7067970</v>
+        <v>7068202</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5920,7 +5910,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5930,12 +5920,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5954,22 +5944,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5987,10 +5977,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123932697</v>
+        <v>123925602</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6003,39 +5993,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497385</v>
+        <v>497599</v>
       </c>
       <c r="R40" t="n">
-        <v>7067784</v>
+        <v>7067878</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6067,7 +6062,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6077,7 +6072,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6096,22 +6096,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123925995</v>
+        <v>123933142</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6141,41 +6141,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497628</v>
+        <v>497133</v>
       </c>
       <c r="R41" t="n">
-        <v>7067895</v>
+        <v>7067678</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6214,7 +6219,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6233,22 +6238,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6266,7 +6271,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123934022</v>
+        <v>123933859</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -6306,13 +6311,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496970</v>
+        <v>497016</v>
       </c>
       <c r="R42" t="n">
-        <v>7067716</v>
+        <v>7067743</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6351,7 +6356,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6408,10 +6413,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123934569</v>
+        <v>123932710</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6424,21 +6429,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6448,13 +6453,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497124</v>
+        <v>497376</v>
       </c>
       <c r="R43" t="n">
-        <v>7067682</v>
+        <v>7067768</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6483,7 +6488,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6493,7 +6498,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6507,27 +6512,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6545,10 +6550,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123925387</v>
+        <v>123935202</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6557,45 +6562,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6604,13 +6595,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497600</v>
+        <v>497524</v>
       </c>
       <c r="R44" t="n">
-        <v>7067872</v>
+        <v>7067827</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6637,14 +6628,19 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6659,6 +6655,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6676,10 +6692,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123933422</v>
+        <v>123934442</v>
       </c>
       <c r="B45" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6692,42 +6708,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497077</v>
+        <v>496964</v>
       </c>
       <c r="R45" t="n">
-        <v>7067679</v>
+        <v>7067764</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6756,7 +6767,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6766,7 +6777,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6795,12 +6806,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6818,7 +6829,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123931616</v>
+        <v>123933774</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -6854,14 +6865,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497562</v>
+        <v>497066</v>
       </c>
       <c r="R46" t="n">
-        <v>7067959</v>
+        <v>7067728</v>
       </c>
       <c r="S46" t="n">
         <v>11</v>
@@ -6893,7 +6904,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6903,7 +6914,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6917,7 +6928,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6955,10 +6966,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123934908</v>
+        <v>123934569</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6971,39 +6982,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497399</v>
+        <v>497124</v>
       </c>
       <c r="R47" t="n">
-        <v>7067620</v>
+        <v>7067682</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -7035,7 +7041,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7045,7 +7051,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7059,27 +7065,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7097,10 +7103,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123925602</v>
+        <v>123933962</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7113,47 +7119,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497599</v>
+        <v>496999</v>
       </c>
       <c r="R48" t="n">
-        <v>7067878</v>
+        <v>7067688</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7182,7 +7178,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7192,12 +7188,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7226,12 +7217,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7249,7 +7240,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123928379</v>
+        <v>123933492</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -7285,14 +7276,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497732</v>
+        <v>497103</v>
       </c>
       <c r="R49" t="n">
-        <v>7068101</v>
+        <v>7067696</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -7324,7 +7315,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7334,7 +7325,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7386,10 +7377,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123932969</v>
+        <v>123929459</v>
       </c>
       <c r="B50" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7402,16 +7393,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7422,7 +7413,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7432,17 +7423,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497236</v>
+        <v>497843</v>
       </c>
       <c r="R50" t="n">
-        <v>7067739</v>
+        <v>7067903</v>
       </c>
       <c r="S50" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7471,7 +7462,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7481,12 +7472,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7501,6 +7492,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7518,10 +7529,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123925856</v>
+        <v>123934908</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7534,37 +7545,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497652</v>
+        <v>497399</v>
       </c>
       <c r="R51" t="n">
-        <v>7067886</v>
+        <v>7067620</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7593,7 +7609,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7603,7 +7619,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7632,12 +7648,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7655,10 +7671,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123935093</v>
+        <v>123932969</v>
       </c>
       <c r="B52" t="n">
-        <v>91008</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7671,27 +7687,32 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7700,13 +7721,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497438</v>
+        <v>497236</v>
       </c>
       <c r="R52" t="n">
-        <v>7067653</v>
+        <v>7067739</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7735,7 +7756,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7745,7 +7766,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7759,27 +7785,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7797,10 +7803,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123933650</v>
+        <v>123934085</v>
       </c>
       <c r="B53" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7809,31 +7815,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7842,13 +7862,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497112</v>
+        <v>496980</v>
       </c>
       <c r="R53" t="n">
-        <v>7067726</v>
+        <v>7067690</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7877,7 +7897,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7887,7 +7907,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7901,27 +7926,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7939,10 +7944,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123933712</v>
+        <v>123928858</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7951,51 +7956,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497111</v>
+        <v>497900</v>
       </c>
       <c r="R54" t="n">
-        <v>7067721</v>
+        <v>7068251</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8024,7 +8019,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8034,12 +8029,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8053,7 +8048,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8071,10 +8086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123931528</v>
+        <v>123926190</v>
       </c>
       <c r="B55" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8087,47 +8102,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497563</v>
+        <v>497654</v>
       </c>
       <c r="R55" t="n">
-        <v>7067965</v>
+        <v>7067926</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8156,7 +8161,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8166,12 +8171,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123935202</v>
+        <v>123929370</v>
       </c>
       <c r="B56" t="n">
-        <v>91008</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8235,31 +8235,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -8268,13 +8268,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497524</v>
+        <v>497852</v>
       </c>
       <c r="R56" t="n">
-        <v>7067827</v>
+        <v>7067984</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8332,22 +8332,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123948037</v>
+        <v>123948074</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497443</v>
+        <v>497809</v>
       </c>
       <c r="R57" t="n">
-        <v>7067840</v>
+        <v>7068221</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8441,6 +8441,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8467,7 +8472,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123948070</v>
+        <v>123948064</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8507,10 +8512,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497876</v>
+        <v>497471</v>
       </c>
       <c r="R58" t="n">
-        <v>7068110</v>
+        <v>7067944</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8574,7 +8579,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123948068</v>
+        <v>123948050</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8614,10 +8619,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497549</v>
+        <v>496963</v>
       </c>
       <c r="R59" t="n">
-        <v>7067939</v>
+        <v>7067823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8681,7 +8686,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123948060</v>
+        <v>123948061</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -8721,10 +8726,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497140</v>
+        <v>497152</v>
       </c>
       <c r="R60" t="n">
-        <v>7067713</v>
+        <v>7067720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8788,7 +8793,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123948055</v>
+        <v>123948056</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -8828,10 +8833,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497062</v>
+        <v>497093</v>
       </c>
       <c r="R61" t="n">
-        <v>7068109</v>
+        <v>7068094</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8895,7 +8900,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123948056</v>
+        <v>123948054</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497093</v>
+        <v>497062</v>
       </c>
       <c r="R62" t="n">
-        <v>7068094</v>
+        <v>7068118</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9002,7 +9007,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123948061</v>
+        <v>123948058</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -9042,10 +9047,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497152</v>
+        <v>497156</v>
       </c>
       <c r="R63" t="n">
-        <v>7067720</v>
+        <v>7067976</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9082,7 +9087,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9109,10 +9114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948075</v>
+        <v>123948081</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9121,25 +9126,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9149,10 +9154,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497629</v>
+        <v>497267</v>
       </c>
       <c r="R64" t="n">
-        <v>7068330</v>
+        <v>7068098</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9185,11 +9190,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9216,7 +9216,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948053</v>
+        <v>123948065</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497052</v>
+        <v>497547</v>
       </c>
       <c r="R65" t="n">
-        <v>7067797</v>
+        <v>7068008</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9323,10 +9323,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948074</v>
+        <v>123948083</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9339,21 +9339,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497809</v>
+        <v>497012</v>
       </c>
       <c r="R66" t="n">
-        <v>7068221</v>
+        <v>7067783</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9399,11 +9399,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9430,7 +9425,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948051</v>
+        <v>123948060</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -9470,10 +9465,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496962</v>
+        <v>497140</v>
       </c>
       <c r="R67" t="n">
-        <v>7067810</v>
+        <v>7067713</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9537,7 +9532,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948079</v>
+        <v>123948052</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -9577,10 +9572,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497614</v>
+        <v>496977</v>
       </c>
       <c r="R68" t="n">
-        <v>7067898</v>
+        <v>7067794</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9644,7 +9639,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948065</v>
+        <v>123948048</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -9684,10 +9679,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497547</v>
+        <v>497417</v>
       </c>
       <c r="R69" t="n">
-        <v>7068008</v>
+        <v>7067613</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9724,7 +9719,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9751,10 +9746,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948081</v>
+        <v>123948055</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9763,25 +9758,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9791,10 +9786,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497267</v>
+        <v>497062</v>
       </c>
       <c r="R70" t="n">
-        <v>7068098</v>
+        <v>7068109</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9827,6 +9822,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948083</v>
+        <v>123948075</v>
       </c>
       <c r="B71" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9869,21 +9869,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497012</v>
+        <v>497629</v>
       </c>
       <c r="R71" t="n">
-        <v>7067783</v>
+        <v>7068330</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9929,6 +9929,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9955,10 +9960,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948066</v>
+        <v>123948037</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9971,21 +9976,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9995,10 +10000,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497568</v>
+        <v>497443</v>
       </c>
       <c r="R72" t="n">
-        <v>7067974</v>
+        <v>7067840</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10031,11 +10036,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10062,7 +10062,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948062</v>
+        <v>123948073</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497431</v>
+        <v>497810</v>
       </c>
       <c r="R73" t="n">
-        <v>7067834</v>
+        <v>7068216</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10169,7 +10169,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948048</v>
+        <v>123948076</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497417</v>
+        <v>497599</v>
       </c>
       <c r="R74" t="n">
-        <v>7067613</v>
+        <v>7068342</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10276,7 +10276,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948058</v>
+        <v>123948079</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497156</v>
+        <v>497614</v>
       </c>
       <c r="R75" t="n">
-        <v>7067976</v>
+        <v>7067898</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10383,7 +10383,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948059</v>
+        <v>123948049</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497338</v>
+        <v>496958</v>
       </c>
       <c r="R76" t="n">
-        <v>7068065</v>
+        <v>7067783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10490,7 +10490,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948067</v>
+        <v>123948071</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497567</v>
+        <v>497830</v>
       </c>
       <c r="R77" t="n">
-        <v>7067939</v>
+        <v>7068267</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10597,7 +10597,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948052</v>
+        <v>123948068</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496977</v>
+        <v>497549</v>
       </c>
       <c r="R78" t="n">
-        <v>7067794</v>
+        <v>7067939</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10704,7 +10704,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948057</v>
+        <v>123948067</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497142</v>
+        <v>497567</v>
       </c>
       <c r="R79" t="n">
-        <v>7068071</v>
+        <v>7067939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10811,10 +10811,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948063</v>
+        <v>123948082</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10823,25 +10823,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497448</v>
+        <v>497300</v>
       </c>
       <c r="R80" t="n">
-        <v>7067857</v>
+        <v>7068117</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10887,11 +10887,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10918,7 +10913,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948064</v>
+        <v>123948069</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -10958,10 +10953,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497471</v>
+        <v>497544</v>
       </c>
       <c r="R81" t="n">
-        <v>7067944</v>
+        <v>7067872</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11025,7 +11020,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948076</v>
+        <v>123948066</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11065,10 +11060,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497599</v>
+        <v>497568</v>
       </c>
       <c r="R82" t="n">
-        <v>7068342</v>
+        <v>7067974</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11105,7 +11100,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11132,7 +11127,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948073</v>
+        <v>123948041</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11172,10 +11167,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497810</v>
+        <v>497578</v>
       </c>
       <c r="R83" t="n">
-        <v>7068216</v>
+        <v>7067475</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11212,7 +11207,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11239,10 +11234,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948084</v>
+        <v>123948051</v>
       </c>
       <c r="B84" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11255,21 +11250,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11279,10 +11274,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497101</v>
+        <v>496962</v>
       </c>
       <c r="R84" t="n">
-        <v>7067728</v>
+        <v>7067810</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11315,6 +11310,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11341,7 +11341,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948050</v>
+        <v>123948053</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11381,10 +11381,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496963</v>
+        <v>497052</v>
       </c>
       <c r="R85" t="n">
-        <v>7067823</v>
+        <v>7067797</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11448,7 +11448,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948071</v>
+        <v>123948063</v>
       </c>
       <c r="B86" t="n">
         <v>57513</v>
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497830</v>
+        <v>497448</v>
       </c>
       <c r="R86" t="n">
-        <v>7068267</v>
+        <v>7067857</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11657,7 +11657,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948077</v>
+        <v>123948078</v>
       </c>
       <c r="B88" t="n">
         <v>57513</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497583</v>
+        <v>497569</v>
       </c>
       <c r="R88" t="n">
-        <v>7068342</v>
+        <v>7068352</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11764,10 +11764,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948082</v>
+        <v>123948084</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11776,25 +11776,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497300</v>
+        <v>497101</v>
       </c>
       <c r="R89" t="n">
-        <v>7068117</v>
+        <v>7067728</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11866,7 +11866,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948054</v>
+        <v>123948070</v>
       </c>
       <c r="B90" t="n">
         <v>57513</v>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497062</v>
+        <v>497876</v>
       </c>
       <c r="R90" t="n">
-        <v>7068118</v>
+        <v>7068110</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948078</v>
+        <v>123948059</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497569</v>
+        <v>497338</v>
       </c>
       <c r="R91" t="n">
-        <v>7068352</v>
+        <v>7068065</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12080,7 +12080,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948049</v>
+        <v>123948057</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496958</v>
+        <v>497142</v>
       </c>
       <c r="R92" t="n">
-        <v>7067783</v>
+        <v>7068071</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12187,7 +12187,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948041</v>
+        <v>123948062</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497578</v>
+        <v>497431</v>
       </c>
       <c r="R93" t="n">
-        <v>7067475</v>
+        <v>7067834</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12294,7 +12294,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948069</v>
+        <v>123948077</v>
       </c>
       <c r="B94" t="n">
         <v>57513</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497544</v>
+        <v>497583</v>
       </c>
       <c r="R94" t="n">
-        <v>7067872</v>
+        <v>7068342</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123929700</v>
+        <v>123932552</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12437,24 +12437,19 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497829</v>
+        <v>497461</v>
       </c>
       <c r="R95" t="n">
-        <v>7067835</v>
+        <v>7067890</v>
       </c>
       <c r="S95" t="n">
         <v>8</v>
@@ -12486,7 +12481,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12491,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12515,7 +12510,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -12553,10 +12548,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123929067</v>
+        <v>123932201</v>
       </c>
       <c r="B96" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12565,36 +12560,40 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12603,13 +12602,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497903</v>
+        <v>497553</v>
       </c>
       <c r="R96" t="n">
-        <v>7068110</v>
+        <v>7068083</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12638,7 +12637,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12648,12 +12647,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12664,31 +12663,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12705,10 +12679,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123934404</v>
+        <v>123934695</v>
       </c>
       <c r="B97" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12717,36 +12691,31 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12755,13 +12724,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>496972</v>
+        <v>497164</v>
       </c>
       <c r="R97" t="n">
-        <v>7067780</v>
+        <v>7067665</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12790,7 +12759,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12800,12 +12769,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12819,27 +12788,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12857,7 +12826,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123931338</v>
+        <v>123929700</v>
       </c>
       <c r="B98" t="n">
         <v>57513</v>
@@ -12893,7 +12862,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -12903,17 +12872,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497552</v>
+        <v>497829</v>
       </c>
       <c r="R98" t="n">
-        <v>7067881</v>
+        <v>7067835</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12942,7 +12911,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12952,12 +12921,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12971,7 +12940,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13009,7 +12978,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123932552</v>
+        <v>123931338</v>
       </c>
       <c r="B99" t="n">
         <v>57513</v>
@@ -13048,19 +13017,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497461</v>
+        <v>497552</v>
       </c>
       <c r="R99" t="n">
-        <v>7067890</v>
+        <v>7067881</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13089,7 +13063,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13099,12 +13073,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13156,10 +13130,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123932201</v>
+        <v>123934404</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13168,55 +13142,51 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497553</v>
+        <v>496972</v>
       </c>
       <c r="R100" t="n">
-        <v>7068083</v>
+        <v>7067780</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13245,7 +13215,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13255,12 +13225,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13271,6 +13241,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13287,10 +13282,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123929267</v>
+        <v>123931433</v>
       </c>
       <c r="B101" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13303,27 +13298,32 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -13332,13 +13332,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497833</v>
+        <v>497554</v>
       </c>
       <c r="R101" t="n">
-        <v>7067988</v>
+        <v>7067886</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13401,22 +13401,22 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123931433</v>
+        <v>123929267</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13450,32 +13450,27 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13484,13 +13479,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497554</v>
+        <v>497833</v>
       </c>
       <c r="R102" t="n">
-        <v>7067886</v>
+        <v>7067988</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13519,7 +13514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13529,12 +13524,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13553,22 +13548,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13586,10 +13581,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123934695</v>
+        <v>123929067</v>
       </c>
       <c r="B103" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13598,43 +13593,48 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497164</v>
+        <v>497903</v>
       </c>
       <c r="R103" t="n">
-        <v>7067665</v>
+        <v>7068110</v>
       </c>
       <c r="S103" t="n">
         <v>9</v>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13695,27 +13695,27 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935469</v>
+        <v>123935511</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,24 +13886,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
@@ -13913,10 +13923,10 @@
         <v>497429</v>
       </c>
       <c r="R105" t="n">
-        <v>7067378</v>
+        <v>7067368</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13945,7 +13955,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13955,7 +13965,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13984,12 +13994,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14281,7 +14291,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123935892</v>
+        <v>123936388</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -14321,13 +14331,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497488</v>
+        <v>497347</v>
       </c>
       <c r="R108" t="n">
-        <v>7067338</v>
+        <v>7067031</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14356,7 +14366,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14366,7 +14376,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14570,10 +14580,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935511</v>
+        <v>123935892</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -14586,47 +14596,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497429</v>
+        <v>497488</v>
       </c>
       <c r="R110" t="n">
-        <v>7067368</v>
+        <v>7067338</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14854,7 +14854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123936388</v>
+        <v>123935469</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -14894,13 +14894,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497347</v>
+        <v>497429</v>
       </c>
       <c r="R112" t="n">
-        <v>7067031</v>
+        <v>7067378</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14991,7 +14991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948045</v>
+        <v>123948038</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497439</v>
+        <v>497227</v>
       </c>
       <c r="R113" t="n">
-        <v>7067336</v>
+        <v>7067047</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948039</v>
+        <v>123948047</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497241</v>
+        <v>497422</v>
       </c>
       <c r="R114" t="n">
-        <v>7067063</v>
+        <v>7067360</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,10 +15205,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948080</v>
+        <v>123948040</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15221,16 +15221,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497370</v>
+        <v>497269</v>
       </c>
       <c r="R115" t="n">
-        <v>7067042</v>
+        <v>7067065</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15312,7 +15312,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948040</v>
+        <v>123948045</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497269</v>
+        <v>497439</v>
       </c>
       <c r="R116" t="n">
-        <v>7067065</v>
+        <v>7067336</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948042</v>
+        <v>123948039</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497448</v>
+        <v>497241</v>
       </c>
       <c r="R117" t="n">
-        <v>7067435</v>
+        <v>7067063</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,7 +15526,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948047</v>
+        <v>123948042</v>
       </c>
       <c r="B118" t="n">
         <v>57513</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497422</v>
+        <v>497448</v>
       </c>
       <c r="R118" t="n">
-        <v>7067360</v>
+        <v>7067435</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15633,10 +15633,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948038</v>
+        <v>123948080</v>
       </c>
       <c r="B119" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497227</v>
+        <v>497370</v>
       </c>
       <c r="R119" t="n">
-        <v>7067047</v>
+        <v>7067042</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123928438</v>
+        <v>123934442</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497801</v>
+        <v>496964</v>
       </c>
       <c r="R2" t="n">
-        <v>7068154</v>
+        <v>7067764</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123925768</v>
+        <v>123934022</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -848,17 +848,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497652</v>
+        <v>496970</v>
       </c>
       <c r="R3" t="n">
-        <v>7067869</v>
+        <v>7067716</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -949,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929301</v>
+        <v>123927550</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,42 +970,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497846</v>
+        <v>497670</v>
       </c>
       <c r="R4" t="n">
-        <v>7067985</v>
+        <v>7068014</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123928831</v>
+        <v>123932682</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,41 +1103,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497927</v>
+        <v>497368</v>
       </c>
       <c r="R5" t="n">
-        <v>7068210</v>
+        <v>7067763</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,6 +1196,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1213,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123926766</v>
+        <v>123927679</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,31 +1245,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1258,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497661</v>
+        <v>497679</v>
       </c>
       <c r="R6" t="n">
-        <v>7067931</v>
+        <v>7068046</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1293,7 +1327,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1303,12 +1337,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1323,26 +1357,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1374,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123927550</v>
+        <v>123929497</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,37 +1390,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497670</v>
+        <v>497846</v>
       </c>
       <c r="R7" t="n">
-        <v>7068014</v>
+        <v>7067895</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1435,7 +1459,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1445,7 +1469,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,12 +1503,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1497,10 +1526,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123934349</v>
+        <v>123934908</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,37 +1542,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496957</v>
+        <v>497399</v>
       </c>
       <c r="R8" t="n">
-        <v>7067780</v>
+        <v>7067620</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1572,7 +1606,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1582,7 +1616,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,12 +1645,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1634,10 +1668,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123934742</v>
+        <v>123935202</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1650,47 +1684,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497184</v>
+        <v>497524</v>
       </c>
       <c r="R9" t="n">
-        <v>7067677</v>
+        <v>7067827</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1719,7 +1748,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1729,12 +1758,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1748,7 +1772,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1766,7 +1810,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123935093</v>
+        <v>123933422</v>
       </c>
       <c r="B10" t="n">
         <v>91008</v>
@@ -1811,13 +1855,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497438</v>
+        <v>497077</v>
       </c>
       <c r="R10" t="n">
-        <v>7067653</v>
+        <v>7067679</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1846,7 +1890,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1856,7 +1900,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1870,7 +1914,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1908,10 +1952,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123933712</v>
+        <v>123928574</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1924,47 +1968,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497111</v>
+        <v>497848</v>
       </c>
       <c r="R11" t="n">
-        <v>7067721</v>
+        <v>7068101</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1993,7 +2027,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2003,12 +2037,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2022,7 +2051,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2040,10 +2069,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123928574</v>
+        <v>123933712</v>
       </c>
       <c r="B12" t="n">
-        <v>79919</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2056,37 +2085,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497848</v>
+        <v>497111</v>
       </c>
       <c r="R12" t="n">
-        <v>7068101</v>
+        <v>7067721</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2115,7 +2154,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2125,7 +2164,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2139,7 +2183,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2157,10 +2201,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123932385</v>
+        <v>123932969</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2173,37 +2217,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497528</v>
+        <v>497236</v>
       </c>
       <c r="R13" t="n">
-        <v>7067930</v>
+        <v>7067739</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2232,7 +2286,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2242,7 +2296,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2257,26 +2316,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2294,7 +2333,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123929497</v>
+        <v>123925602</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2344,13 +2383,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497846</v>
+        <v>497599</v>
       </c>
       <c r="R14" t="n">
-        <v>7067895</v>
+        <v>7067878</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2379,7 +2418,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2389,12 +2428,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en något grövre gran.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2446,10 +2485,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123928741</v>
+        <v>123928831</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>79919</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2462,56 +2501,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497907</v>
+        <v>497927</v>
       </c>
       <c r="R15" t="n">
-        <v>7068146</v>
+        <v>7068210</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2540,7 +2560,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2550,12 +2570,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2587,10 +2602,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123931684</v>
+        <v>123934349</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2603,47 +2618,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497576</v>
+        <v>496957</v>
       </c>
       <c r="R16" t="n">
-        <v>7067995</v>
+        <v>7067780</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2682,12 +2687,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123927991</v>
+        <v>123933650</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2755,47 +2755,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497659</v>
+        <v>497112</v>
       </c>
       <c r="R17" t="n">
-        <v>7068053</v>
+        <v>7067726</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2824,7 +2819,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2834,12 +2829,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2891,10 +2881,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123925387</v>
+        <v>123927991</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2903,20 +2893,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2924,19 +2914,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2950,13 +2931,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497600</v>
+        <v>497659</v>
       </c>
       <c r="R18" t="n">
-        <v>7067872</v>
+        <v>7068053</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2983,14 +2964,24 @@
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3004,7 +2995,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3022,7 +3033,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123933086</v>
+        <v>123928379</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -3058,17 +3069,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497126</v>
+        <v>497732</v>
       </c>
       <c r="R19" t="n">
-        <v>7067709</v>
+        <v>7068101</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3097,7 +3108,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3107,7 +3118,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3159,10 +3170,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123925995</v>
+        <v>123931684</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3175,37 +3186,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497628</v>
+        <v>497576</v>
       </c>
       <c r="R20" t="n">
-        <v>7067895</v>
+        <v>7067995</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3234,7 +3255,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3244,7 +3265,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3273,12 +3299,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3296,7 +3322,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123934022</v>
+        <v>123929190</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3332,17 +3358,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496970</v>
+        <v>497832</v>
       </c>
       <c r="R21" t="n">
-        <v>7067716</v>
+        <v>7067981</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3371,7 +3397,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3381,7 +3407,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3438,10 +3464,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123932682</v>
+        <v>123934255</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3454,42 +3480,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497368</v>
+        <v>496932</v>
       </c>
       <c r="R22" t="n">
-        <v>7067763</v>
+        <v>7067736</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3518,7 +3539,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3528,7 +3549,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3542,27 +3563,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3580,10 +3601,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123928379</v>
+        <v>123925387</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3592,41 +3613,60 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497732</v>
+        <v>497600</v>
       </c>
       <c r="R23" t="n">
-        <v>7068101</v>
+        <v>7067872</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3653,19 +3693,14 @@
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-09</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:41</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3680,26 +3715,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3717,7 +3732,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932697</v>
+        <v>123929282</v>
       </c>
       <c r="B24" t="n">
         <v>79892</v>
@@ -3751,24 +3766,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497385</v>
+        <v>497853</v>
       </c>
       <c r="R24" t="n">
-        <v>7067784</v>
+        <v>7067970</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3797,7 +3807,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3807,7 +3817,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3836,12 +3851,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3859,10 +3874,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123927793</v>
+        <v>123935093</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3875,33 +3890,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3909,17 +3915,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497653</v>
+        <v>497438</v>
       </c>
       <c r="R25" t="n">
-        <v>7068061</v>
+        <v>7067653</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3958,12 +3964,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer i högstubbe med bohål.</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4015,7 +4016,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123928514</v>
+        <v>123926190</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -4055,13 +4056,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497851</v>
+        <v>497654</v>
       </c>
       <c r="R26" t="n">
-        <v>7068090</v>
+        <v>7067926</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4090,7 +4091,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4100,7 +4101,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4152,10 +4153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123927679</v>
+        <v>123928438</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4164,60 +4165,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497679</v>
+        <v>497801</v>
       </c>
       <c r="R27" t="n">
-        <v>7068046</v>
+        <v>7068154</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4246,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4256,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4276,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4293,10 +4290,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123934255</v>
+        <v>123933127</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4309,37 +4306,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496932</v>
+        <v>497133</v>
       </c>
       <c r="R28" t="n">
-        <v>7067736</v>
+        <v>7067678</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4368,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4378,7 +4380,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4392,27 +4394,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4430,10 +4432,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123929190</v>
+        <v>123929301</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4446,37 +4448,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497832</v>
+        <v>497846</v>
       </c>
       <c r="R29" t="n">
-        <v>7067981</v>
+        <v>7067985</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4505,7 +4512,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4515,12 +4522,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på en gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4572,10 +4579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123933127</v>
+        <v>123932608</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4588,42 +4595,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497133</v>
+        <v>497492</v>
       </c>
       <c r="R30" t="n">
-        <v>7067678</v>
+        <v>7067833</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4652,7 +4654,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4662,7 +4664,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4681,22 +4683,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4714,10 +4716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123929282</v>
+        <v>123932385</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4730,21 +4732,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4754,13 +4756,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497853</v>
+        <v>497528</v>
       </c>
       <c r="R31" t="n">
-        <v>7067970</v>
+        <v>7067930</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4789,7 +4791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4799,12 +4801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en nedfallen stam av en gammal flerstammig sälg.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4823,22 +4820,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,7 +4853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123925856</v>
+        <v>123933086</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4892,17 +4889,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497652</v>
+        <v>497126</v>
       </c>
       <c r="R32" t="n">
-        <v>7067886</v>
+        <v>7067709</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4941,7 +4938,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4993,7 +4990,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123932608</v>
+        <v>123928803</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -5033,10 +5030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497492</v>
+        <v>497932</v>
       </c>
       <c r="R33" t="n">
-        <v>7067833</v>
+        <v>7068202</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -5068,7 +5065,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5078,7 +5075,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5130,10 +5132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123931616</v>
+        <v>123934085</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5142,41 +5144,60 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497562</v>
+        <v>496980</v>
       </c>
       <c r="R34" t="n">
-        <v>7067959</v>
+        <v>7067690</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5205,7 +5226,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5215,7 +5236,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5230,26 +5256,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5267,10 +5273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123933422</v>
+        <v>123926766</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5283,42 +5289,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497077</v>
+        <v>497661</v>
       </c>
       <c r="R35" t="n">
-        <v>7067679</v>
+        <v>7067931</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5347,7 +5353,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5357,7 +5363,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5386,12 +5397,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5409,10 +5420,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123931528</v>
+        <v>123933492</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5425,44 +5436,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497563</v>
+        <v>497103</v>
       </c>
       <c r="R36" t="n">
-        <v>7067965</v>
+        <v>7067696</v>
       </c>
       <c r="S36" t="n">
         <v>8</v>
@@ -5494,7 +5495,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5504,12 +5505,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5538,12 +5534,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5561,10 +5557,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123928327</v>
+        <v>123925856</v>
       </c>
       <c r="B37" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5573,48 +5569,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497712</v>
+        <v>497652</v>
       </c>
       <c r="R37" t="n">
-        <v>7068103</v>
+        <v>7067886</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5646,7 +5632,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5656,12 +5642,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5676,6 +5657,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5693,10 +5694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123933650</v>
+        <v>123925995</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5709,42 +5710,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497112</v>
+        <v>497628</v>
       </c>
       <c r="R38" t="n">
-        <v>7067726</v>
+        <v>7067895</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5773,7 +5769,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5783,7 +5779,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5797,7 +5793,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5812,12 +5808,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5835,7 +5831,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123928803</v>
+        <v>123931616</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -5875,13 +5871,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497932</v>
+        <v>497562</v>
       </c>
       <c r="R39" t="n">
-        <v>7068202</v>
+        <v>7067959</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5910,7 +5906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5920,12 +5916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5977,10 +5968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123925602</v>
+        <v>123928858</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5993,44 +5984,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497599</v>
+        <v>497900</v>
       </c>
       <c r="R40" t="n">
-        <v>7067878</v>
+        <v>7068251</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6062,7 +6043,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6072,12 +6053,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6106,12 +6087,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6129,10 +6110,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123933142</v>
+        <v>123929459</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6141,43 +6122,48 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497133</v>
+        <v>497843</v>
       </c>
       <c r="R41" t="n">
-        <v>7067678</v>
+        <v>7067903</v>
       </c>
       <c r="S41" t="n">
         <v>8</v>
@@ -6209,7 +6195,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6219,7 +6205,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6238,22 +6229,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6271,10 +6262,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123933859</v>
+        <v>123933142</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6283,41 +6274,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497016</v>
+        <v>497133</v>
       </c>
       <c r="R42" t="n">
-        <v>7067743</v>
+        <v>7067678</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6346,7 +6342,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6356,12 +6352,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6380,22 +6371,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6550,10 +6541,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123935202</v>
+        <v>123932697</v>
       </c>
       <c r="B44" t="n">
-        <v>91008</v>
+        <v>79892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6566,42 +6557,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497524</v>
+        <v>497385</v>
       </c>
       <c r="R44" t="n">
-        <v>7067827</v>
+        <v>7067784</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6630,7 +6621,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6640,7 +6631,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6659,22 +6650,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6692,7 +6683,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123934442</v>
+        <v>123933859</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -6732,13 +6723,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496964</v>
+        <v>497016</v>
       </c>
       <c r="R45" t="n">
-        <v>7067764</v>
+        <v>7067743</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6767,7 +6758,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6777,7 +6768,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6829,10 +6825,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123933774</v>
+        <v>123931528</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6845,37 +6841,47 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497066</v>
+        <v>497563</v>
       </c>
       <c r="R46" t="n">
-        <v>7067728</v>
+        <v>7067965</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6904,7 +6910,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6914,7 +6920,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6928,7 +6939,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6943,12 +6954,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6966,10 +6977,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123934569</v>
+        <v>123927793</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6982,37 +6993,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497124</v>
+        <v>497653</v>
       </c>
       <c r="R47" t="n">
-        <v>7067682</v>
+        <v>7068061</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -7041,7 +7066,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7051,7 +7076,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i högstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7070,22 +7100,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7103,10 +7133,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123933962</v>
+        <v>123934569</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7119,21 +7149,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -7143,10 +7173,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496999</v>
+        <v>497124</v>
       </c>
       <c r="R48" t="n">
-        <v>7067688</v>
+        <v>7067682</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -7178,7 +7208,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7188,7 +7218,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7202,27 +7232,27 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7240,10 +7270,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123933492</v>
+        <v>123928327</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>56725</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7252,41 +7282,51 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497103</v>
+        <v>497712</v>
       </c>
       <c r="R49" t="n">
-        <v>7067696</v>
+        <v>7068103</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7315,7 +7355,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7325,7 +7365,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7340,26 +7385,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7377,10 +7402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123929459</v>
+        <v>123929370</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>79926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7389,36 +7414,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7427,13 +7447,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497843</v>
+        <v>497852</v>
       </c>
       <c r="R50" t="n">
-        <v>7067903</v>
+        <v>7067984</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7462,7 +7482,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7472,12 +7492,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7496,22 +7511,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7529,10 +7544,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123934908</v>
+        <v>123925768</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7545,42 +7560,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497399</v>
+        <v>497652</v>
       </c>
       <c r="R51" t="n">
-        <v>7067620</v>
+        <v>7067869</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7609,7 +7619,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7619,7 +7629,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7648,12 +7658,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7671,10 +7681,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123932969</v>
+        <v>123928741</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7683,20 +7693,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7704,10 +7714,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7717,17 +7736,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497236</v>
+        <v>497907</v>
       </c>
       <c r="R52" t="n">
-        <v>7067739</v>
+        <v>7068146</v>
       </c>
       <c r="S52" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7756,7 +7775,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7766,12 +7785,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färsk spillning på barmark. Fyndplatsen finns i bitvis tätare och bitvis mer luckig granskog.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7803,10 +7822,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123934085</v>
+        <v>123933962</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7815,60 +7834,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496980</v>
+        <v>496999</v>
       </c>
       <c r="R53" t="n">
-        <v>7067690</v>
+        <v>7067688</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7907,12 +7907,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7927,6 +7922,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7944,7 +7959,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123928858</v>
+        <v>123928514</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -7984,13 +7999,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497900</v>
+        <v>497851</v>
       </c>
       <c r="R54" t="n">
-        <v>7068251</v>
+        <v>7068090</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -8019,7 +8034,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8029,12 +8044,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8086,10 +8096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123926190</v>
+        <v>123934742</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8102,37 +8112,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497654</v>
+        <v>497184</v>
       </c>
       <c r="R55" t="n">
-        <v>7067926</v>
+        <v>7067677</v>
       </c>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8161,7 +8181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8171,7 +8191,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8185,27 +8210,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8223,10 +8228,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123929370</v>
+        <v>123933774</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8235,20 +8240,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8257,24 +8262,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497852</v>
+        <v>497066</v>
       </c>
       <c r="R56" t="n">
-        <v>7067984</v>
+        <v>7067728</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8327,27 +8327,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123948074</v>
+        <v>123948041</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497809</v>
+        <v>497578</v>
       </c>
       <c r="R57" t="n">
-        <v>7068221</v>
+        <v>7067475</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8472,7 +8472,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123948064</v>
+        <v>123948065</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497471</v>
+        <v>497547</v>
       </c>
       <c r="R58" t="n">
-        <v>7067944</v>
+        <v>7068008</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8579,7 +8579,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123948050</v>
+        <v>123948071</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496963</v>
+        <v>497830</v>
       </c>
       <c r="R59" t="n">
-        <v>7067823</v>
+        <v>7068267</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8686,7 +8686,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123948061</v>
+        <v>123948050</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497152</v>
+        <v>496963</v>
       </c>
       <c r="R60" t="n">
-        <v>7067720</v>
+        <v>7067823</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8793,7 +8793,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123948056</v>
+        <v>123948070</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497093</v>
+        <v>497876</v>
       </c>
       <c r="R61" t="n">
-        <v>7068094</v>
+        <v>7068110</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123948054</v>
+        <v>123948060</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497062</v>
+        <v>497140</v>
       </c>
       <c r="R62" t="n">
-        <v>7068118</v>
+        <v>7067713</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948081</v>
+        <v>123948055</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9126,25 +9126,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497267</v>
+        <v>497062</v>
       </c>
       <c r="R64" t="n">
-        <v>7068098</v>
+        <v>7068109</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9190,6 +9190,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9216,7 +9221,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948065</v>
+        <v>123948061</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -9256,10 +9261,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497547</v>
+        <v>497152</v>
       </c>
       <c r="R65" t="n">
-        <v>7068008</v>
+        <v>7067720</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9296,7 +9301,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9323,10 +9328,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948083</v>
+        <v>123948062</v>
       </c>
       <c r="B66" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9339,21 +9344,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9363,10 +9368,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497012</v>
+        <v>497431</v>
       </c>
       <c r="R66" t="n">
-        <v>7067783</v>
+        <v>7067834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9399,6 +9404,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9425,7 +9435,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948060</v>
+        <v>123948053</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -9465,10 +9475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497140</v>
+        <v>497052</v>
       </c>
       <c r="R67" t="n">
-        <v>7067713</v>
+        <v>7067797</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9532,7 +9542,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948052</v>
+        <v>123948054</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -9572,10 +9582,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496977</v>
+        <v>497062</v>
       </c>
       <c r="R68" t="n">
-        <v>7067794</v>
+        <v>7068118</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9639,7 +9649,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948048</v>
+        <v>123948056</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -9679,10 +9689,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497417</v>
+        <v>497093</v>
       </c>
       <c r="R69" t="n">
-        <v>7067613</v>
+        <v>7068094</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9746,7 +9756,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948055</v>
+        <v>123948057</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -9786,10 +9796,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497062</v>
+        <v>497142</v>
       </c>
       <c r="R70" t="n">
-        <v>7068109</v>
+        <v>7068071</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9853,10 +9863,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948075</v>
+        <v>123948081</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9865,25 +9875,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9893,10 +9903,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497629</v>
+        <v>497267</v>
       </c>
       <c r="R71" t="n">
-        <v>7068330</v>
+        <v>7068098</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9929,11 +9939,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9960,10 +9965,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948037</v>
+        <v>123948048</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9976,21 +9981,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10000,10 +10005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497443</v>
+        <v>497417</v>
       </c>
       <c r="R72" t="n">
-        <v>7067840</v>
+        <v>7067613</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10036,6 +10041,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10062,7 +10072,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948073</v>
+        <v>123948076</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -10102,10 +10112,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497810</v>
+        <v>497599</v>
       </c>
       <c r="R73" t="n">
-        <v>7068216</v>
+        <v>7068342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10169,10 +10179,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948076</v>
+        <v>123948084</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10185,21 +10195,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10209,10 +10219,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497599</v>
+        <v>497101</v>
       </c>
       <c r="R74" t="n">
-        <v>7068342</v>
+        <v>7067728</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10245,11 +10255,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10383,7 +10388,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948049</v>
+        <v>123948073</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -10423,10 +10428,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496958</v>
+        <v>497810</v>
       </c>
       <c r="R76" t="n">
-        <v>7067783</v>
+        <v>7068216</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10463,7 +10468,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10490,7 +10495,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948071</v>
+        <v>123948078</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -10530,10 +10535,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497830</v>
+        <v>497569</v>
       </c>
       <c r="R77" t="n">
-        <v>7068267</v>
+        <v>7068352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10597,7 +10602,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948068</v>
+        <v>123948074</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10637,10 +10642,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497549</v>
+        <v>497809</v>
       </c>
       <c r="R78" t="n">
-        <v>7067939</v>
+        <v>7068221</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10677,7 +10682,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10704,7 +10709,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948067</v>
+        <v>123948066</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -10744,10 +10749,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497567</v>
+        <v>497568</v>
       </c>
       <c r="R79" t="n">
-        <v>7067939</v>
+        <v>7067974</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10784,7 +10789,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10811,10 +10816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948082</v>
+        <v>123948049</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10823,25 +10828,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10851,10 +10856,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497300</v>
+        <v>496958</v>
       </c>
       <c r="R80" t="n">
-        <v>7068117</v>
+        <v>7067783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10887,6 +10892,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10913,10 +10923,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948069</v>
+        <v>123948083</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10929,21 +10939,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10953,10 +10963,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497544</v>
+        <v>497012</v>
       </c>
       <c r="R81" t="n">
-        <v>7067872</v>
+        <v>7067783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10989,11 +10999,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11020,7 +11025,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948066</v>
+        <v>123948069</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11060,10 +11065,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497568</v>
+        <v>497544</v>
       </c>
       <c r="R82" t="n">
-        <v>7067974</v>
+        <v>7067872</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11100,7 +11105,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11127,7 +11132,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948041</v>
+        <v>123948051</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11167,10 +11172,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497578</v>
+        <v>496962</v>
       </c>
       <c r="R83" t="n">
-        <v>7067475</v>
+        <v>7067810</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11207,7 +11212,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11234,7 +11239,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948051</v>
+        <v>123948075</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -11274,10 +11279,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496962</v>
+        <v>497629</v>
       </c>
       <c r="R84" t="n">
-        <v>7067810</v>
+        <v>7068330</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11314,7 +11319,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11341,7 +11346,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948053</v>
+        <v>123948063</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11381,10 +11386,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497052</v>
+        <v>497448</v>
       </c>
       <c r="R85" t="n">
-        <v>7067797</v>
+        <v>7067857</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11448,10 +11453,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948063</v>
+        <v>123948037</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11464,21 +11469,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11488,10 +11493,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497448</v>
+        <v>497443</v>
       </c>
       <c r="R86" t="n">
-        <v>7067857</v>
+        <v>7067840</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11524,11 +11529,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11555,10 +11555,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948085</v>
+        <v>123948064</v>
       </c>
       <c r="B87" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11571,21 +11571,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497243</v>
+        <v>497471</v>
       </c>
       <c r="R87" t="n">
-        <v>7067786</v>
+        <v>7067944</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11631,6 +11631,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11657,10 +11662,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948078</v>
+        <v>123948082</v>
       </c>
       <c r="B88" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11669,25 +11674,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11697,10 +11702,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497569</v>
+        <v>497300</v>
       </c>
       <c r="R88" t="n">
-        <v>7068352</v>
+        <v>7068117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11733,11 +11738,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11764,10 +11764,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948084</v>
+        <v>123948077</v>
       </c>
       <c r="B89" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11780,21 +11780,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497101</v>
+        <v>497583</v>
       </c>
       <c r="R89" t="n">
-        <v>7067728</v>
+        <v>7068342</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11840,6 +11840,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11866,7 +11871,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948070</v>
+        <v>123948052</v>
       </c>
       <c r="B90" t="n">
         <v>57513</v>
@@ -11906,10 +11911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497876</v>
+        <v>496977</v>
       </c>
       <c r="R90" t="n">
-        <v>7068110</v>
+        <v>7067794</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11973,7 +11978,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948059</v>
+        <v>123948068</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -12013,10 +12018,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497338</v>
+        <v>497549</v>
       </c>
       <c r="R91" t="n">
-        <v>7068065</v>
+        <v>7067939</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12053,7 +12058,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12080,7 +12085,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948057</v>
+        <v>123948059</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -12120,10 +12125,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497142</v>
+        <v>497338</v>
       </c>
       <c r="R92" t="n">
-        <v>7068071</v>
+        <v>7068065</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12160,7 +12165,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12187,7 +12192,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948062</v>
+        <v>123948067</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -12227,10 +12232,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497431</v>
+        <v>497567</v>
       </c>
       <c r="R93" t="n">
-        <v>7067834</v>
+        <v>7067939</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12267,7 +12272,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12294,10 +12299,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948077</v>
+        <v>123948085</v>
       </c>
       <c r="B94" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12310,21 +12315,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12334,10 +12339,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497583</v>
+        <v>497243</v>
       </c>
       <c r="R94" t="n">
-        <v>7068342</v>
+        <v>7067786</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12370,11 +12375,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123932552</v>
+        <v>123934404</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12440,19 +12440,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497461</v>
+        <v>496972</v>
       </c>
       <c r="R95" t="n">
-        <v>7067890</v>
+        <v>7067780</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12481,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12491,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12548,10 +12553,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123932201</v>
+        <v>123929267</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12560,40 +12565,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12602,13 +12598,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497553</v>
+        <v>497833</v>
       </c>
       <c r="R96" t="n">
-        <v>7068083</v>
+        <v>7067988</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12637,7 +12633,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12647,12 +12643,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12663,6 +12659,31 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12679,10 +12700,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123934695</v>
+        <v>123929067</v>
       </c>
       <c r="B97" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12691,43 +12712,48 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497164</v>
+        <v>497903</v>
       </c>
       <c r="R97" t="n">
-        <v>7067665</v>
+        <v>7068110</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -12759,7 +12785,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12769,12 +12795,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12788,27 +12814,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12826,7 +12852,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123929700</v>
+        <v>123931338</v>
       </c>
       <c r="B98" t="n">
         <v>57513</v>
@@ -12862,7 +12888,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -12872,17 +12898,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497829</v>
+        <v>497552</v>
       </c>
       <c r="R98" t="n">
-        <v>7067835</v>
+        <v>7067881</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12911,7 +12937,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12921,12 +12947,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12940,7 +12966,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -12978,7 +13004,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123931338</v>
+        <v>123932552</v>
       </c>
       <c r="B99" t="n">
         <v>57513</v>
@@ -13017,24 +13043,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497552</v>
+        <v>497461</v>
       </c>
       <c r="R99" t="n">
-        <v>7067881</v>
+        <v>7067890</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13063,7 +13084,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13073,12 +13094,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13130,7 +13151,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123934404</v>
+        <v>123929700</v>
       </c>
       <c r="B100" t="n">
         <v>57513</v>
@@ -13166,7 +13187,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13176,17 +13197,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496972</v>
+        <v>497829</v>
       </c>
       <c r="R100" t="n">
-        <v>7067780</v>
+        <v>7067835</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13215,7 +13236,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13225,12 +13246,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13244,7 +13265,7 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13282,10 +13303,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123931433</v>
+        <v>123934695</v>
       </c>
       <c r="B101" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13294,51 +13315,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497554</v>
+        <v>497164</v>
       </c>
       <c r="R101" t="n">
-        <v>7067886</v>
+        <v>7067665</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13367,7 +13383,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13377,12 +13393,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13396,27 +13412,27 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13434,10 +13450,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929267</v>
+        <v>123932201</v>
       </c>
       <c r="B102" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13446,31 +13462,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13479,13 +13504,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497833</v>
+        <v>497553</v>
       </c>
       <c r="R102" t="n">
-        <v>7067988</v>
+        <v>7068083</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13514,7 +13539,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13524,12 +13549,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13540,31 +13565,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13581,7 +13581,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123929067</v>
+        <v>123931433</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13631,13 +13631,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497903</v>
+        <v>497554</v>
       </c>
       <c r="R103" t="n">
-        <v>7068110</v>
+        <v>7067886</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13870,10 +13870,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123935511</v>
+        <v>123936388</v>
       </c>
       <c r="B105" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13886,47 +13886,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497429</v>
+        <v>497347</v>
       </c>
       <c r="R105" t="n">
-        <v>7067368</v>
+        <v>7067031</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13955,7 +13945,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13965,7 +13955,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13994,12 +13984,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14017,7 +14007,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123935971</v>
+        <v>123935892</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -14057,13 +14047,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497477</v>
+        <v>497488</v>
       </c>
       <c r="R106" t="n">
-        <v>7067373</v>
+        <v>7067338</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14092,7 +14082,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14102,7 +14092,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14154,7 +14144,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123935623</v>
+        <v>123935662</v>
       </c>
       <c r="B107" t="n">
         <v>78810</v>
@@ -14194,13 +14184,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497400</v>
+        <v>497407</v>
       </c>
       <c r="R107" t="n">
-        <v>7067320</v>
+        <v>7067289</v>
       </c>
       <c r="S107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14229,7 +14219,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14239,7 +14229,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14291,10 +14281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123936388</v>
+        <v>123935511</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14307,37 +14297,47 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497347</v>
+        <v>497429</v>
       </c>
       <c r="R108" t="n">
-        <v>7067031</v>
+        <v>7067368</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14405,12 +14405,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14428,10 +14428,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123936336</v>
+        <v>123935971</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14444,47 +14444,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>497296</v>
+        <v>497477</v>
       </c>
       <c r="R109" t="n">
-        <v>7067024</v>
+        <v>7067373</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14513,7 +14503,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14523,12 +14513,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14557,12 +14542,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14580,7 +14565,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123935892</v>
+        <v>123935469</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -14620,13 +14605,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497488</v>
+        <v>497429</v>
       </c>
       <c r="R110" t="n">
-        <v>7067338</v>
+        <v>7067378</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14655,7 +14640,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14665,7 +14650,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14717,7 +14702,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123935662</v>
+        <v>123935623</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -14757,13 +14742,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497407</v>
+        <v>497400</v>
       </c>
       <c r="R111" t="n">
-        <v>7067289</v>
+        <v>7067320</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14792,7 +14777,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14802,7 +14787,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14854,10 +14839,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123935469</v>
+        <v>123936336</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14870,37 +14855,47 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rask-Nilsudden, Rask-Nilsudden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497429</v>
+        <v>497296</v>
       </c>
       <c r="R112" t="n">
-        <v>7067378</v>
+        <v>7067024</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14929,7 +14924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14939,7 +14934,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14991,7 +14991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123948038</v>
+        <v>123948042</v>
       </c>
       <c r="B113" t="n">
         <v>57513</v>
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497227</v>
+        <v>497448</v>
       </c>
       <c r="R113" t="n">
-        <v>7067047</v>
+        <v>7067435</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948047</v>
+        <v>123948038</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497422</v>
+        <v>497227</v>
       </c>
       <c r="R114" t="n">
-        <v>7067360</v>
+        <v>7067047</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948045</v>
+        <v>123948039</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497439</v>
+        <v>497241</v>
       </c>
       <c r="R116" t="n">
-        <v>7067336</v>
+        <v>7067063</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948039</v>
+        <v>123948045</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497241</v>
+        <v>497439</v>
       </c>
       <c r="R117" t="n">
-        <v>7067063</v>
+        <v>7067336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,10 +15526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948042</v>
+        <v>123948080</v>
       </c>
       <c r="B118" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497448</v>
+        <v>497370</v>
       </c>
       <c r="R118" t="n">
-        <v>7067435</v>
+        <v>7067042</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15633,10 +15633,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123948080</v>
+        <v>123948047</v>
       </c>
       <c r="B119" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -15673,10 +15673,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497370</v>
+        <v>497422</v>
       </c>
       <c r="R119" t="n">
-        <v>7067042</v>
+        <v>7067360</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123934442</v>
+        <v>123932682</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496964</v>
+        <v>497368</v>
       </c>
       <c r="R2" t="n">
-        <v>7067764</v>
+        <v>7067763</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123934022</v>
+        <v>123934442</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -852,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496970</v>
+        <v>496964</v>
       </c>
       <c r="R3" t="n">
-        <v>7067716</v>
+        <v>7067764</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927550</v>
+        <v>123934022</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -990,17 +990,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497670</v>
+        <v>496970</v>
       </c>
       <c r="R4" t="n">
-        <v>7068014</v>
+        <v>7067716</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1091,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123932682</v>
+        <v>123927550</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,42 +1112,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497368</v>
+        <v>497670</v>
       </c>
       <c r="R5" t="n">
-        <v>7067763</v>
+        <v>7068014</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123934908</v>
+        <v>123933712</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1538,31 +1538,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1571,13 +1576,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497399</v>
+        <v>497111</v>
       </c>
       <c r="R8" t="n">
-        <v>7067620</v>
+        <v>7067721</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1616,7 +1621,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1630,27 +1640,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2069,10 +2059,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123933712</v>
+        <v>123925602</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2081,31 +2071,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2115,17 +2105,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497111</v>
+        <v>497599</v>
       </c>
       <c r="R12" t="n">
-        <v>7067721</v>
+        <v>7067878</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2154,7 +2144,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2164,12 +2154,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färsk spillning, längd ca 6 cm, ovanpå snötäcket.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2183,7 +2173,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2333,10 +2343,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123925602</v>
+        <v>123934908</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2349,47 +2359,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497599</v>
+        <v>497399</v>
       </c>
       <c r="R14" t="n">
-        <v>7067878</v>
+        <v>7067620</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2418,7 +2423,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2428,12 +2433,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123927991</v>
+        <v>123928379</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2897,47 +2897,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497659</v>
+        <v>497732</v>
       </c>
       <c r="R18" t="n">
-        <v>7068053</v>
+        <v>7068101</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2966,7 +2956,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2976,12 +2966,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2995,7 +2980,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3010,12 +2995,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3033,10 +3018,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123928379</v>
+        <v>123931684</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3049,37 +3034,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497732</v>
+        <v>497576</v>
       </c>
       <c r="R19" t="n">
-        <v>7068101</v>
+        <v>7067995</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3108,7 +3103,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3118,7 +3113,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123931684</v>
+        <v>123927991</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3186,16 +3186,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497576</v>
+        <v>497659</v>
       </c>
       <c r="R20" t="n">
-        <v>7067995</v>
+        <v>7068053</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stubben efter en nyligen knäck gran.</t>
+          <t>Ett gammalt bohål med rund form på ca 2,3 meters höjd i en granticka-angripen högstubbe. Möjligen bohål efter tretåig hackspett då det finns ringhackade träd i samma skogsbestånd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123929190</v>
+        <v>123934255</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -3358,17 +3358,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497832</v>
+        <v>496932</v>
       </c>
       <c r="R21" t="n">
-        <v>7067981</v>
+        <v>7067736</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3407,12 +3407,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3426,7 +3421,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3464,7 +3459,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123934255</v>
+        <v>123929190</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3500,17 +3495,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496932</v>
+        <v>497832</v>
       </c>
       <c r="R22" t="n">
-        <v>7067736</v>
+        <v>7067981</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3539,7 +3534,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3549,7 +3544,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9114,7 +9114,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948055</v>
+        <v>123948061</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497062</v>
+        <v>497152</v>
       </c>
       <c r="R64" t="n">
-        <v>7068109</v>
+        <v>7067720</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948061</v>
+        <v>123948055</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -9261,10 +9261,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497152</v>
+        <v>497062</v>
       </c>
       <c r="R65" t="n">
-        <v>7067720</v>
+        <v>7068109</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -11453,10 +11453,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948037</v>
+        <v>123948064</v>
       </c>
       <c r="B86" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11469,21 +11469,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497443</v>
+        <v>497471</v>
       </c>
       <c r="R86" t="n">
-        <v>7067840</v>
+        <v>7067944</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11529,6 +11529,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11555,10 +11560,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948064</v>
+        <v>123948037</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11571,21 +11576,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11595,10 +11600,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497471</v>
+        <v>497443</v>
       </c>
       <c r="R87" t="n">
-        <v>7067944</v>
+        <v>7067840</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11631,11 +11636,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -8365,10 +8365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123948041</v>
+        <v>123948037</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497578</v>
+        <v>497443</v>
       </c>
       <c r="R57" t="n">
-        <v>7067475</v>
+        <v>7067840</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8441,11 +8441,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8472,7 +8467,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123948065</v>
+        <v>123948055</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -8512,10 +8507,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497547</v>
+        <v>497062</v>
       </c>
       <c r="R58" t="n">
-        <v>7068008</v>
+        <v>7068109</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8552,7 +8547,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8579,7 +8574,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123948071</v>
+        <v>123948053</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -8619,10 +8614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497830</v>
+        <v>497052</v>
       </c>
       <c r="R59" t="n">
-        <v>7068267</v>
+        <v>7067797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8686,7 +8681,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123948050</v>
+        <v>123948062</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -8726,10 +8721,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496963</v>
+        <v>497431</v>
       </c>
       <c r="R60" t="n">
-        <v>7067823</v>
+        <v>7067834</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8766,7 +8761,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8793,7 +8788,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123948070</v>
+        <v>123948061</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -8833,10 +8828,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497876</v>
+        <v>497152</v>
       </c>
       <c r="R61" t="n">
-        <v>7068110</v>
+        <v>7067720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8900,7 +8895,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123948060</v>
+        <v>123948057</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497140</v>
+        <v>497142</v>
       </c>
       <c r="R62" t="n">
-        <v>7067713</v>
+        <v>7068071</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9007,7 +9002,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123948058</v>
+        <v>123948048</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -9047,10 +9042,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497156</v>
+        <v>497417</v>
       </c>
       <c r="R63" t="n">
-        <v>7067976</v>
+        <v>7067613</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9087,7 +9082,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9114,7 +9109,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123948061</v>
+        <v>123948075</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -9154,10 +9149,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497152</v>
+        <v>497629</v>
       </c>
       <c r="R64" t="n">
-        <v>7067720</v>
+        <v>7068330</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9194,7 +9189,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9221,7 +9216,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123948055</v>
+        <v>123948063</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -9261,10 +9256,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497062</v>
+        <v>497448</v>
       </c>
       <c r="R65" t="n">
-        <v>7068109</v>
+        <v>7067857</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9328,7 +9323,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123948062</v>
+        <v>123948054</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -9368,10 +9363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497431</v>
+        <v>497062</v>
       </c>
       <c r="R66" t="n">
-        <v>7067834</v>
+        <v>7068118</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9435,10 +9430,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123948053</v>
+        <v>123948082</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9447,25 +9442,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9475,10 +9470,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497052</v>
+        <v>497300</v>
       </c>
       <c r="R67" t="n">
-        <v>7067797</v>
+        <v>7068117</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9511,11 +9506,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9542,10 +9532,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123948054</v>
+        <v>123948081</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9554,25 +9544,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9582,10 +9572,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497062</v>
+        <v>497267</v>
       </c>
       <c r="R68" t="n">
-        <v>7068118</v>
+        <v>7068098</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9618,11 +9608,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9649,10 +9634,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123948056</v>
+        <v>123948085</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9665,21 +9650,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9689,10 +9674,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497093</v>
+        <v>497243</v>
       </c>
       <c r="R69" t="n">
-        <v>7068094</v>
+        <v>7067786</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9725,11 +9710,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9756,7 +9736,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123948057</v>
+        <v>123948071</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -9796,10 +9776,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497142</v>
+        <v>497830</v>
       </c>
       <c r="R70" t="n">
-        <v>7068071</v>
+        <v>7068267</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9863,10 +9843,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123948081</v>
+        <v>123948049</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9875,25 +9855,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9903,10 +9883,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497267</v>
+        <v>496958</v>
       </c>
       <c r="R71" t="n">
-        <v>7068098</v>
+        <v>7067783</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9939,6 +9919,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9965,7 +9950,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123948048</v>
+        <v>123948060</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -10005,10 +9990,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497417</v>
+        <v>497140</v>
       </c>
       <c r="R72" t="n">
-        <v>7067613</v>
+        <v>7067713</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10072,7 +10057,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948076</v>
+        <v>123948065</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -10112,10 +10097,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497599</v>
+        <v>497547</v>
       </c>
       <c r="R73" t="n">
-        <v>7068342</v>
+        <v>7068008</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10152,7 +10137,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10179,10 +10164,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948084</v>
+        <v>123948067</v>
       </c>
       <c r="B74" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10195,21 +10180,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10219,10 +10204,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497101</v>
+        <v>497567</v>
       </c>
       <c r="R74" t="n">
-        <v>7067728</v>
+        <v>7067939</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10255,6 +10240,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10281,7 +10271,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948079</v>
+        <v>123948077</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -10321,10 +10311,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497614</v>
+        <v>497583</v>
       </c>
       <c r="R75" t="n">
-        <v>7067898</v>
+        <v>7068342</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10361,7 +10351,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10388,7 +10378,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123948073</v>
+        <v>123948078</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -10428,10 +10418,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497810</v>
+        <v>497569</v>
       </c>
       <c r="R76" t="n">
-        <v>7068216</v>
+        <v>7068352</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10495,10 +10485,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123948078</v>
+        <v>123948083</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10511,21 +10501,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10535,10 +10525,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497569</v>
+        <v>497012</v>
       </c>
       <c r="R77" t="n">
-        <v>7068352</v>
+        <v>7067783</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10571,11 +10561,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10602,7 +10587,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123948074</v>
+        <v>123948041</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -10642,10 +10627,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497809</v>
+        <v>497578</v>
       </c>
       <c r="R78" t="n">
-        <v>7068221</v>
+        <v>7067475</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10682,7 +10667,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10709,7 +10694,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123948066</v>
+        <v>123948073</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -10749,10 +10734,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497568</v>
+        <v>497810</v>
       </c>
       <c r="R79" t="n">
-        <v>7067974</v>
+        <v>7068216</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10789,7 +10774,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10816,7 +10801,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123948049</v>
+        <v>123948076</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -10856,10 +10841,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496958</v>
+        <v>497599</v>
       </c>
       <c r="R80" t="n">
-        <v>7067783</v>
+        <v>7068342</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10896,7 +10881,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10923,10 +10908,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123948083</v>
+        <v>123948066</v>
       </c>
       <c r="B81" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10939,21 +10924,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10963,10 +10948,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>497012</v>
+        <v>497568</v>
       </c>
       <c r="R81" t="n">
-        <v>7067783</v>
+        <v>7067974</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10999,6 +10984,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11025,7 +11015,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123948069</v>
+        <v>123948058</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11065,10 +11055,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497544</v>
+        <v>497156</v>
       </c>
       <c r="R82" t="n">
-        <v>7067872</v>
+        <v>7067976</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11105,7 +11095,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11132,7 +11122,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123948051</v>
+        <v>123948064</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11172,10 +11162,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496962</v>
+        <v>497471</v>
       </c>
       <c r="R83" t="n">
-        <v>7067810</v>
+        <v>7067944</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11239,10 +11229,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123948075</v>
+        <v>123948084</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11255,21 +11245,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11279,10 +11269,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497629</v>
+        <v>497101</v>
       </c>
       <c r="R84" t="n">
-        <v>7068330</v>
+        <v>7067728</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11315,11 +11305,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11346,7 +11331,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123948063</v>
+        <v>123948070</v>
       </c>
       <c r="B85" t="n">
         <v>57513</v>
@@ -11386,10 +11371,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497448</v>
+        <v>497876</v>
       </c>
       <c r="R85" t="n">
-        <v>7067857</v>
+        <v>7068110</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11453,7 +11438,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123948064</v>
+        <v>123948079</v>
       </c>
       <c r="B86" t="n">
         <v>57513</v>
@@ -11493,10 +11478,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497471</v>
+        <v>497614</v>
       </c>
       <c r="R86" t="n">
-        <v>7067944</v>
+        <v>7067898</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11560,10 +11545,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123948037</v>
+        <v>123948056</v>
       </c>
       <c r="B87" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11576,21 +11561,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11600,10 +11585,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497443</v>
+        <v>497093</v>
       </c>
       <c r="R87" t="n">
-        <v>7067840</v>
+        <v>7068094</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11636,6 +11621,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11662,10 +11652,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123948082</v>
+        <v>123948074</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11674,25 +11664,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11702,10 +11692,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497300</v>
+        <v>497809</v>
       </c>
       <c r="R88" t="n">
-        <v>7068117</v>
+        <v>7068221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11738,6 +11728,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11764,7 +11759,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123948077</v>
+        <v>123948059</v>
       </c>
       <c r="B89" t="n">
         <v>57513</v>
@@ -11804,10 +11799,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497583</v>
+        <v>497338</v>
       </c>
       <c r="R89" t="n">
-        <v>7068342</v>
+        <v>7068065</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11844,7 +11839,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11871,7 +11866,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123948052</v>
+        <v>123948050</v>
       </c>
       <c r="B90" t="n">
         <v>57513</v>
@@ -11911,10 +11906,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>496977</v>
+        <v>496963</v>
       </c>
       <c r="R90" t="n">
-        <v>7067794</v>
+        <v>7067823</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11951,7 +11946,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11978,7 +11973,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123948068</v>
+        <v>123948069</v>
       </c>
       <c r="B91" t="n">
         <v>57513</v>
@@ -12018,10 +12013,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497549</v>
+        <v>497544</v>
       </c>
       <c r="R91" t="n">
-        <v>7067939</v>
+        <v>7067872</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12058,7 +12053,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12085,7 +12080,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123948059</v>
+        <v>123948051</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -12125,10 +12120,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497338</v>
+        <v>496962</v>
       </c>
       <c r="R92" t="n">
-        <v>7068065</v>
+        <v>7067810</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12165,7 +12160,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12192,7 +12187,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123948067</v>
+        <v>123948052</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -12232,10 +12227,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497567</v>
+        <v>496977</v>
       </c>
       <c r="R93" t="n">
-        <v>7067939</v>
+        <v>7067794</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12272,7 +12267,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12299,10 +12294,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123948085</v>
+        <v>123948068</v>
       </c>
       <c r="B94" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12315,21 +12310,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12339,10 +12334,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497243</v>
+        <v>497549</v>
       </c>
       <c r="R94" t="n">
-        <v>7067786</v>
+        <v>7067939</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12375,6 +12370,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12401,10 +12401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123934404</v>
+        <v>123932201</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12413,51 +12413,55 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>496972</v>
+        <v>497553</v>
       </c>
       <c r="R95" t="n">
-        <v>7067780</v>
+        <v>7068083</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12486,7 +12490,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12500,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12512,31 +12516,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12553,10 +12532,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123929267</v>
+        <v>123934404</v>
       </c>
       <c r="B96" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12569,42 +12548,47 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497833</v>
+        <v>496972</v>
       </c>
       <c r="R96" t="n">
-        <v>7067988</v>
+        <v>7067780</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12633,7 +12617,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12643,12 +12627,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12667,22 +12651,22 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12700,7 +12684,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123929067</v>
+        <v>123929700</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12736,7 +12720,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -12746,17 +12730,17 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497903</v>
+        <v>497829</v>
       </c>
       <c r="R97" t="n">
-        <v>7068110</v>
+        <v>7067835</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12785,7 +12769,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12795,12 +12779,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12814,7 +12798,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -12852,10 +12836,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123931338</v>
+        <v>123934695</v>
       </c>
       <c r="B98" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12864,48 +12848,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497552</v>
+        <v>497164</v>
       </c>
       <c r="R98" t="n">
-        <v>7067881</v>
+        <v>7067665</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12937,7 +12916,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12947,12 +12926,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12966,27 +12945,27 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13004,7 +12983,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123932552</v>
+        <v>123931338</v>
       </c>
       <c r="B99" t="n">
         <v>57513</v>
@@ -13043,19 +13022,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497461</v>
+        <v>497552</v>
       </c>
       <c r="R99" t="n">
-        <v>7067890</v>
+        <v>7067881</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13084,7 +13068,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13094,12 +13078,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13151,7 +13135,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123929700</v>
+        <v>123931433</v>
       </c>
       <c r="B100" t="n">
         <v>57513</v>
@@ -13187,7 +13171,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13197,14 +13181,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497829</v>
+        <v>497554</v>
       </c>
       <c r="R100" t="n">
-        <v>7067835</v>
+        <v>7067886</v>
       </c>
       <c r="S100" t="n">
         <v>8</v>
@@ -13236,7 +13220,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13246,12 +13230,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13265,7 +13249,7 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13303,10 +13287,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123934695</v>
+        <v>123929267</v>
       </c>
       <c r="B101" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13315,43 +13299,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497164</v>
+        <v>497833</v>
       </c>
       <c r="R101" t="n">
-        <v>7067665</v>
+        <v>7067988</v>
       </c>
       <c r="S101" t="n">
         <v>9</v>
@@ -13383,7 +13367,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13393,12 +13377,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13412,17 +13396,17 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
@@ -13432,7 +13416,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13450,10 +13434,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123932201</v>
+        <v>123929067</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13462,40 +13446,36 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13504,13 +13484,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497553</v>
+        <v>497903</v>
       </c>
       <c r="R102" t="n">
-        <v>7068083</v>
+        <v>7068110</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13539,7 +13519,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13549,12 +13529,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13565,6 +13545,31 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13581,7 +13586,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123931433</v>
+        <v>123932552</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13620,21 +13625,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497554</v>
+        <v>497461</v>
       </c>
       <c r="R103" t="n">
-        <v>7067886</v>
+        <v>7067890</v>
       </c>
       <c r="S103" t="n">
         <v>8</v>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -15098,7 +15098,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123948038</v>
+        <v>123948040</v>
       </c>
       <c r="B114" t="n">
         <v>57513</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497227</v>
+        <v>497269</v>
       </c>
       <c r="R114" t="n">
-        <v>7067047</v>
+        <v>7067065</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15205,10 +15205,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123948040</v>
+        <v>123948080</v>
       </c>
       <c r="B115" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15221,16 +15221,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497269</v>
+        <v>497370</v>
       </c>
       <c r="R115" t="n">
-        <v>7067065</v>
+        <v>7067042</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15312,7 +15312,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123948039</v>
+        <v>123948045</v>
       </c>
       <c r="B116" t="n">
         <v>57513</v>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497241</v>
+        <v>497439</v>
       </c>
       <c r="R116" t="n">
-        <v>7067063</v>
+        <v>7067336</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123948045</v>
+        <v>123948039</v>
       </c>
       <c r="B117" t="n">
         <v>57513</v>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497439</v>
+        <v>497241</v>
       </c>
       <c r="R117" t="n">
-        <v>7067336</v>
+        <v>7067063</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15526,10 +15526,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123948080</v>
+        <v>123948038</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497370</v>
+        <v>497227</v>
       </c>
       <c r="R118" t="n">
-        <v>7067042</v>
+        <v>7067047</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Hack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,10 +12401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123932201</v>
+        <v>123929700</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12413,52 +12413,48 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497553</v>
+        <v>497829</v>
       </c>
       <c r="R95" t="n">
-        <v>7068083</v>
+        <v>7067835</v>
       </c>
       <c r="S95" t="n">
         <v>8</v>
@@ -12490,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12500,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12516,6 +12512,31 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12532,10 +12553,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123934404</v>
+        <v>123932201</v>
       </c>
       <c r="B96" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12544,51 +12565,55 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>496972</v>
+        <v>497553</v>
       </c>
       <c r="R96" t="n">
-        <v>7067780</v>
+        <v>7068083</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12617,7 +12642,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12627,12 +12652,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12643,31 +12668,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12684,7 +12684,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123929700</v>
+        <v>123929067</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12720,7 +12720,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -12730,17 +12730,17 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497829</v>
+        <v>497903</v>
       </c>
       <c r="R97" t="n">
-        <v>7067835</v>
+        <v>7068110</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -12983,7 +12983,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123931338</v>
+        <v>123931433</v>
       </c>
       <c r="B99" t="n">
         <v>57513</v>
@@ -13033,13 +13033,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497552</v>
+        <v>497554</v>
       </c>
       <c r="R99" t="n">
-        <v>7067881</v>
+        <v>7067886</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13135,7 +13135,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123931433</v>
+        <v>123934404</v>
       </c>
       <c r="B100" t="n">
         <v>57513</v>
@@ -13181,17 +13181,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497554</v>
+        <v>496972</v>
       </c>
       <c r="R100" t="n">
-        <v>7067886</v>
+        <v>7067780</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13230,12 +13230,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13287,10 +13287,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123929267</v>
+        <v>123932552</v>
       </c>
       <c r="B101" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13303,27 +13303,27 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -13332,13 +13332,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497833</v>
+        <v>497461</v>
       </c>
       <c r="R101" t="n">
-        <v>7067988</v>
+        <v>7067890</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13401,22 +13401,22 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929067</v>
+        <v>123929267</v>
       </c>
       <c r="B102" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13450,32 +13450,27 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13484,10 +13479,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497903</v>
+        <v>497833</v>
       </c>
       <c r="R102" t="n">
-        <v>7068110</v>
+        <v>7067988</v>
       </c>
       <c r="S102" t="n">
         <v>9</v>
@@ -13519,7 +13514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13529,12 +13524,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13553,22 +13548,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13586,7 +13581,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123932552</v>
+        <v>123931338</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13625,19 +13620,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497461</v>
+        <v>497552</v>
       </c>
       <c r="R103" t="n">
-        <v>7067890</v>
+        <v>7067881</v>
       </c>
       <c r="S103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123929700</v>
+        <v>123931433</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12437,7 +12437,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -12447,14 +12447,14 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497829</v>
+        <v>497554</v>
       </c>
       <c r="R95" t="n">
-        <v>7067835</v>
+        <v>7067886</v>
       </c>
       <c r="S95" t="n">
         <v>8</v>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -12553,10 +12553,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123932201</v>
+        <v>123929267</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12565,40 +12565,31 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12607,13 +12598,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497553</v>
+        <v>497833</v>
       </c>
       <c r="R96" t="n">
-        <v>7068083</v>
+        <v>7067988</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12642,7 +12633,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12652,12 +12643,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12668,6 +12659,31 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12684,7 +12700,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123929067</v>
+        <v>123932552</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12723,24 +12739,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497903</v>
+        <v>497461</v>
       </c>
       <c r="R97" t="n">
-        <v>7068110</v>
+        <v>7067890</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12769,7 +12780,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12779,12 +12790,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12983,10 +12994,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123931433</v>
+        <v>123932201</v>
       </c>
       <c r="B99" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12995,36 +13006,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -13033,10 +13048,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497554</v>
+        <v>497553</v>
       </c>
       <c r="R99" t="n">
-        <v>7067886</v>
+        <v>7068083</v>
       </c>
       <c r="S99" t="n">
         <v>8</v>
@@ -13068,7 +13083,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13078,12 +13093,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13094,31 +13109,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13135,7 +13125,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123934404</v>
+        <v>123929067</v>
       </c>
       <c r="B100" t="n">
         <v>57513</v>
@@ -13181,17 +13171,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496972</v>
+        <v>497903</v>
       </c>
       <c r="R100" t="n">
-        <v>7067780</v>
+        <v>7068110</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13220,7 +13210,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13230,12 +13220,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13287,7 +13277,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123932552</v>
+        <v>123929700</v>
       </c>
       <c r="B101" t="n">
         <v>57513</v>
@@ -13323,19 +13313,24 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497461</v>
+        <v>497829</v>
       </c>
       <c r="R101" t="n">
-        <v>7067890</v>
+        <v>7067835</v>
       </c>
       <c r="S101" t="n">
         <v>8</v>
@@ -13367,7 +13362,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13377,12 +13372,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13396,7 +13391,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13434,10 +13429,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929267</v>
+        <v>123934404</v>
       </c>
       <c r="B102" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13450,42 +13445,47 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497833</v>
+        <v>496972</v>
       </c>
       <c r="R102" t="n">
-        <v>7067988</v>
+        <v>7067780</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13548,22 +13548,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,7 +12401,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123931433</v>
+        <v>123931338</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -12451,13 +12451,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497554</v>
+        <v>497552</v>
       </c>
       <c r="R95" t="n">
-        <v>7067886</v>
+        <v>7067881</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12700,7 +12700,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123932552</v>
+        <v>123931433</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12739,16 +12739,21 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497461</v>
+        <v>497554</v>
       </c>
       <c r="R97" t="n">
-        <v>7067890</v>
+        <v>7067886</v>
       </c>
       <c r="S97" t="n">
         <v>8</v>
@@ -12780,7 +12785,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12790,12 +12795,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12847,10 +12852,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123934695</v>
+        <v>123934404</v>
       </c>
       <c r="B98" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12859,31 +12864,36 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12892,13 +12902,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497164</v>
+        <v>496972</v>
       </c>
       <c r="R98" t="n">
-        <v>7067665</v>
+        <v>7067780</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12927,7 +12937,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12937,12 +12947,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12956,27 +12966,27 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12994,10 +13004,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123932201</v>
+        <v>123934695</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13006,55 +13016,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497553</v>
+        <v>497164</v>
       </c>
       <c r="R99" t="n">
-        <v>7068083</v>
+        <v>7067665</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13083,7 +13084,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13093,12 +13094,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13109,6 +13110,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13125,7 +13151,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123929067</v>
+        <v>123929700</v>
       </c>
       <c r="B100" t="n">
         <v>57513</v>
@@ -13161,7 +13187,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13171,17 +13197,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497903</v>
+        <v>497829</v>
       </c>
       <c r="R100" t="n">
-        <v>7068110</v>
+        <v>7067835</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13210,7 +13236,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13220,12 +13246,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13239,7 +13265,7 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13277,10 +13303,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123929700</v>
+        <v>123932201</v>
       </c>
       <c r="B101" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13289,48 +13315,52 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497829</v>
+        <v>497553</v>
       </c>
       <c r="R101" t="n">
-        <v>7067835</v>
+        <v>7068083</v>
       </c>
       <c r="S101" t="n">
         <v>8</v>
@@ -13362,7 +13392,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13372,12 +13402,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13388,31 +13418,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13429,7 +13434,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123934404</v>
+        <v>123929067</v>
       </c>
       <c r="B102" t="n">
         <v>57513</v>
@@ -13475,17 +13480,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496972</v>
+        <v>497903</v>
       </c>
       <c r="R102" t="n">
-        <v>7067780</v>
+        <v>7068110</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13514,7 +13519,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13524,12 +13529,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13581,7 +13586,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123931338</v>
+        <v>123932552</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13620,24 +13625,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497552</v>
+        <v>497461</v>
       </c>
       <c r="R103" t="n">
-        <v>7067881</v>
+        <v>7067890</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,10 +12401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123931338</v>
+        <v>123929267</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12417,32 +12417,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12451,10 +12446,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497552</v>
+        <v>497833</v>
       </c>
       <c r="R95" t="n">
-        <v>7067881</v>
+        <v>7067988</v>
       </c>
       <c r="S95" t="n">
         <v>9</v>
@@ -12486,7 +12481,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12491,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12520,22 +12515,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12553,10 +12548,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123929267</v>
+        <v>123934695</v>
       </c>
       <c r="B96" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12565,43 +12560,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497833</v>
+        <v>497164</v>
       </c>
       <c r="R96" t="n">
-        <v>7067988</v>
+        <v>7067665</v>
       </c>
       <c r="S96" t="n">
         <v>9</v>
@@ -12633,7 +12628,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12643,12 +12638,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12662,17 +12657,17 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -12682,7 +12677,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12700,7 +12695,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123931433</v>
+        <v>123932552</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12739,21 +12734,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497554</v>
+        <v>497461</v>
       </c>
       <c r="R97" t="n">
-        <v>7067886</v>
+        <v>7067890</v>
       </c>
       <c r="S97" t="n">
         <v>8</v>
@@ -12785,7 +12775,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12795,12 +12785,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12852,7 +12842,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123934404</v>
+        <v>123929067</v>
       </c>
       <c r="B98" t="n">
         <v>57513</v>
@@ -12898,17 +12888,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496972</v>
+        <v>497903</v>
       </c>
       <c r="R98" t="n">
-        <v>7067780</v>
+        <v>7068110</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12937,7 +12927,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12947,12 +12937,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13004,10 +12994,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123934695</v>
+        <v>123934404</v>
       </c>
       <c r="B99" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13016,31 +13006,36 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -13049,13 +13044,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497164</v>
+        <v>496972</v>
       </c>
       <c r="R99" t="n">
-        <v>7067665</v>
+        <v>7067780</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13084,7 +13079,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13094,12 +13089,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13113,27 +13108,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13151,10 +13146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123929700</v>
+        <v>123932201</v>
       </c>
       <c r="B100" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13163,48 +13158,52 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497829</v>
+        <v>497553</v>
       </c>
       <c r="R100" t="n">
-        <v>7067835</v>
+        <v>7068083</v>
       </c>
       <c r="S100" t="n">
         <v>8</v>
@@ -13236,7 +13235,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13246,12 +13245,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13262,31 +13261,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13303,10 +13277,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123932201</v>
+        <v>123931338</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13315,40 +13289,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -13357,13 +13327,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497553</v>
+        <v>497552</v>
       </c>
       <c r="R101" t="n">
-        <v>7068083</v>
+        <v>7067881</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13392,7 +13362,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13402,12 +13372,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13418,6 +13388,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13434,7 +13429,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929067</v>
+        <v>123929700</v>
       </c>
       <c r="B102" t="n">
         <v>57513</v>
@@ -13470,7 +13465,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -13480,17 +13475,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497903</v>
+        <v>497829</v>
       </c>
       <c r="R102" t="n">
-        <v>7068110</v>
+        <v>7067835</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13519,7 +13514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13529,12 +13524,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13548,7 +13543,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13586,7 +13581,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123932552</v>
+        <v>123931433</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13625,16 +13620,21 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497461</v>
+        <v>497554</v>
       </c>
       <c r="R103" t="n">
-        <v>7067890</v>
+        <v>7067886</v>
       </c>
       <c r="S103" t="n">
         <v>8</v>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,10 +12401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123929267</v>
+        <v>123934404</v>
       </c>
       <c r="B95" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12417,42 +12417,47 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497833</v>
+        <v>496972</v>
       </c>
       <c r="R95" t="n">
-        <v>7067988</v>
+        <v>7067780</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12481,7 +12486,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12491,12 +12496,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Färska och äldre ringhack på en levande gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12515,22 +12520,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12548,10 +12553,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123934695</v>
+        <v>123929700</v>
       </c>
       <c r="B96" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12560,46 +12565,51 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Ängstadviken, Ängstadviken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497164</v>
+        <v>497829</v>
       </c>
       <c r="R96" t="n">
-        <v>7067665</v>
+        <v>7067835</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12628,7 +12638,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12638,12 +12648,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12662,22 +12672,22 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12695,7 +12705,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123932552</v>
+        <v>123931338</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12734,19 +12744,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497461</v>
+        <v>497552</v>
       </c>
       <c r="R97" t="n">
-        <v>7067890</v>
+        <v>7067881</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12775,7 +12790,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12785,12 +12800,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Gott om både färska och äldre ringhack på en gran.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12842,10 +12857,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123929067</v>
+        <v>123929267</v>
       </c>
       <c r="B98" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12858,32 +12873,27 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12892,10 +12902,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497903</v>
+        <v>497833</v>
       </c>
       <c r="R98" t="n">
-        <v>7068110</v>
+        <v>7067988</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12927,7 +12937,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12937,12 +12947,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12961,22 +12971,22 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12994,10 +13004,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123934404</v>
+        <v>123934695</v>
       </c>
       <c r="B99" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13006,36 +13016,31 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -13044,13 +13049,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496972</v>
+        <v>497164</v>
       </c>
       <c r="R99" t="n">
-        <v>7067780</v>
+        <v>7067665</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13079,7 +13084,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13089,12 +13094,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13108,27 +13113,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13146,10 +13151,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123932201</v>
+        <v>123931433</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13158,40 +13163,36 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -13200,10 +13201,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497553</v>
+        <v>497554</v>
       </c>
       <c r="R100" t="n">
-        <v>7068083</v>
+        <v>7067886</v>
       </c>
       <c r="S100" t="n">
         <v>8</v>
@@ -13235,7 +13236,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13245,12 +13246,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13261,6 +13262,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13277,10 +13303,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123931338</v>
+        <v>123932201</v>
       </c>
       <c r="B101" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13289,36 +13315,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -13327,13 +13357,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497552</v>
+        <v>497553</v>
       </c>
       <c r="R101" t="n">
-        <v>7067881</v>
+        <v>7068083</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13362,7 +13392,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13372,12 +13402,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13388,31 +13418,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13429,7 +13434,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929700</v>
+        <v>123929067</v>
       </c>
       <c r="B102" t="n">
         <v>57513</v>
@@ -13465,7 +13470,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -13475,17 +13480,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497829</v>
+        <v>497903</v>
       </c>
       <c r="R102" t="n">
-        <v>7067835</v>
+        <v>7068110</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13514,7 +13519,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13524,12 +13529,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13543,7 +13548,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13581,7 +13586,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123931433</v>
+        <v>123932552</v>
       </c>
       <c r="B103" t="n">
         <v>57513</v>
@@ -13620,21 +13625,16 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497554</v>
+        <v>497461</v>
       </c>
       <c r="R103" t="n">
-        <v>7067886</v>
+        <v>7067890</v>
       </c>
       <c r="S103" t="n">
         <v>8</v>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13676,12 +13676,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -13004,10 +13004,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123934695</v>
+        <v>123931433</v>
       </c>
       <c r="B99" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13016,46 +13016,51 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497164</v>
+        <v>497554</v>
       </c>
       <c r="R99" t="n">
-        <v>7067665</v>
+        <v>7067886</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13084,7 +13089,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13094,12 +13099,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Tydligt färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13113,27 +13118,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13151,10 +13156,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123931433</v>
+        <v>123934695</v>
       </c>
       <c r="B100" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13163,51 +13168,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497554</v>
+        <v>497164</v>
       </c>
       <c r="R100" t="n">
-        <v>7067886</v>
+        <v>7067665</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Tydligt färska ringhack på en gran.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13265,27 +13265,27 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>

--- a/artfynd/A 10092-2025 artfynd.xlsx
+++ b/artfynd/A 10092-2025 artfynd.xlsx
@@ -12401,10 +12401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123934404</v>
+        <v>123929267</v>
       </c>
       <c r="B95" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12417,47 +12417,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>496972</v>
+        <v>497833</v>
       </c>
       <c r="R95" t="n">
-        <v>7067780</v>
+        <v>7067988</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12486,7 +12481,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12496,12 +12491,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på en levande gran.</t>
+          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12520,22 +12515,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12553,7 +12548,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123929700</v>
+        <v>123929067</v>
       </c>
       <c r="B96" t="n">
         <v>57513</v>
@@ -12589,7 +12584,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -12599,17 +12594,17 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ängstadviken, Ängstadviken, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497829</v>
+        <v>497903</v>
       </c>
       <c r="R96" t="n">
-        <v>7067835</v>
+        <v>7068110</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12638,7 +12633,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12648,12 +12643,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Färska och äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12667,7 +12662,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -12705,7 +12700,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123931338</v>
+        <v>123932552</v>
       </c>
       <c r="B97" t="n">
         <v>57513</v>
@@ -12744,24 +12739,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497552</v>
+        <v>497461</v>
       </c>
       <c r="R97" t="n">
-        <v>7067881</v>
+        <v>7067890</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12790,7 +12780,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12800,12 +12790,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack längs flera meter på en granstam.</t>
+          <t>Gott om både färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12857,10 +12847,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123929267</v>
+        <v>123931338</v>
       </c>
       <c r="B98" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12873,27 +12863,32 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12902,10 +12897,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497833</v>
+        <v>497552</v>
       </c>
       <c r="R98" t="n">
-        <v>7067988</v>
+        <v>7067881</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12937,7 +12932,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12947,12 +12942,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en gammal flerstammig sälg med delvis knäckt stam.</t>
+          <t>Färska ringhack längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12971,22 +12966,22 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13156,10 +13151,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123934695</v>
+        <v>123932201</v>
       </c>
       <c r="B100" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13168,46 +13163,55 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stryån, Stryån, Jmt</t>
+          <t>Långflon, Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497164</v>
+        <v>497553</v>
       </c>
       <c r="R100" t="n">
-        <v>7067665</v>
+        <v>7068083</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13236,7 +13240,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13246,12 +13250,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13262,31 +13266,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13303,10 +13282,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123932201</v>
+        <v>123934695</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13315,55 +13294,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497553</v>
+        <v>497164</v>
       </c>
       <c r="R101" t="n">
-        <v>7068083</v>
+        <v>7067665</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13392,7 +13362,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13402,12 +13372,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13418,6 +13388,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13434,7 +13429,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123929067</v>
+        <v>123934404</v>
       </c>
       <c r="B102" t="n">
         <v>57513</v>
@@ -13480,17 +13475,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långflon, Långflon, Jmt</t>
+          <t>Stryån, Stryån, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497903</v>
+        <v>496972</v>
       </c>
       <c r="R102" t="n">
-        <v>7068110</v>
+        <v>7067780</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13519,7 +13514,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-  